--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,16 +526,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -545,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-623.0099999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.57401e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-72.952</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1650674662668564</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5549845837615387</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.363128930817634</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.149577294685953</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.93084244871603</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.45292921465098</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 12.574x + -28201.092</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-28201.09178890567</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.056416622690032e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>623.0099999999998</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000016756e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8242676901990474</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-504.3099999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.56412e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-74.56399999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2736116545982634</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.268378182860415</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.15031638533613</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.674168130089671</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.80286403888009</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.097124853336</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 14.658x + -31360.187</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-31360.18726880851</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.112707972135273e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>504.3099999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8241254196300632</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-469.9100000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.55721e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-75.127</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.51330888409691</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.414204342249551</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.604457362102806</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.96022294770729</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.14648789362288</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 14.846x + -31127.174</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-31127.173971162</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.815855118874455e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>469.9100000000003</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8237063366450689</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-419.7399999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.55024e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-75.589</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4702481162184389</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9661719137756178</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.293539875683755</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.946403148114801</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.56198688339764</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.59878191968943</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 16.826x + -35125.198</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-35125.19756241179</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.63302351941651e-11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>419.7399999999998</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8234555665830496</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-399.7500000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.54605e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-75.898</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3791940254858774</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.126468990099835</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.15136111918272</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.846486941498246</v>
+      </c>
+      <c r="J6" t="n">
+        <v>44.74587739047713</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.71561516356934</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 17.426x + -35969.188</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-35969.18841330808</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.488599732128164e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>399.7500000000002</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001406e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8234316890880138</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-405.3399999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.5422e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.18000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1069857373370196</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3685025977628416</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.281113549117138</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.40172463083164</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.79253006075959</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.46749422115867</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 16.199x + -32754.611</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-32754.61125789627</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.765633490352265e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>405.3399999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000069956e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8235496976852456</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-385.0799999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.53894e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-76.45699999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1276451266109239</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9308488260428285</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.713901477001346</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.915748445427535</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.21684934252337</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.69009664940322</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 17.291x + -34622.080</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-34622.08000848163</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.956228576195496e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>385.0799999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000019195e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8238142756687453</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-367.98</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.53697e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-76.702</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1727803459943715</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9901722831672802</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.107277902920565</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.457085246361697</v>
+      </c>
+      <c r="J9" t="n">
+        <v>43.03532824807541</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.87893981558044</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 18.340x + -36377.157</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-36377.15682085705</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.814563337053614e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>367.98</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000029614e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8241104811090402</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-358.04</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.53505e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-76.91</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3824880002434367</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.24481106596834</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.32645342256603</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.825841798127732</v>
+      </c>
+      <c r="J10" t="n">
+        <v>44.55603278052667</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.94331169274881</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 18.727x + -36705.949</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-36705.94919155094</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.23578224501478e-07</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000441e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8244502093963471</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-357.1300000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.53331e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.114</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1390257733706653</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8892175097959155</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.850109721214845</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.237524751820191</v>
+      </c>
+      <c r="J11" t="n">
+        <v>38.70147375986723</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.9312949383677</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 18.653x + -36054.009</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-36054.00851363573</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.74785093408461e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>357.1300000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000217e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8247941255967071</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,16 +1192,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -693,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-502.9199999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.50004e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.64</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06425795817064275</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6076386554385961</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.360816358586916</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.507661216995888</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26.7300899720776</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.89058114120699</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 13.919x + -28991.162</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-28991.16153508377</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.510135070532941e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>502.9199999999998</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000001778e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8265850089570875</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-454.5299999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.51102e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.379</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3932157403624341</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.013037356104345</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.982198547551324</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.914076583735237</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33.86824046029018</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.31767280895311</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 15.538x + -30954.554</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-30954.55371271355</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.79831657726653e-07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>454.5299999999997</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000024504e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8267268638347558</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-439.6499999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.51466e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.627</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5876815472593551</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.075886618148008</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.150526073785553</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.048025814431051</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.2842781878584</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.4262846092787</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 16.012x + -31391.212</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-31391.21171684274</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.991055649108947e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>439.6499999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000051e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8266248727835603</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-430.99</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.5165e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.818</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.222575220508038</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9611648272170795</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.613633973016985</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.965925485010344</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.94690100165576</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.39875074378122</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 15.889x + -30736.738</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-30736.7377805057</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.850830035747453e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>430.99</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000080165e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8266088071396418</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-427.6199999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.51811e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.982</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1440046312661648</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5818661082500007</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.614685331608231</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.513492003480348</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.18670127139052</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.35648859664379</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 15.704x + -29952.366</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-29952.36625244576</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.844789500519175e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>427.6199999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000004047e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8267189876327405</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-420.1199999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.51943e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.14</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04717061174936945</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6962426477528748</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.585955181025398</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.43276517004047</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.7214047661177</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.4199536652922</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 15.983x + -30162.526</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-30162.5259755867</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.52258029742102e-07</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>420.1199999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8268609504714997</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-411.7600000000002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.5207e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.29000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2315810190666911</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8737129437598938</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.510702469073988</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.182012128743176</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.45296193901632</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.49432150808033</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 16.323x + -30478.487</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-30478.48684392136</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.485356779899677e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>411.7600000000002</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000008346e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8270277682538686</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-413.1200000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.5216e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.437</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1948243618132591</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7170322281104334</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.188964489315391</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.234167935281457</v>
+      </c>
+      <c r="J9" t="n">
+        <v>28.1796550393625</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.43294306281678</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 16.042x + -29548.280</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-29548.28009746718</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.025157866703415e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>413.1200000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8272128362855552</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-398.1199999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.52248e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.578</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3564582982927729</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9738072229168079</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.692213325284977</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.749505495319023</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35.48587501248416</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.69212434102343</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 17.302x + -31727.570</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-31727.57024208668</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.363936699890571e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>398.1199999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8274422784139749</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-399.3900000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.52341e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.712</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2534407658758364</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5916940763955781</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.206825929620066</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.097144385010214</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29.2297717000819</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.56174560042169</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 16.644x + -30061.464</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-30061.4637081375</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.247260777176046e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>399.3900000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000136e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8276841655474365</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-385.4700000000003</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.52439e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-77.849</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3503153845720646</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.123751886717174</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.767942774096321</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.080443501320247</v>
+      </c>
+      <c r="J12" t="n">
+        <v>36.93495941832646</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.81621396371668</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 17.978x + -32328.598</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-32328.5981546775</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.956810348397113e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>385.4700000000003</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000007325e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8279487310879348</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-393.46</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.52549e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-77.97799999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.07213260358113249</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6803670196235168</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.712619851829439</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.338202816288167</v>
+      </c>
+      <c r="J13" t="n">
+        <v>43.62611715266262</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.56116836155518</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 16.641x + -29390.551</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-29390.55095881574</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.863094206737142e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>393.46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8282284202666524</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-381.6299999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.52653e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-78.114</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3514438450363402</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7614099968617162</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.126480799921935</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.287398595663241</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30.9549680883127</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.70606722612064</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 17.375x + -30458.102</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-30458.10196291071</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.533076738296481e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>381.6299999999999</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8285339454945814</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-376.5700000000002</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.52702e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.23699999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6028740639987121</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6861836116186314</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.147178207744133</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.194050857629477</v>
+      </c>
+      <c r="J15" t="n">
+        <v>31.69488557103657</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.75790308421584</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 17.654x + -30643.927</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-30643.92707375035</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.423201680666198e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>376.5700000000002</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.00000000000358e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8288536447033206</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-368.3100000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.5283e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.36799999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2073903397471574</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8684943637873257</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.235085901281633</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.280292783794675</v>
+      </c>
+      <c r="J16" t="n">
+        <v>32.14686701685889</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.82729542649483</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 18.041x + -31012.742</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-31012.74184024507</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.717588606704249e-11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>368.3100000000002</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8291749244229223</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-375.6699999999998</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.5291e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.48399999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.06791133519174512</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6143765304703964</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.469837583735835</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.952546405014778</v>
+      </c>
+      <c r="J17" t="n">
+        <v>40.40165298776852</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.68360062180015</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 17.257x + -29230.517</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-29230.51674900182</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.576323773700991e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>375.6699999999998</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.829507767945693</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-359.3899999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.52989e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-78.624</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4030431277504534</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5960450346988236</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.287878751417443</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.702405313590097</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33.48814521033854</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.9144181668314</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 18.551x + -31257.842</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-31257.84190078008</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.013589953556943e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>359.3899999999999</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000001457e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8298581761819848</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-357.77</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.53084e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-78.748</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0215291921705341</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8857525904918987</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.995128975193394</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.624781518826493</v>
+      </c>
+      <c r="J19" t="n">
+        <v>49.5543184928886</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.87903498585916</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 18.340x + -30525.324</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-30525.32398314323</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.953048004923163e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>357.77</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.0000000000009e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8302197522919494</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-345.74</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.53203e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-78.881</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4723982132646455</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.017224856929306</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.329350434276381</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.276299143391189</v>
+      </c>
+      <c r="J20" t="n">
+        <v>35.07082730472803</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.02362293112694</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 19.233x + -31775.450</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-31775.45002257308</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.841031908188941e-11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>345.74</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8305808911348863</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-349.1199999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.5329e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-79.012</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1363695274804358</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7788871450986161</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.762340884121442</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.887475269664472</v>
+      </c>
+      <c r="J21" t="n">
+        <v>44.75524764933483</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.88913060003294</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 18.400x + -29922.067</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-29922.06724334456</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.242137843961746e-07</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>349.1199999999999</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8309558658949489</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-338.77</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.53389e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.129</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1060031320689041</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9623639413515105</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.882772455950384</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.775384402384164</v>
+      </c>
+      <c r="J22" t="n">
+        <v>52.24298591091859</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.03347136547411</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 19.297x + -31136.932</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-31136.93196388157</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.494309733862835e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>338.77</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8313228917593165</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,16 +2430,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -841,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-525.4000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.53124e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-74.625</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1801920256102183</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8393173089589898</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.467900516677071</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.897011830636001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26.89246783280537</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.89071615359568</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 13.919x + -30166.940</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-30166.94007316015</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.05281980478126e-13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>525.4000000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8251954356590534</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-448.2999999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.53789e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.79600000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02652691608029523</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3467496334630583</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.306101189873482</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.281490483888315</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26.73770044640898</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.1608278406142</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 14.902x + -30519.508</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-30519.50844804617</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.660224636532493e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>448.2999999999997</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000403e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8252864880973554</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-404.02</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.53565e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.209</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1916138106092728</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.002635331976212</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.69541612363482</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.35585643513833</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.00938769098927</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.57862696020709</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 16.727x + -33959.316</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-33959.31579090837</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.182037553156567e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>404.02</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000266e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8250530874427202</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-375.6399999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.53249e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.479</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6667620513131908</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.13615347427783</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.558056504054709</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.938892018392753</v>
+      </c>
+      <c r="J5" t="n">
+        <v>51.71403513644741</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.81806056477348</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 17.988x + -36290.286</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-36290.28550049723</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.514443058564051e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>375.6399999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000171e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8249425961151271</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-382.3599999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.53002e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.69499999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2509806960501849</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6303373967366028</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.189991576524773</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.230030849991817</v>
+      </c>
+      <c r="J6" t="n">
+        <v>32.10123922334103</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.53586969744448</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 16.520x + -32714.961</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-32714.96106571314</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.519367777101565e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>382.3599999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000005195e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8249900597356645</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-354.0700000000002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.52852e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.88200000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9773197322887962</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.261542882318882</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.341347683936883</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.148338173970164</v>
+      </c>
+      <c r="J7" t="n">
+        <v>56.65936494051753</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.94878174546064</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 18.760x + -37110.335</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-37110.33527682364</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.215015646185163e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>354.0700000000002</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000486655e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8251202635819013</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-356.72</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.52785e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.05200000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5367234467856273</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.072882720097479</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.895963325935674</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.600027398843837</v>
+      </c>
+      <c r="J8" t="n">
+        <v>45.59247811833898</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.87770306304131</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 18.332x + -35776.915</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-35776.91518777932</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.521091378039949e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>356.72</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8252998589228745</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-353.77</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.52729e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.212</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.317386472600338</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.068921856582534</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.680452373574527</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.971917522759614</v>
+      </c>
+      <c r="J9" t="n">
+        <v>39.63199549800601</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.84706650513631</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 18.154x + -35000.370</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-35000.37010581527</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.685100697067799e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>353.77</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8254979992962646</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-347.2399999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.5272e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.36499999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4509203318924647</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.914255683905449</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.651544009852143</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.110013865780466</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40.4382655462739</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.90282034536423</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 18.481x + -35287.150</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-35287.14975881372</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.090302632229841e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>347.2399999999998</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000109261e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8257033486524447</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-344.2400000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.52684e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.50700000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2447465250465831</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5276828962240485</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.335563245290159</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.508110204517596</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35.96843208271671</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.86137687425156</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 18.237x + -34407.431</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-34407.43105320478</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.937229951758916e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>344.2400000000002</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000429e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8259341023867339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-335.3699999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.52707e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-77.657</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2947751144627036</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6058344562378516</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.263029464626446</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.429218489871278</v>
+      </c>
+      <c r="J12" t="n">
+        <v>36.84529562467973</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.91743783836387</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 18.569x + -34705.311</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-34705.3107485142</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.499255348249995e-12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>335.3699999999999</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8262020762927021</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-332.99</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.52718e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-77.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3909943412414645</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7338519648944231</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.454334862191505</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.917137437768965</v>
+      </c>
+      <c r="J13" t="n">
+        <v>37.71961080006641</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.95814273549837</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 18.818x + -34809.402</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-34809.40230175739</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.087622909754997e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>332.99</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000122232e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8264990874504575</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-326.0100000000002</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.52771e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-77.955</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.311509654026523</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8079733326397429</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.684933848340813</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.749402605756793</v>
+      </c>
+      <c r="J14" t="n">
+        <v>38.75544178424765</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.00304408435548</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 19.101x + -34976.813</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-34976.81278903653</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.525177688158116e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>326.0100000000002</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8268283521545878</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-324.01</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.52781e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.09</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2829165222740225</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9387506862166443</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.668597414829905</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.884688303713231</v>
+      </c>
+      <c r="J15" t="n">
+        <v>39.50877383454537</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.04276874533961</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 19.358x + -35072.032</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-35072.03224711869</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.664232797329004e-07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>324.01</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000005796e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8271788112347632</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-317.4999999999998</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.52811e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.22499999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4279143569390065</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5565234833939996</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.541323358907429</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.990274379990816</v>
+      </c>
+      <c r="J16" t="n">
+        <v>40.45841648378202</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.09344548909095</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 19.696x + -35328.713</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-35328.71272590429</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.89096825964452e-11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>317.4999999999998</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8275372123783906</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-306.2199999999998</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.52868e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.369</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4960560544405491</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.289551303158387</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.136175569799037</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.365018809311994</v>
+      </c>
+      <c r="J17" t="n">
+        <v>47.59883504618947</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.23894294840383</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 20.735x + -36897.207</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-36897.20660805568</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.978464390456257e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>306.2199999999998</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8278950204766552</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-308.04</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.52882e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-78.51000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1351890199679069</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.016811985602027</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.091682274277697</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.804691196863292</v>
+      </c>
+      <c r="J18" t="n">
+        <v>42.19934442486388</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.17351607895897</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 20.255x + -35564.236</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-35564.23592944665</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.284714122398459e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>308.04</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000346e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8282612677417099</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-298.8399999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.52934e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-78.65300000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5099623627577058</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9182516642162626</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.640542615174507</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.974601823056653</v>
+      </c>
+      <c r="J19" t="n">
+        <v>42.89551335266252</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.22612169028926</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 20.639x + -35864.193</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-35864.19313921292</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.354485503458207e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>298.8399999999999</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000003194e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8286278357126966</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-299.3900000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.53015e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-78.792</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.09914873155188095</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.4330389528465312</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.542463069421675</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.344261144732145</v>
+      </c>
+      <c r="J20" t="n">
+        <v>39.23390355961232</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.14887220293056</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 20.079x + -34407.531</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-34407.53095909335</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.139287850934626e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>299.3900000000001</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000001523e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8290005492378028</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-300.7099999999998</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.53017e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-78.914</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1945374400380215</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7858199823204817</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.028605367811144</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.778542340618885</v>
+      </c>
+      <c r="J21" t="n">
+        <v>62.53606866656896</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.1156343712935</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 19.847x + -33569.697</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-33569.69663751725</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.362127781428673e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>300.7099999999998</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8293730125661111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-285.3499999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.53087e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.059</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1807140068647638</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9691180518124376</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.875278098436351</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.165418035876983</v>
+      </c>
+      <c r="J22" t="n">
+        <v>45.89279931207455</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.35126644074171</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 21.616x + -36339.819</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-36339.8189413394</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.372464324196523e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>285.3499999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8297530188150996</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,16 +3668,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -989,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-840.25</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.5001e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-70.41200000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2178094390026852</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.579598051157125</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.347343251859648</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.991102803738245</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.13765766583666</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.19046246294992</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 9.829x + -24997.431</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-24997.43137088413</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.303982630054166e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>840.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000181e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8258388708884479</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-620.2400000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.54464e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-73.14</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2031715103409918</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9477794160965117</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.686984166233768</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.027621698722696</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.81224853521792</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.28715285424678</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 12.130x + -27565.470</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-27565.46982795976</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.027264422883348e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>620.2400000000002</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8265687249403512</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-522.1799999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.54627e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-74.203</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2641956650395271</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8302785451606841</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.975736698305918</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.187621221848168</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.51938106155979</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.80846979182415</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 13.645x + -30145.256</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-30145.25553207761</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.490016179154979e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>522.1799999999998</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8265884527879066</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-475.6400000000003</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.54211e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-74.762</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2295164204649512</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.00616242414245</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.889171803704261</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.402527621983111</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.91859604907683</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.05945880664815</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 14.517x + -31587.872</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-31587.87185633738</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.144489126443623e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>475.6400000000003</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8265766186621232</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-440.3799999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.54191e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-75.22199999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1256973254048485</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7692802743076637</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.838299579266176</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.679565167381093</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.3280694541386</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.11307700200918</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 14.718x + -31474.984</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-31474.98355327969</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.548216533372171e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>440.3799999999997</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000003255e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8266483033213513</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-409.71</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.54119e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-75.56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3900544419199495</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.233916613513748</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.274215194199154</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.53929771433787</v>
+      </c>
+      <c r="J7" t="n">
+        <v>47.76445268272009</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.35285388353074</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 15.689x + -33203.451</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-33203.45057500096</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.732947559555632e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>409.71</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000745e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8267952413704284</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-396.3199999999997</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.54148e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-75.866</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1033303887548405</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9315123319930231</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.785893231407031</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.835390709562708</v>
+      </c>
+      <c r="J8" t="n">
+        <v>39.55742931302856</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.33888110495191</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 15.628x + -32524.185</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-32524.18541169792</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>55.32024370684625</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>396.3199999999997</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.21800867779173e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8153662182863143</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-376.7100000000003</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.54227e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-76.111</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4442439458367829</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9774636523192359</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.900375628405256</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.621944916236063</v>
+      </c>
+      <c r="J9" t="n">
+        <v>54.57605873390234</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.54551968335916</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 16.566x + -34119.538</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-34119.53825081394</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.279973392616429e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>376.7100000000003</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000267e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8271923041919251</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-362.6399999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.54354e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-76.369</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4929539753827957</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.152963934241642</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.035337931022544</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.767788394829134</v>
+      </c>
+      <c r="J10" t="n">
+        <v>59.02001720643462</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.63348124091696</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 17.000x + -34552.016</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-34552.01601601497</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.131601412929603e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>362.6399999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000002425e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8274572559379482</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-366.0299999999997</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.5438e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-76.583</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1610144074664977</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6465140278659557</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.213670559821654</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.60206611131509</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36.88207102180518</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.44959084298355</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 16.117x + -32136.093</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-32136.09250418279</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.417712274107404e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>366.0299999999997</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8277414423943498</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,16 +4334,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1137,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-610.2400000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.55122e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-73.96299999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.343244108179024</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.170537229285486</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.728661101182546</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.254400102491897</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23.849220500133</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.4708409920854</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 12.624x + -27105.564</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-27105.56415712392</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.447897582249577e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>610.2400000000002</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000419e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8269099999641284</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-472.5199999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.54604e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.68300000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09405656314112094</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6759690630915296</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.413615112024564</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.381917775512362</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.52172227402621</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.05000010707244</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 14.482x + -29385.844</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29385.84419624559</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.205559113675395e-07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>472.5199999999998</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8271180947318536</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-412.55</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.5459e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.233</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2975143819293747</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9937159720115946</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.726695406741832</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.111951068656441</v>
+      </c>
+      <c r="J4" t="n">
+        <v>37.63415879425644</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.42140310113929</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 15.990x + -31996.782</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-31996.78182317718</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.485706429267026e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>412.55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000015418e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8270087841248112</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-387.5799999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.54624e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.518</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1338677250870446</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.113558802404923</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.853608714771259</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.105258843879832</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40.52170442952787</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.56204422563872</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 16.646x + -32934.342</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-32934.34229431956</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.632115304134711e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>387.5799999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000057924e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8269396847626918</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-383.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.54669e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.70999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09486613269935072</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7709446144972689</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.543080741583905</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.927732674784138</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.45556063195478</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.51364633659323</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 16.414x + -32047.954</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-32047.95423730018</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.985211892199435e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000274e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.826894879562493</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-370.26</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.54689e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.892</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2059889110799717</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8203002462826183</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.542490154682773</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.682035734203371</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37.21257938312691</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.59770310977548</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 16.821x + -32526.562</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-32526.56197133243</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.891140733194403e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>370.26</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8269644167517142</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-371.8799999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.54753e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.045</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06303532466437811</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6014548418497445</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.272114318500783</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.350095472693655</v>
+      </c>
+      <c r="J8" t="n">
+        <v>33.13941568566664</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.52518866776535</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 16.469x + -31434.637</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-31434.63661951823</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.73059805577069e-07</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>371.8799999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000143e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8270838825182354</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-362.5799999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.54803e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.20399999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3188553373832474</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7285232382870646</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.522897906501201</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.296334669115968</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33.9281509626128</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.60289325858444</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 16.846x + -31850.460</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-31850.46018202034</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.111847671222076e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>362.5799999999999</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000265015e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.827259533955124</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-342.3600000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.54834e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.358</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3400186619084299</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.330540225779815</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.221899365461815</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.463382798537753</v>
+      </c>
+      <c r="J10" t="n">
+        <v>48.14014036384618</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.89942277969941</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 18.461x + -34772.737</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-34772.73658822454</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.644906582154696e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>342.3600000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8275119222540035</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-348.3599999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.5487e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.506</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2121515769327901</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9506481374953056</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.148694459376462</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.634505929817847</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35.50976064383462</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.73429990381979</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 17.526x + -32495.997</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-32495.99702496241</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.996092547629272e-12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>348.3599999999999</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8278024218732957</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-340.8999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.54927e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-77.679</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.09489999484065412</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4311979777969741</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.190339657586836</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.099742607596265</v>
+      </c>
+      <c r="J12" t="n">
+        <v>32.76931080055596</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.67873190410205</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 17.232x + -31530.902</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-31530.90224453312</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.114934500518794e-07</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>340.8999999999999</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000032092e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8281110816190586</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-339.7200000000003</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.54918e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-77.82299999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.007234616303934139</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.3586948838538097</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.158081667695954</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.026069947177137</v>
+      </c>
+      <c r="J13" t="n">
+        <v>33.11977045828908</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.71155560266718</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 17.404x + -31509.526</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-31509.52581457571</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.32968214810881e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>339.7200000000003</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000099046e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8284451324124779</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-320.9699999999998</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.54987e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-77.97799999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4581958408014727</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9793960053568523</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.528639437143441</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.915934468164805</v>
+      </c>
+      <c r="J14" t="n">
+        <v>44.70218133334625</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.99640089905161</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 19.058x + -34341.293</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-34341.29255935515</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.504153050287589e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>320.9699999999998</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000566e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8287898612707991</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-315.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.55014e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.126</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3645261053263743</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.09889366822235</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.846404053311056</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.261631878503264</v>
+      </c>
+      <c r="J15" t="n">
+        <v>45.46974460640434</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.05216231562386</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 19.419x + -34612.018</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-34612.01789997334</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.083282705389819e-07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>315.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000035747e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8291597473511912</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-308.0999999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.55091e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.28</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2833758296267709</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.063099600661028</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.748898640851663</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.212672966300171</v>
+      </c>
+      <c r="J16" t="n">
+        <v>46.58390217819283</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.11243818638889</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 19.825x + -34961.106</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-34961.10598432533</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6.640999144036718e-09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>308.0999999999999</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8295226583781842</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-312.95</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.55166e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.422</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1069776460038319</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6549158647336614</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.248227903487882</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.143663960820237</v>
+      </c>
+      <c r="J17" t="n">
+        <v>36.71814939995072</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.94054213592946</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 18.710x + -32462.683</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-32462.68281610273</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.641468707511774e-07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>312.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000742e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8299037479201862</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-293.53</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.5523e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-78.58</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.451997019423848</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.614050214777665</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.892888247249612</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.001089913411422</v>
+      </c>
+      <c r="J18" t="n">
+        <v>49.2343906052411</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.21101859249019</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 20.527x + -35418.111</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-35418.1106533694</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.361552495473717e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>293.53</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000006193e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8302911440284173</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-287.75</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.5529e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-78.72499999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6044503028590926</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.323328430231166</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.822285498022811</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.222901477932556</v>
+      </c>
+      <c r="J19" t="n">
+        <v>51.28419153259743</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.24260243608222</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 20.763x + -35432.798</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-35432.79796440994</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.443762620555358e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>287.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000007964e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8306843462999087</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-285.6800000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.55332e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-78.873</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5541436089126346</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.636319352510031</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.657314220910577</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.943464659977168</v>
+      </c>
+      <c r="J20" t="n">
+        <v>45.44192702396482</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.20445645515159</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 20.479x + -34469.828</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-34469.82774745971</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.370783292064139e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>285.6800000000001</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8310789482890005</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-289.1899999999998</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.55423e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-79.024</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2149127891263654</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7512461198576351</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.858646667509359</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.616144574427232</v>
+      </c>
+      <c r="J21" t="n">
+        <v>67.55876472164553</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.02346503572944</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 19.232x + -31823.654</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-31823.6538609025</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.725611565560686e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>289.1899999999998</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8314747356605672</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-284.26</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.55471e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.157</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1379931430981599</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.918518666343635</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.9719984875297</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.704651795419183</v>
+      </c>
+      <c r="J22" t="n">
+        <v>69.6065199889767</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.08180461592221</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 19.617x + -32106.825</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-32106.82479283401</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>6.971610374595483e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>284.26</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.831892729535577</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,16 +5572,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1285,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-857.8899999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.51828e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-70.357</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2216122307157797</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4412849162011018</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.528965517241383</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.753553038104981</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.5848113692186</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.06997857984675</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 9.627x + -23988.672</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-23988.67161412517</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.094284275004969e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>857.8899999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000491e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8253028516832255</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-631.5700000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.5463e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-73.116</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1088632306231208</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3916728236613677</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.612239523520143</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.688816192147043</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.73098717059535</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.14728109852139</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 11.779x + -26656.466</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-26656.46554165931</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.777000906103705e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>631.5700000000002</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000023e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.825870838465928</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-530.1599999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.54451e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-74.128</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.41852182547271</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7362285884925156</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.863180192457629</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.348382381368683</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.60692549954295</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.78090769053057</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 13.556x + -30015.886</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-30015.88560368071</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.871236760553751e-14</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>530.1599999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.82590012173334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-488.0500000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.53886e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-74.675</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4119777516375659</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.042900854376783</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.018802145562122</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.488049043319196</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.32855949190218</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.03689023723601</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 14.434x + -31510.326</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-31510.32553480652</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.029584111272498e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>488.0500000000002</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001307e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8259081854434839</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-454.6600000000003</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.54082e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-75.134</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05512496199842216</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.429849780111535</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.239506887239859</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.5505126600295</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.61514969011886</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.95668707320529</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 14.147x + -30286.850</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-30286.84957451514</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.84097581558627e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>454.6600000000003</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.00000000000009e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8259859256404509</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-417.4000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.54129e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-75.452</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3304586722413748</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.017652937610361</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.077607849190506</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.526871145307404</v>
+      </c>
+      <c r="J7" t="n">
+        <v>46.3782470482157</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.34013489689221</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 15.634x + -33262.273</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-33262.27268777401</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.654196279765398e-12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>417.4000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.82614900257313</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-390.25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.54278e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-75.73099999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3880203045684867</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.195115332428903</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.688817204301153</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.073964832671592</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.17519798686017</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.581193104094</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 16.739x + -35276.919</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-35276.91877928114</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>56.41577637011398</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>390.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.215077235745217e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8146841725410688</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-393.5499999999997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.54435e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-75.974</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.06931278845621631</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8534380006500225</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.606057007125864</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.008285753828983</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40.82871013427115</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.36678670884372</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 15.749x + -32521.822</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-32521.82245420742</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.124629398836019e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>393.5499999999997</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8266126128866734</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-376.1499999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.54613e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-76.20099999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3675462602126122</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.087407004741156</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.177479896442853</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.195114678432455</v>
+      </c>
+      <c r="J10" t="n">
+        <v>42.05196782341935</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.46740804464203</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 16.199x + -33030.040</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-33030.03958684207</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.852318402191515e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>376.1499999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000721248e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8268687985707787</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-357.8499999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.54794e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-76.40600000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6013967672703947</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.397486766518532</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.33420676087883</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.761883474509469</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58.59438551615129</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.66742351906323</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 17.173x + -34703.407</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-34703.40742953988</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.292427635820399e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>357.8499999999999</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8271394971160694</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,16 +6238,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1433,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-640.0799999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.55451e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-74.03</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1461101091074448</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9255509875273277</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.76166963436632</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.790784098875858</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.10709059263578</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.26503803742386</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 12.073x + -25360.258</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-25360.25761020574</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.272520016605016e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>640.0799999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8272098373655483</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-497.1400000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.54978e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.67700000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08755284990593351</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6342144965496943</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.162328698122521</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.021326505918887</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.96118726412003</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.85756892798655</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 13.807x + -27619.299</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-27619.29941574144</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.504708599181555e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>497.1400000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8273663063473612</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-429.1699999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.54721e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.22799999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3242874798871323</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8462575621109579</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.722481243399608</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.025226734126893</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.08678122639542</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.37244468159501</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 15.773x + -31237.972</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-31237.97154215303</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.25461203434129e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>429.1699999999998</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8273605829591431</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-415.5899999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.54876e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.506</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09819420241169272</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.916010130570728</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.506116735416825</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.829548226454254</v>
+      </c>
+      <c r="J5" t="n">
+        <v>32.30489660578142</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.36967910136703</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 15.761x + -30741.488</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-30741.488300718</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.467837727914035e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>415.5899999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000058e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8273413122080273</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-398.5099999999998</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.55017e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.723</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1304772911869604</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7558626420622401</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.757614335514852</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.798639819763188</v>
+      </c>
+      <c r="J6" t="n">
+        <v>33.85140945906273</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.46644118551589</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 16.194x + -31255.293</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-31255.29273366674</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.428258509733219e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>398.5099999999998</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8274043718995371</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-388.0299999999997</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.55111e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.899</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2037572059711193</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7677133838948107</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.944534349645895</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.721832615290086</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.95228437943943</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.52047740049771</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 16.446x + -31403.741</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-31403.74141723057</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.139853926920892e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>388.0299999999997</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000011329e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8275555910164117</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-368.4100000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.55234e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.06699999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7001713863672027</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.465220578625757</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.060473649001391</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.913781177572388</v>
+      </c>
+      <c r="J8" t="n">
+        <v>54.51352189543636</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.82391415134171</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 18.021x + -34287.767</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-34287.76684967094</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.194038909073669e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>368.4100000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000012003e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8277479681036791</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-366.96</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.55307e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.205</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5928028324336824</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.202176888437066</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.313450300382262</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.283741254977389</v>
+      </c>
+      <c r="J9" t="n">
+        <v>43.98469708685295</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.7647900908143</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 17.691x + -33225.870</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-33225.87018089015</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.911543712929486e-07</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>366.96</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000221e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8279835716156516</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-371.05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.55378e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.34999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1544710366806198</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5938928252737448</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.445974017913367</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.493430898708846</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33.09154711779961</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.59667715992504</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 16.815x + -31091.603</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-31091.60252052121</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.589425969651113e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>371.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000010251e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8282531796466067</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-367.7599999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.55444e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.48999999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1207446667834743</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7505893949850109</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.411430493443546</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.491364102943404</v>
+      </c>
+      <c r="J11" t="n">
+        <v>33.70999383301645</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.63710266218561</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 17.018x + -31158.698</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-31158.69792909854</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.218747229191968e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>367.7599999999998</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000005637e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8285636792480321</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-361.4200000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.55496e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-77.63500000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2382856874445066</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7845834872993026</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.375496453670586</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.630155984089924</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.52561284823814</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.67237945162864</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 17.199x + -31181.095</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-31181.09533649846</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.495794803160773e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>361.4200000000001</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8288912003939648</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-354.8200000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.55583e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-77.76300000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2161550193640273</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6808942719817035</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.518387307861929</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.620584041759896</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.86415408509932</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.72741549520923</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 17.489x + -31400.854</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-31400.85391835023</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.087838234381142e-07</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>354.8200000000002</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000859348e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8292267556824336</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-342.6299999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.55627e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-77.914</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3519499866584619</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.245911089930424</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.939230368150182</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.07381031396449</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41.26069740994348</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.87501756284391</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 18.317x + -32649.957</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-32649.95671846926</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.23833172258368e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>342.6299999999999</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8295688023830374</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-347</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.55733e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.05800000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.07452943411675268</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5958709236379094</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.463868408600154</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.117434689885117</v>
+      </c>
+      <c r="J15" t="n">
+        <v>32.84097566787658</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.72566485057003</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 17.479x + -30680.447</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-30680.44679676006</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.233578663534895e-07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>347</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000128576e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8299283596411257</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-339.0800000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.55792e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.18300000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2162934815568205</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7801161098374505</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.262194641201849</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.792309374735803</v>
+      </c>
+      <c r="J16" t="n">
+        <v>36.99726855151574</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.86596343878402</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 18.264x + -31811.788</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-31811.78809521202</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.110046833897703e-07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>339.0800000000002</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000433062e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8303118633528034</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-337.6700000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.55865e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.342</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.07838058010472888</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8690599988315624</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.077133002665275</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.415511587012869</v>
+      </c>
+      <c r="J17" t="n">
+        <v>52.95001699589514</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.72961676194363</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 17.501x + -30004.383</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-30004.38342051718</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>9.463125812017704e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>337.6700000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000049399e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8306920563252771</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-319.4000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.55936e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-78.471</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7657535266191636</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9444762159669153</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.737976854215695</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.223350250879815</v>
+      </c>
+      <c r="J18" t="n">
+        <v>44.52741998391706</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.08194290508197</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 19.618x + -33555.578</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-33555.57762910577</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.132741841604442e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>319.4000000000001</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.00000000000546e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8310744570390908</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-317.95</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.55983e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-78.61799999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.05719654924308014</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9614640309811299</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.688993750298643</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.805198497840451</v>
+      </c>
+      <c r="J19" t="n">
+        <v>40.0761260394243</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.01667204533068</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 19.188x + -32377.096</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-32377.09633251138</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.157994264965029e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>317.95</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8314681343215892</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-307.3299999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.56098e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-78.746</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7672995505878822</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.315655812727029</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.914459961870544</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.969941266394154</v>
+      </c>
+      <c r="J20" t="n">
+        <v>47.50383804629146</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.17222440948095</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 20.245x + -33903.544</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-33903.54393270001</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.84339648003393e-07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>307.3299999999999</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8318499840812067</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-310.1599999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.56129e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-78.889</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4211083111009665</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9890083215020519</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.348875997099359</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.540133000461447</v>
+      </c>
+      <c r="J21" t="n">
+        <v>37.48063718076545</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.02268624965933</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 19.227x + -31673.888</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-31673.88839292728</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8.359280786738904e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>310.1599999999999</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.00000000000018e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8322595460561064</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-298.0699999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.56205e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.03100000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.555720480451233</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.097788605435654</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.07194101906383</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.654305533411074</v>
+      </c>
+      <c r="J22" t="n">
+        <v>42.94122329417656</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.15910525370883</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 20.152x + -32912.498</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-32912.49848217268</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.467360730497264e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>298.0699999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000671e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8326683780320826</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,16 +7476,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1581,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-928.0900000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.50818e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-70.142</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1994732221246743</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4240167364016407</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.079463087248373</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.925574425574501</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.20417438251172</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.63503772770461</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 8.965x + -22177.929</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-22177.92908583114</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.182570499047168e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>928.0900000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8235389366040871</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-663.3600000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.55608e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-73.051</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2622679870036993</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.016160416102168</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.788669679446209</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.17922075762824</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.13064877003294</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.08997401163158</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 11.641x + -25873.603</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-25873.60345906585</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.641420491502718e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>663.3600000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8244098618608863</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-558.0100000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.55542e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-74.208</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1143068595357596</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7021589890325559</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.649448064829402</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.659569678833181</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24.40533902646196</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.58355515337779</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 12.948x + -27929.120</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-27929.11952677896</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.935819490544788e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>558.0100000000002</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000040485e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8246569878850278</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-509.7000000000003</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.55174e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-74.773</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2233731826437387</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8129367396499096</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.532466627612913</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.745975177693677</v>
+      </c>
+      <c r="J5" t="n">
+        <v>27.60463979360149</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.82559054158641</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 13.701x + -29087.006</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-29087.00570661683</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.861860459995864e-11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>509.7000000000003</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8248754942505564</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-459.8699999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.5523e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-75.238</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4380111507411761</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.946503896128835</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.92824690192442</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.485927688346285</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38.92421143006025</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.14632727722568</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 14.845x + -31185.382</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-31185.3822423091</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.447256478326925e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>459.8699999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000004894e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8250863204450599</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-431.5800000000002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.5533e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-75.584</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5291467156942083</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.214637296781612</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.109369487088906</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.552529062637802</v>
+      </c>
+      <c r="J7" t="n">
+        <v>42.98317447967308</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.27191915962126</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 15.347x + -31797.228</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-31797.22813634483</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.033027993547383e-07</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>431.5800000000002</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.00000000003441e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8253742726708515</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-398.52</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.55459e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-75.905</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.390505359877544</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.075877192982474</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.164421768707504</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.328760226557464</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.14922839133954</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.52124993113947</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 16.450x + -33745.744</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-33745.74401886032</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.920523641782357e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>398.52</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000001441e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8256439566405775</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-403.7499999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.55649e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-76.117</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5474835973437139</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9829253819042763</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.53047991584094</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.143740725676562</v>
+      </c>
+      <c r="J9" t="n">
+        <v>38.07220227551741</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.33751659904978</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 15.623x + -31401.606</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-31401.60645278211</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.164242542498674e-07</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>403.7499999999998</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000035413e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8258872042344967</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-388.8300000000002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.55979e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-76.375</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2830498359356353</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8907599945364864</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.430817859905218</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.439799492199469</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33.86999757282</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.29157954390369</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 15.429x + -30527.163</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-30527.16340045061</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.618416090041746e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>388.8300000000002</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000444e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8261096052838799</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-386.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.56226e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-76.55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.06429706158882542</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5985893896577428</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.326524792841036</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.461093294971591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>30.0707324088152</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.24885512448218</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 15.252x + -29729.496</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-29729.4956525476</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.488565273240728e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>386.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000007784e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8263403127084581</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,16 +8142,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1729,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-620.1099999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.57138e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-74.10599999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4823709767576</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.40656131877337</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.294128228737363</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.29497651818394</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.24095623139149</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 12.012x + -25001.691</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-25001.69081116027</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.614824750024697e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>620.1099999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000002177e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8253812966683933</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-458.4399999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.56059e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.765</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3522347977594464</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.066168652087228</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.999465210836017</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.939323133232163</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.8984182178854</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.16521386443776</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 14.919x + -29924.882</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29924.88177488731</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.034253212907334e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>458.4399999999998</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000281e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8255742954399388</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-441.5000000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.55947e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.163</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2036626582116553</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3621534504698898</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.352183001761373</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.326520435890985</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.7646908631733</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.1224753536069</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 14.754x + -28957.730</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-28957.73037579245</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.288773157832972e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>441.5000000000002</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000146725e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8255850427780846</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-410.3099999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.56151e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.396</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3079486906682764</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.134881203967945</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.133469796988982</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.025067970069523</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37.37423936498105</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.46458198322632</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 16.186x + -31609.437</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-31609.43672057775</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.146716851668575e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>410.3099999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000152916e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.825630742229314</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-404.9699999999998</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.56145e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.548</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8952941362593415</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.046172783536006</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.730912800668669</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.179552300981663</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.74461990416287</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.50419148557604</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 16.370x + -31639.705</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-31639.7050943957</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.128634375804588e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>404.9699999999998</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000029e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8257774838069417</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-396.1199999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.56295e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.739</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3286553828928107</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.891791050443983</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.969828173078912</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.632240784608492</v>
+      </c>
+      <c r="J7" t="n">
+        <v>33.80572169469745</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.47439655625823</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 16.231x + -30998.940</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-30998.9395754244</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.01343190634668e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>396.1199999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000006521e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8258596233710385</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-408.4200000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.56656e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-76.812</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1851896961456174</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4668496937274058</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.18122305904035</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.879880773385925</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.09548274502991</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.30722350466797</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 15.494x + -29165.055</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-29165.0548599034</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.270165455564024e-07</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>408.4200000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000014658e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8259844762401788</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-385.4199999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.56748e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.02200000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0524435247607746</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7946072852291249</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.668789267608288</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.434991236314748</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.46587944301125</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.49018023772855</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 16.304x + -30472.432</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-30472.43202429854</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.065072671323593e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>385.4199999999998</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000355e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8261797601106761</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-373.8799999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.56694e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.178</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3019451430327393</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.205121021963245</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.571007605126333</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.940788271314906</v>
+      </c>
+      <c r="J10" t="n">
+        <v>36.39970424869411</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.66014286444735</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 17.136x + -31800.165</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-31800.16477470212</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.110470417100931e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>373.8799999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000075e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8263988533012309</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-369.9100000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.56884e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.30200000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.252350930539006</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9873278202913608</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.683071971839047</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.807774279191396</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36.99355517790342</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.71182300552242</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 17.406x + -31994.031</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-31994.03138025086</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.091815773086266e-07</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>369.9100000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000142e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.826646192193352</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-372.7500000000002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.56939e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-77.459</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1237183724847317</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4227633001373961</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.172209744714361</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.092448736070843</v>
+      </c>
+      <c r="J12" t="n">
+        <v>30.22918929331317</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.53389226853824</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 16.510x + -29867.562</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-29867.56232307294</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.32397366149695e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>372.7500000000002</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000003696e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8269100335493037</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-350.9500000000003</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.57091e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-77.634</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1436135170764348</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4576877683566348</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.457895047829971</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.695440702515718</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.51073339502064</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.72309669613963</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 17.466x + -31383.629</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-31383.62879914522</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.743200290483485e-07</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>350.9500000000003</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000847e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8272045140411995</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-342.5800000000002</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.5723e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-77.798</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.124310309935976</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6076091671486561</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.23562149662447</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.404716404455512</v>
+      </c>
+      <c r="J14" t="n">
+        <v>35.90034311547598</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.77244950582413</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 17.733x + -31538.116</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-31538.11576055409</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.058927311162519e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>342.5800000000002</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000002522e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8275311280678673</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-327.3299999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.57241e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.008</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3172758958305833</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7744531895494953</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.316187805856388</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.635200362016866</v>
+      </c>
+      <c r="J15" t="n">
+        <v>37.89010605348048</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.8254226228315</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 18.030x + -31728.962</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-31728.96189146264</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.367241277796674e-07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>327.3299999999999</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000456e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8278656786794472</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-337.0600000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.57271e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.072</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.189432656286483</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8023910362825287</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.749955928354499</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.695098919485724</v>
+      </c>
+      <c r="J16" t="n">
+        <v>37.27325350820988</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.8837951853873</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 18.368x + -32006.938</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-32006.93782961402</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.556427182879011e-09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>337.0600000000002</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000095e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.82821351609438</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-334.8299999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.57264e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.211</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1313457412788438</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.440704566292406</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.510458647452139</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.323166230389238</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33.76551820004038</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.83410191399658</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 18.079x + -31086.690</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-31086.68979129966</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.153163672748359e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>334.8299999999999</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000215e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8285616354157982</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-320.0599999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.57417e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-78.36499999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.353459504858812</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.132666423753909</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.694077240586154</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.602734985932872</v>
+      </c>
+      <c r="J18" t="n">
+        <v>39.2669945325752</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.98419580198654</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 18.981x + -32379.190</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-32379.18983177853</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.619802128066902e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>320.0599999999999</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8289442752101198</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-313.4200000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.57495e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-78.496</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5501543546422062</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.251700665235457</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.957689468163936</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.205206508987711</v>
+      </c>
+      <c r="J19" t="n">
+        <v>45.97647248959593</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.12366954272167</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 19.903x + -33667.700</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-33667.70040112365</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.89175714841225e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>313.4200000000001</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8293184717762465</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-300.1600000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.57697e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-78.697</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3493945162204768</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8543314544212635</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.710390318122641</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.807839724798174</v>
+      </c>
+      <c r="J20" t="n">
+        <v>42.42880582418234</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.08398938991256</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 19.632x + -32750.634</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-32750.63359749494</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7.722922622809486e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>300.1600000000001</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8297066466462508</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-295.3899999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.57805e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-78.84099999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4512036954263052</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9883676964958398</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.788345569724325</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.737193726092971</v>
+      </c>
+      <c r="J21" t="n">
+        <v>43.40387777232429</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.14094224806178</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 20.023x + -33032.993</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-33032.99326825517</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4.358347694258068e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>295.3899999999999</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000023054e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8301054528868912</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-299.6400000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.57798e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-78.97799999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1522414386676776</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8547876527996116</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.854582671808476</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.684667311948293</v>
+      </c>
+      <c r="J22" t="n">
+        <v>62.53527098464035</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.00352108731381</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 19.104x + -30999.440</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-30999.43984475506</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>4.557780522910367e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>299.6400000000001</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8304928078988155</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,16 +9380,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1877,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-862.5200000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.55519e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-72.762</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2984587129839105</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5503235085758734</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.295407063996701</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.201367887845575</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.06829981423687</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.00238532110781</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 9.518x + -19687.671</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-19687.67058978109</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.227213321259076e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>862.5200000000002</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8258135490724141</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-563.0599999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.57788e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.021</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5473258795153151</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.915563526913495</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.668900354401958</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.655455202596611</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.74862233669194</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.7863302037798</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 13.573x + -24905.664</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-24905.66372225419</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.171980325841046e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>563.0599999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000602e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8265843011122188</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-469.71</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.5718e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-77.06399999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3428758584215009</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7752308095820803</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.551726354173395</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.548997375451561</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25.35120121337593</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.21063658149419</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 15.098x + -26779.132</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-26779.13229182119</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.249067248825103e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>469.71</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8267106954024259</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-427.3399999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.56788e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.556</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7096036637415876</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9578641893540959</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.499849518365299</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.141400817615567</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.93231034931165</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.327269592563</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 15.579x + -27094.245</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-27094.24542119744</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.46915560628849e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>427.3399999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000118e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8267997364134732</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-421.24</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.56482e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.854</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0779883780275317</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5769559201787673</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.6304451067178</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.882517482755546</v>
+      </c>
+      <c r="J6" t="n">
+        <v>33.45898954220266</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.26507633017883</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 15.319x + -26104.724</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-26104.72380503079</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.462544229633462e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>421.24</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000038e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8270244849704278</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-393.6000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.56741e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.133</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2425594263848884</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.177764464245338</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.864105977116657</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.237019120512175</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.6141986595615</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.44243777535029</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 16.085x + -27035.563</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-27035.56261448654</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.34133417951443e-07</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>393.6000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000583e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8273420005662727</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-390.27</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.56929e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.286</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.438545367318975</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9688445409614496</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.427470375024197</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.783133730882984</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.97030910785634</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.628056008865</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 16.972x + -28160.046</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-28160.04567139671</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.147090937601186e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8277202436395137</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-371.4400000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.57095e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.539</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4510895034805998</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7349982571398452</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.49288446168808</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.340661062500574</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.56489238584371</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.69976234518663</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 17.342x + -28316.699</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-28316.6990865787</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.221931878622256e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>371.4400000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.00000000000014e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8281014582459626</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-362.1300000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.57463e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.715</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5625408907901498</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.01682833919423</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.357429693205487</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.174363814642796</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.41782952084932</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.77015134218537</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 17.721x + -28499.631</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-28499.6313728429</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.161654329277473e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>362.1300000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8284659277598504</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-358.3999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.57704e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.87</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3773723588284709</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.92036495922839</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.588233970254703</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.44614223993069</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32.16349160839334</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.81805336551434</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 17.988x + -28516.759</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-28516.75874047502</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.333681706639339e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>358.3999999999999</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8288280427575897</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>85.45292921465098</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.574x + -28201.092</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.574126166089</v>
       </c>
       <c r="X2" t="n">
         <v>-28201.09178890567</v>
@@ -600,7 +598,7 @@
         <v>2.056416622690032e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>623.0099999999998</v>
+        <v>2581.254761896013</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000016756e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>86.097124853336</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.658x + -31360.187</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.65768983811093</v>
       </c>
       <c r="X3" t="n">
         <v>-31360.18726880851</v>
@@ -652,7 +648,7 @@
         <v>9.112707972135273e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>504.3099999999999</v>
+        <v>2476.106213132825</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>86.14648789362288</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.846x + -31127.174</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.84603153122611</v>
       </c>
       <c r="X4" t="n">
         <v>-31127.173971162</v>
@@ -704,7 +698,7 @@
         <v>1.815855118874455e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>469.9100000000003</v>
+        <v>2439.113361443799</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>86.59878191968943</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.826x + -35125.198</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.82587261235322</v>
       </c>
       <c r="X5" t="n">
         <v>-35125.19756241179</v>
@@ -756,7 +748,7 @@
         <v>2.63302351941651e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>419.7399999999998</v>
+        <v>2409.721247893156</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>86.71561516356934</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.426x + -35969.188</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.42579244517613</v>
       </c>
       <c r="X6" t="n">
         <v>-35969.18841330808</v>
@@ -808,7 +798,7 @@
         <v>6.488599732128164e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>399.7500000000002</v>
+        <v>2379.388754172694</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001406e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>86.46749422115867</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.199x + -32754.611</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.19902900569469</v>
       </c>
       <c r="X7" t="n">
         <v>-32754.61125789627</v>
@@ -860,7 +848,7 @@
         <v>8.765633490352265e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>405.3399999999999</v>
+        <v>2348.738601048445</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000069956e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>86.69009664940322</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.291x + -34622.080</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.29114810385839</v>
       </c>
       <c r="X8" t="n">
         <v>-34622.08000848163</v>
@@ -912,7 +898,7 @@
         <v>5.956228576195496e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>385.0799999999999</v>
+        <v>2315.924558131071</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000019195e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>86.87893981558044</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.340x + -36377.157</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.33963268226879</v>
       </c>
       <c r="X9" t="n">
         <v>-36377.15682085705</v>
@@ -964,7 +948,7 @@
         <v>8.814563337053614e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>367.98</v>
+        <v>2285.518688244928</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000029614e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>86.94331169274881</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.727x + -36705.949</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.72661065638534</v>
       </c>
       <c r="X10" t="n">
         <v>-36705.94919155094</v>
@@ -1016,7 +998,7 @@
         <v>1.23578224501478e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>358.04</v>
+        <v>2256.066654033975</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000441e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>86.9312949383677</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.653x + -36054.009</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.65313944637202</v>
       </c>
       <c r="X11" t="n">
         <v>-36054.00851363573</v>
@@ -1068,7 +1048,7 @@
         <v>4.74785093408461e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>357.1300000000001</v>
+        <v>2228.394763180187</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000217e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>85.89058114120699</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.919x + -28991.162</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.91863455735371</v>
       </c>
       <c r="X2" t="n">
         <v>-28991.16153508377</v>
@@ -1266,7 +1244,7 @@
         <v>1.510135070532941e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>502.9199999999998</v>
+        <v>2395.134252965344</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000001778e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>86.31767280895311</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.538x + -30954.554</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.53823673049421</v>
       </c>
       <c r="X3" t="n">
         <v>-30954.55371271355</v>
@@ -1318,7 +1294,7 @@
         <v>1.79831657726653e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>454.5299999999997</v>
+        <v>2292.798956728872</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000024504e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>86.4262846092787</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.012x + -31391.212</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.01175604184736</v>
       </c>
       <c r="X4" t="n">
         <v>-31391.21171684274</v>
@@ -1370,7 +1344,7 @@
         <v>2.991055649108947e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>439.6499999999999</v>
+        <v>2256.385991460089</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000051e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>86.39875074378122</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.889x + -30736.738</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.88901656105269</v>
       </c>
       <c r="X5" t="n">
         <v>-30736.7377805057</v>
@@ -1422,7 +1394,7 @@
         <v>1.850830035747453e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>430.99</v>
+        <v>2229.873538728859</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000080165e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>86.35648859664379</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.704x + -29952.366</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.70422609131919</v>
       </c>
       <c r="X6" t="n">
         <v>-29952.36625244576</v>
@@ -1474,7 +1444,7 @@
         <v>9.844789500519175e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>427.6199999999999</v>
+        <v>2202.272950076202</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000004047e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>86.4199536652922</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.983x + -30162.526</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.98336725996145</v>
       </c>
       <c r="X7" t="n">
         <v>-30162.5259755867</v>
@@ -1526,7 +1494,7 @@
         <v>1.52258029742102e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>420.1199999999999</v>
+        <v>2175.928952545116</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000002e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>86.49432150808033</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.323x + -30478.487</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.3233059569961</v>
       </c>
       <c r="X8" t="n">
         <v>-30478.48684392136</v>
@@ -1578,7 +1544,7 @@
         <v>5.485356779899677e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>411.7600000000002</v>
+        <v>2150.672623079922</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000008346e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>86.43294306281678</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.042x + -29548.280</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.04172200347248</v>
       </c>
       <c r="X9" t="n">
         <v>-29548.28009746718</v>
@@ -1630,7 +1594,7 @@
         <v>2.025157866703415e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>413.1200000000001</v>
+        <v>2126.060245595298</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>86.69212434102343</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.302x + -31727.570</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.30177099962916</v>
       </c>
       <c r="X10" t="n">
         <v>-31727.57024208668</v>
@@ -1682,7 +1644,7 @@
         <v>4.363936699890571e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>398.1199999999999</v>
+        <v>2102.50280066501</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000002e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>86.56174560042169</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 16.644x + -30061.464</t>
-        </is>
+      <c r="W11" t="n">
+        <v>16.64419821914188</v>
       </c>
       <c r="X11" t="n">
         <v>-30061.4637081375</v>
@@ -1734,7 +1694,7 @@
         <v>2.247260777176046e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>399.3900000000001</v>
+        <v>2079.622519861135</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000136e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>86.81621396371668</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 17.978x + -32328.598</t>
-        </is>
+      <c r="W12" t="n">
+        <v>17.97758862844818</v>
       </c>
       <c r="X12" t="n">
         <v>-32328.5981546775</v>
@@ -1786,7 +1744,7 @@
         <v>1.956810348397113e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>385.4700000000003</v>
+        <v>2057.309668834576</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000007325e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>86.56116836155518</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 16.641x + -29390.551</t>
-        </is>
+      <c r="W13" t="n">
+        <v>16.64139762140234</v>
       </c>
       <c r="X13" t="n">
         <v>-29390.55095881574</v>
@@ -1838,7 +1794,7 @@
         <v>9.863094206737142e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>393.46</v>
+        <v>2035.023675134674</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000015e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>86.70606722612064</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 17.375x + -30458.102</t>
-        </is>
+      <c r="W14" t="n">
+        <v>17.37517029881817</v>
       </c>
       <c r="X14" t="n">
         <v>-30458.10196291071</v>
@@ -1890,7 +1844,7 @@
         <v>5.533076738296481e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>381.6299999999999</v>
+        <v>2012.9000484975</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000002e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>86.75790308421584</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 17.654x + -30643.927</t>
-        </is>
+      <c r="W15" t="n">
+        <v>17.65357924324432</v>
       </c>
       <c r="X15" t="n">
         <v>-30643.92707375035</v>
@@ -1942,7 +1894,7 @@
         <v>1.423201680666198e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>376.5700000000002</v>
+        <v>1991.069193723529</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000000358e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>86.82729542649483</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 18.041x + -31012.742</t>
-        </is>
+      <c r="W16" t="n">
+        <v>18.04050906164337</v>
       </c>
       <c r="X16" t="n">
         <v>-31012.74184024507</v>
@@ -1994,7 +1944,7 @@
         <v>5.717588606704249e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>368.3100000000002</v>
+        <v>1969.449034051546</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>86.68360062180015</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 17.257x + -29230.517</t>
-        </is>
+      <c r="W17" t="n">
+        <v>17.25720336505253</v>
       </c>
       <c r="X17" t="n">
         <v>-29230.51674900182</v>
@@ -2046,7 +1994,7 @@
         <v>2.576323773700991e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>375.6699999999998</v>
+        <v>1948.413987382764</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000001e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>86.9144181668314</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 18.551x + -31257.842</t>
-        </is>
+      <c r="W18" t="n">
+        <v>18.55091909327782</v>
       </c>
       <c r="X18" t="n">
         <v>-31257.84190078008</v>
@@ -2098,7 +2044,7 @@
         <v>3.013589953556943e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>359.3899999999999</v>
+        <v>1927.069102713171</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000001457e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>86.87903498585916</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 18.340x + -30525.324</t>
-        </is>
+      <c r="W19" t="n">
+        <v>18.34019303632208</v>
       </c>
       <c r="X19" t="n">
         <v>-30525.32398314323</v>
@@ -2150,7 +2094,7 @@
         <v>6.953048004923163e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>357.77</v>
+        <v>1905.719562304891</v>
       </c>
       <c r="AA19" t="n">
         <v>1.0000000000009e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>87.02362293112694</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 19.233x + -31775.450</t>
-        </is>
+      <c r="W20" t="n">
+        <v>19.23285604809107</v>
       </c>
       <c r="X20" t="n">
         <v>-31775.45002257308</v>
@@ -2202,7 +2144,7 @@
         <v>1.841031908188941e-11</v>
       </c>
       <c r="Z20" t="n">
-        <v>345.74</v>
+        <v>1884.579597572348</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>86.88913060003294</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 18.400x + -29922.067</t>
-        </is>
+      <c r="W21" t="n">
+        <v>18.39982963730563</v>
       </c>
       <c r="X21" t="n">
         <v>-29922.06724334456</v>
@@ -2254,7 +2194,7 @@
         <v>2.242137843961746e-07</v>
       </c>
       <c r="Z21" t="n">
-        <v>349.1199999999999</v>
+        <v>1863.316605824914</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000021e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>87.03347136547411</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 19.297x + -31136.932</t>
-        </is>
+      <c r="W22" t="n">
+        <v>19.29682109598957</v>
       </c>
       <c r="X22" t="n">
         <v>-31136.93196388157</v>
@@ -2306,7 +2244,7 @@
         <v>3.494309733862835e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>338.77</v>
+        <v>1842.231028052715</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000012e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>85.89071615359568</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.919x + -30166.940</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.91909343246344</v>
       </c>
       <c r="X2" t="n">
         <v>-30166.94007316015</v>
@@ -2504,7 +2440,7 @@
         <v>2.05281980478126e-13</v>
       </c>
       <c r="Z2" t="n">
-        <v>525.4000000000001</v>
+        <v>2490.927275342699</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000011e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>86.1608278406142</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.902x + -30519.508</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.90165119489015</v>
       </c>
       <c r="X3" t="n">
         <v>-30519.50844804617</v>
@@ -2556,7 +2490,7 @@
         <v>8.660224636532493e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>448.2999999999997</v>
+        <v>2379.443356561666</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000403e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>86.57862696020709</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.727x + -33959.316</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.72651918017262</v>
       </c>
       <c r="X4" t="n">
         <v>-33959.31579090837</v>
@@ -2608,7 +2540,7 @@
         <v>5.182037553156567e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>404.02</v>
+        <v>2345.279277117374</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000266e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>86.81806056477348</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.988x + -36290.286</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.98804321143036</v>
       </c>
       <c r="X5" t="n">
         <v>-36290.28550049723</v>
@@ -2660,7 +2590,7 @@
         <v>4.514443058564051e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>375.6399999999999</v>
+        <v>2320.684009820747</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000171e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>86.53586969744448</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.520x + -32714.961</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.51957148521605</v>
       </c>
       <c r="X6" t="n">
         <v>-32714.96106571314</v>
@@ -2712,7 +2640,7 @@
         <v>9.519367777101565e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>382.3599999999999</v>
+        <v>2296.347114203406</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000005195e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>86.94878174546064</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.760x + -37110.335</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.76024640031629</v>
       </c>
       <c r="X7" t="n">
         <v>-37110.33527682364</v>
@@ -2764,7 +2690,7 @@
         <v>5.215015646185163e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>354.0700000000002</v>
+        <v>2271.132823863362</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000486655e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>86.87770306304131</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.332x + -35776.915</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.33235389766648</v>
       </c>
       <c r="X8" t="n">
         <v>-35776.91518777932</v>
@@ -2816,7 +2740,7 @@
         <v>2.521091378039949e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>356.72</v>
+        <v>2246.079576360868</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000008e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>86.84706650513631</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.154x + -35000.370</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.15386642125246</v>
       </c>
       <c r="X9" t="n">
         <v>-35000.37010581527</v>
@@ -2868,7 +2790,7 @@
         <v>1.685100697067799e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>353.77</v>
+        <v>2222.159574987513</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>86.90282034536423</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.481x + -35287.150</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.48131784129867</v>
       </c>
       <c r="X10" t="n">
         <v>-35287.14975881372</v>
@@ -2920,7 +2840,7 @@
         <v>1.090302632229841e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>347.2399999999998</v>
+        <v>2199.120134081117</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000109261e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>86.86137687425156</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.237x + -34407.431</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.23680487197554</v>
       </c>
       <c r="X11" t="n">
         <v>-34407.43105320478</v>
@@ -2972,7 +2890,7 @@
         <v>8.937229951758916e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>344.2400000000002</v>
+        <v>2176.092588861285</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000429e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>86.91743783836387</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 18.569x + -34705.311</t>
-        </is>
+      <c r="W12" t="n">
+        <v>18.56912670160928</v>
       </c>
       <c r="X12" t="n">
         <v>-34705.3107485142</v>
@@ -3024,7 +2940,7 @@
         <v>3.499255348249995e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>335.3699999999999</v>
+        <v>2153.305815194798</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>86.95814273549837</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 18.818x + -34809.402</t>
-        </is>
+      <c r="W13" t="n">
+        <v>18.81808817874004</v>
       </c>
       <c r="X13" t="n">
         <v>-34809.40230175739</v>
@@ -3076,7 +2990,7 @@
         <v>2.087622909754997e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>332.99</v>
+        <v>2129.940765735583</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000122232e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>87.00304408435548</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.101x + -34976.813</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.1005533340824</v>
       </c>
       <c r="X14" t="n">
         <v>-34976.81278903653</v>
@@ -3128,7 +3040,7 @@
         <v>1.525177688158116e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>326.0100000000002</v>
+        <v>2106.236350545985</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000006e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>87.04276874533961</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 19.358x + -35072.032</t>
-        </is>
+      <c r="W15" t="n">
+        <v>19.3575976773984</v>
       </c>
       <c r="X15" t="n">
         <v>-35072.03224711869</v>
@@ -3180,7 +3090,7 @@
         <v>1.664232797329004e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>324.01</v>
+        <v>2082.413684566668</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000005796e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>87.09344548909095</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.696x + -35328.713</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.69569882429078</v>
       </c>
       <c r="X16" t="n">
         <v>-35328.71272590429</v>
@@ -3232,7 +3140,7 @@
         <v>1.89096825964452e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>317.4999999999998</v>
+        <v>2058.941304661459</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>87.23894294840383</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 20.735x + -36897.207</t>
-        </is>
+      <c r="W17" t="n">
+        <v>20.73532716721984</v>
       </c>
       <c r="X17" t="n">
         <v>-36897.20660805568</v>
@@ -3284,7 +3190,7 @@
         <v>1.978464390456257e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>306.2199999999998</v>
+        <v>2035.344534759897</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000046e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>87.17351607895897</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 20.255x + -35564.236</t>
-        </is>
+      <c r="W18" t="n">
+        <v>20.25459736760367</v>
       </c>
       <c r="X18" t="n">
         <v>-35564.23592944665</v>
@@ -3336,7 +3240,7 @@
         <v>6.284714122398459e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>308.04</v>
+        <v>2012.017147002048</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000346e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>87.22612169028926</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 20.639x + -35864.193</t>
-        </is>
+      <c r="W19" t="n">
+        <v>20.63933666687459</v>
       </c>
       <c r="X19" t="n">
         <v>-35864.19313921292</v>
@@ -3388,7 +3290,7 @@
         <v>2.354485503458207e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>298.8399999999999</v>
+        <v>1988.552696207287</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000003194e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>87.14887220293056</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.079x + -34407.531</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.0792400701859</v>
       </c>
       <c r="X20" t="n">
         <v>-34407.53095909335</v>
@@ -3440,7 +3340,7 @@
         <v>4.139287850934626e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>299.3900000000001</v>
+        <v>1964.995383232124</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000001523e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>87.1156343712935</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 19.847x + -33569.697</t>
-        </is>
+      <c r="W21" t="n">
+        <v>19.84747339109529</v>
       </c>
       <c r="X21" t="n">
         <v>-33569.69663751725</v>
@@ -3492,7 +3390,7 @@
         <v>2.362127781428673e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>300.7099999999998</v>
+        <v>1941.746070284501</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000026e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>87.35126644074171</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 21.616x + -36339.819</t>
-        </is>
+      <c r="W22" t="n">
+        <v>21.6159746562087</v>
       </c>
       <c r="X22" t="n">
         <v>-36339.8189413394</v>
@@ -3544,7 +3440,7 @@
         <v>1.372464324196523e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>285.3499999999999</v>
+        <v>1918.842308706892</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.19046246294992</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.829x + -24997.431</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.82854326502509</v>
       </c>
       <c r="X2" t="n">
         <v>-24997.43137088413</v>
@@ -3742,7 +3636,7 @@
         <v>1.303982630054166e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>840.25</v>
+        <v>2909.818712444293</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000181e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>85.28715285424678</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.130x + -27565.470</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.12992942070545</v>
       </c>
       <c r="X3" t="n">
         <v>-27565.46982795976</v>
@@ -3794,7 +3686,7 @@
         <v>1.027264422883348e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>620.2400000000002</v>
+        <v>2638.38498157474</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000002e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>85.80846979182415</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.645x + -30145.256</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.64502420854157</v>
       </c>
       <c r="X4" t="n">
         <v>-30145.25553207761</v>
@@ -3846,7 +3736,7 @@
         <v>3.490016179154979e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>522.1799999999998</v>
+        <v>2564.013292644723</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>86.05945880664815</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.517x + -31587.872</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.51714644016701</v>
       </c>
       <c r="X5" t="n">
         <v>-31587.87185633738</v>
@@ -3898,7 +3786,7 @@
         <v>1.144489126443623e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>475.6400000000003</v>
+        <v>2521.660895132992</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000022e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.11307700200918</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.718x + -31474.984</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.71803192158183</v>
       </c>
       <c r="X6" t="n">
         <v>-31474.98355327969</v>
@@ -3950,7 +3836,7 @@
         <v>6.548216533372171e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>440.3799999999997</v>
+        <v>2483.543930865728</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003255e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.35285388353074</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.689x + -33203.451</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.68853310686682</v>
       </c>
       <c r="X7" t="n">
         <v>-33203.45057500096</v>
@@ -4002,7 +3886,7 @@
         <v>4.732947559555632e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>409.71</v>
+        <v>2446.986355741294</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000745e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.33888110495191</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 15.628x + -32524.185</t>
-        </is>
+      <c r="W8" t="n">
+        <v>15.62849495479089</v>
       </c>
       <c r="X8" t="n">
         <v>-32524.18541169792</v>
@@ -4054,7 +3936,7 @@
         <v>55.32024370684625</v>
       </c>
       <c r="Z8" t="n">
-        <v>396.3199999999997</v>
+        <v>2423.477231855946</v>
       </c>
       <c r="AA8" t="n">
         <v>1.21800867779173e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.54551968335916</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.566x + -34119.538</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.56583090095285</v>
       </c>
       <c r="X9" t="n">
         <v>-34119.53825081394</v>
@@ -4106,7 +3986,7 @@
         <v>6.279973392616429e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>376.7100000000003</v>
+        <v>2374.879365483864</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000267e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>86.63348124091696</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.000x + -34552.016</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.99970595654379</v>
       </c>
       <c r="X10" t="n">
         <v>-34552.01601601497</v>
@@ -4158,7 +4036,7 @@
         <v>4.131601412929603e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>362.6399999999999</v>
+        <v>2340.505857145611</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000002425e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>86.44959084298355</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 16.117x + -32136.093</t>
-        </is>
+      <c r="W11" t="n">
+        <v>16.11713549845106</v>
       </c>
       <c r="X11" t="n">
         <v>-32136.09250418279</v>
@@ -4210,7 +4086,7 @@
         <v>3.417712274107404e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>366.0299999999997</v>
+        <v>2307.848882026657</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000012e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.4708409920854</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.624x + -27105.564</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.62406292981802</v>
       </c>
       <c r="X2" t="n">
         <v>-27105.56415712392</v>
@@ -4408,7 +4282,7 @@
         <v>1.447897582249577e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>610.2400000000002</v>
+        <v>2459.372221786146</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000419e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>86.05000010707244</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.482x + -29385.844</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.48227357692545</v>
       </c>
       <c r="X3" t="n">
         <v>-29385.84419624559</v>
@@ -4460,7 +4332,7 @@
         <v>1.205559113675395e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>472.5199999999998</v>
+        <v>2348.770161627056</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000014e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>86.42140310113929</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.990x + -31996.782</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.98985786581498</v>
       </c>
       <c r="X4" t="n">
         <v>-31996.78182317718</v>
@@ -4512,7 +4382,7 @@
         <v>5.485706429267026e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>412.55</v>
+        <v>2308.411583632859</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000015418e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>86.56204422563872</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.646x + -32934.342</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.64564743187884</v>
       </c>
       <c r="X5" t="n">
         <v>-32934.34229431956</v>
@@ -4564,7 +4432,7 @@
         <v>2.632115304134711e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>387.5799999999999</v>
+        <v>2279.438270186269</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000057924e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>86.51364633659323</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.414x + -32047.954</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.41401149195075</v>
       </c>
       <c r="X6" t="n">
         <v>-32047.95423730018</v>
@@ -4616,7 +4482,7 @@
         <v>9.985211892199435e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>383.3</v>
+        <v>2254.426849274328</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000274e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>86.59770310977548</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.821x + -32526.562</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.82052486067492</v>
       </c>
       <c r="X7" t="n">
         <v>-32526.56197133243</v>
@@ -4668,7 +4532,7 @@
         <v>6.891140733194403e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>370.26</v>
+        <v>2229.998570064815</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000022e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>86.52518866776535</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.469x + -31434.637</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.46866874225862</v>
       </c>
       <c r="X8" t="n">
         <v>-31434.63661951823</v>
@@ -4720,7 +4582,7 @@
         <v>1.73059805577069e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>371.8799999999999</v>
+        <v>2206.114757424268</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000143e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>86.60289325858444</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.846x + -31850.460</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.84628396645909</v>
       </c>
       <c r="X9" t="n">
         <v>-31850.46018202034</v>
@@ -4772,7 +4632,7 @@
         <v>1.111847671222076e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>362.5799999999999</v>
+        <v>2182.328950149695</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000265015e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>86.89942277969941</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.461x + -34772.737</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.46102676625255</v>
       </c>
       <c r="X10" t="n">
         <v>-34772.73658822454</v>
@@ -4824,7 +4682,7 @@
         <v>1.644906582154696e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>342.3600000000001</v>
+        <v>2158.899897121277</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000005e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>86.73429990381979</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.526x + -32495.997</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.52571243868437</v>
       </c>
       <c r="X11" t="n">
         <v>-32495.99702496241</v>
@@ -4876,7 +4732,7 @@
         <v>2.996092547629272e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>348.3599999999999</v>
+        <v>2134.927758173419</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>86.67873190410205</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 17.232x + -31530.902</t>
-        </is>
+      <c r="W12" t="n">
+        <v>17.23184902886677</v>
       </c>
       <c r="X12" t="n">
         <v>-31530.90224453312</v>
@@ -4928,7 +4782,7 @@
         <v>1.114934500518794e-07</v>
       </c>
       <c r="Z12" t="n">
-        <v>340.8999999999999</v>
+        <v>2111.004690412993</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000032092e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>86.71155560266718</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 17.404x + -31509.526</t>
-        </is>
+      <c r="W13" t="n">
+        <v>17.40423320332699</v>
       </c>
       <c r="X13" t="n">
         <v>-31509.52581457571</v>
@@ -4980,7 +4832,7 @@
         <v>2.32968214810881e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>339.7200000000003</v>
+        <v>2087.096422352067</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000099046e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>86.99640089905161</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.058x + -34341.293</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.05823060454423</v>
       </c>
       <c r="X14" t="n">
         <v>-34341.29255935515</v>
@@ -5032,7 +4882,7 @@
         <v>1.504153050287589e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>320.9699999999998</v>
+        <v>2063.006822522449</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000566e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>87.05216231562386</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 19.419x + -34612.018</t>
-        </is>
+      <c r="W15" t="n">
+        <v>19.41939204928792</v>
       </c>
       <c r="X15" t="n">
         <v>-34612.01789997334</v>
@@ -5084,7 +4932,7 @@
         <v>2.083282705389819e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>315.3</v>
+        <v>2038.575381786189</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000035747e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>87.11243818638889</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.825x + -34961.106</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.82546743512302</v>
       </c>
       <c r="X16" t="n">
         <v>-34961.10598432533</v>
@@ -5136,7 +4982,7 @@
         <v>6.640999144036718e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>308.0999999999999</v>
+        <v>2014.978127763932</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000001e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>86.94054213592946</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 18.710x + -32462.683</t>
-        </is>
+      <c r="W17" t="n">
+        <v>18.70962627575569</v>
       </c>
       <c r="X17" t="n">
         <v>-32462.68281610273</v>
@@ -5188,7 +5032,7 @@
         <v>1.641468707511774e-07</v>
       </c>
       <c r="Z17" t="n">
-        <v>312.95</v>
+        <v>1991.248229495919</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000742e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>87.21101859249019</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 20.527x + -35418.111</t>
-        </is>
+      <c r="W18" t="n">
+        <v>20.52739369706097</v>
       </c>
       <c r="X18" t="n">
         <v>-35418.1106533694</v>
@@ -5240,7 +5082,7 @@
         <v>2.361552495473717e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>293.53</v>
+        <v>1967.586212221529</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000006193e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>87.24260243608222</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 20.763x + -35432.798</t>
-        </is>
+      <c r="W19" t="n">
+        <v>20.76288873458724</v>
       </c>
       <c r="X19" t="n">
         <v>-35432.79796440994</v>
@@ -5292,7 +5132,7 @@
         <v>2.443762620555358e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>287.75</v>
+        <v>1944.175870618619</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000007964e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>87.20445645515159</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.479x + -34469.828</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.47913229735686</v>
       </c>
       <c r="X20" t="n">
         <v>-34469.82774745971</v>
@@ -5344,7 +5182,7 @@
         <v>1.370783292064139e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>285.6800000000001</v>
+        <v>1920.597611260568</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000004e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>87.02346503572944</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 19.232x + -31823.654</t>
-        </is>
+      <c r="W21" t="n">
+        <v>19.23183397047734</v>
       </c>
       <c r="X21" t="n">
         <v>-31823.6538609025</v>
@@ -5396,7 +5232,7 @@
         <v>1.725611565560686e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>289.1899999999998</v>
+        <v>1896.732161770606</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>87.08180461592221</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 19.617x + -32106.825</t>
-        </is>
+      <c r="W22" t="n">
+        <v>19.61699616315311</v>
       </c>
       <c r="X22" t="n">
         <v>-32106.82479283401</v>
@@ -5448,7 +5282,7 @@
         <v>6.971610374595483e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>284.26</v>
+        <v>1873.651128718761</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000006e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>84.06997857984675</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.627x + -23988.672</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.627461124910004</v>
       </c>
       <c r="X2" t="n">
         <v>-23988.67161412517</v>
@@ -5646,7 +5478,7 @@
         <v>6.094284275004969e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>857.8899999999999</v>
+        <v>2861.355575806176</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000491e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.14728109852139</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.779x + -26656.466</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.77869834955354</v>
       </c>
       <c r="X3" t="n">
         <v>-26656.46554165931</v>
@@ -5698,7 +5528,7 @@
         <v>1.777000906103705e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>631.5700000000002</v>
+        <v>2639.04534560048</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000023e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.78090769053057</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.556x + -30015.886</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.55556535748099</v>
       </c>
       <c r="X4" t="n">
         <v>-30015.88560368071</v>
@@ -5750,7 +5578,7 @@
         <v>9.871236760553751e-14</v>
       </c>
       <c r="Z4" t="n">
-        <v>530.1599999999999</v>
+        <v>2571.783365457188</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>86.03689023723601</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.434x + -31510.326</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.43421418648794</v>
       </c>
       <c r="X5" t="n">
         <v>-31510.32553480652</v>
@@ -5802,7 +5628,7 @@
         <v>1.029584111272498e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>488.0500000000002</v>
+        <v>2532.379522275629</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001307e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>85.95668707320529</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.147x + -30286.850</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.14697252989372</v>
       </c>
       <c r="X6" t="n">
         <v>-30286.84957451514</v>
@@ -5854,7 +5678,7 @@
         <v>3.84097581558627e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>454.6600000000003</v>
+        <v>2496.352419223506</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000009e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>86.34013489689221</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.634x + -33262.273</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.63386354372579</v>
       </c>
       <c r="X7" t="n">
         <v>-33262.27268777401</v>
@@ -5906,7 +5728,7 @@
         <v>6.654196279765398e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>417.4000000000001</v>
+        <v>2461.186323952877</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>86.581193104094</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.739x + -35276.919</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.73910392781817</v>
       </c>
       <c r="X8" t="n">
         <v>-35276.91877928114</v>
@@ -5958,7 +5778,7 @@
         <v>56.41577637011398</v>
       </c>
       <c r="Z8" t="n">
-        <v>390.25</v>
+        <v>2434.615413122013</v>
       </c>
       <c r="AA8" t="n">
         <v>1.215077235745217e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>86.36678670884372</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.749x + -32521.822</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.74885878059033</v>
       </c>
       <c r="X9" t="n">
         <v>-32521.82245420742</v>
@@ -6010,7 +5828,7 @@
         <v>3.124629398836019e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>393.5499999999997</v>
+        <v>2390.707416245429</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000003e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>86.46740804464203</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 16.199x + -33030.040</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.19863283205609</v>
       </c>
       <c r="X10" t="n">
         <v>-33030.03958684207</v>
@@ -6062,7 +5878,7 @@
         <v>4.852318402191515e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>376.1499999999999</v>
+        <v>2357.173159253746</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000721248e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>86.66742351906323</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.173x + -34703.407</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.17324502233394</v>
       </c>
       <c r="X11" t="n">
         <v>-34703.40742953988</v>
@@ -6114,7 +5928,7 @@
         <v>3.292427635820399e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>357.8499999999999</v>
+        <v>2325.861417769378</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>85.26503803742386</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.073x + -25360.258</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.07301918239592</v>
       </c>
       <c r="X2" t="n">
         <v>-25360.25761020574</v>
@@ -6312,7 +6124,7 @@
         <v>1.272520016605016e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>640.0799999999999</v>
+        <v>2417.257251795772</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000001e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>85.85756892798655</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.807x + -27619.299</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.80733014501527</v>
       </c>
       <c r="X3" t="n">
         <v>-27619.29941574144</v>
@@ -6364,7 +6174,7 @@
         <v>3.504708599181555e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>497.1400000000001</v>
+        <v>2321.521389353818</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>86.37244468159501</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.773x + -31237.972</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.77348852016064</v>
       </c>
       <c r="X4" t="n">
         <v>-31237.97154215303</v>
@@ -6416,7 +6224,7 @@
         <v>3.25461203434129e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>429.1699999999998</v>
+        <v>2281.714614064709</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000026e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>86.36967910136703</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.761x + -30741.488</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.76144008498152</v>
       </c>
       <c r="X5" t="n">
         <v>-30741.488300718</v>
@@ -6468,7 +6274,7 @@
         <v>6.467837727914035e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>415.5899999999999</v>
+        <v>2251.90916464284</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000058e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>86.46644118551589</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.194x + -31255.293</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.19418927705247</v>
       </c>
       <c r="X6" t="n">
         <v>-31255.29273366674</v>
@@ -6520,7 +6324,7 @@
         <v>1.428258509733219e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>398.5099999999998</v>
+        <v>2225.650434128286</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>86.52047740049771</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.446x + -31403.741</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.44631538686392</v>
       </c>
       <c r="X7" t="n">
         <v>-31403.74141723057</v>
@@ -6572,7 +6374,7 @@
         <v>4.139853926920892e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>388.0299999999997</v>
+        <v>2199.84142326194</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000011329e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>86.82391415134171</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.021x + -34287.767</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.02126371719265</v>
       </c>
       <c r="X8" t="n">
         <v>-34287.76684967094</v>
@@ -6624,7 +6424,7 @@
         <v>7.194038909073669e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>368.4100000000001</v>
+        <v>2175.567918374628</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000012003e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>86.7647900908143</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.691x + -33225.870</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.69123984545906</v>
       </c>
       <c r="X9" t="n">
         <v>-33225.87018089015</v>
@@ -6676,7 +6474,7 @@
         <v>1.911543712929486e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>366.96</v>
+        <v>2152.458574001397</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000221e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>86.59667715992504</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 16.815x + -31091.603</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.81544228231631</v>
       </c>
       <c r="X10" t="n">
         <v>-31091.60252052121</v>
@@ -6728,7 +6524,7 @@
         <v>1.589425969651113e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>371.05</v>
+        <v>2129.849988865153</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000010251e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>86.63710266218561</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.018x + -31158.698</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.0180547001853</v>
       </c>
       <c r="X11" t="n">
         <v>-31158.69792909854</v>
@@ -6780,7 +6574,7 @@
         <v>1.218747229191968e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>367.7599999999998</v>
+        <v>2107.427197217289</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005637e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>86.67237945162864</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 17.199x + -31181.095</t>
-        </is>
+      <c r="W12" t="n">
+        <v>17.19887942365197</v>
       </c>
       <c r="X12" t="n">
         <v>-31181.09533649846</v>
@@ -6832,7 +6624,7 @@
         <v>1.495794803160773e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>361.4200000000001</v>
+        <v>2084.479934258037</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>86.72741549520923</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 17.489x + -31400.854</t>
-        </is>
+      <c r="W13" t="n">
+        <v>17.48876422553271</v>
       </c>
       <c r="X13" t="n">
         <v>-31400.85391835023</v>
@@ -6884,7 +6674,7 @@
         <v>1.087838234381142e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>354.8200000000002</v>
+        <v>2062.319116559911</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000859348e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>86.87501756284391</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 18.317x + -32649.957</t>
-        </is>
+      <c r="W14" t="n">
+        <v>18.31656847015248</v>
       </c>
       <c r="X14" t="n">
         <v>-32649.95671846926</v>
@@ -6936,7 +6724,7 @@
         <v>1.23833172258368e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>342.6299999999999</v>
+        <v>2040.0715355379</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000011e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>86.72566485057003</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 17.479x + -30680.447</t>
-        </is>
+      <c r="W15" t="n">
+        <v>17.47939337060038</v>
       </c>
       <c r="X15" t="n">
         <v>-30680.44679676006</v>
@@ -6988,7 +6774,7 @@
         <v>1.233578663534895e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>347</v>
+        <v>2017.470223534055</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000128576e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>86.86596343878402</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 18.264x + -31811.788</t>
-        </is>
+      <c r="W16" t="n">
+        <v>18.26354729329279</v>
       </c>
       <c r="X16" t="n">
         <v>-31811.78809521202</v>
@@ -7040,7 +6824,7 @@
         <v>1.110046833897703e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>339.0800000000002</v>
+        <v>1994.414255381434</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000433062e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>86.72961676194363</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 17.501x + -30004.383</t>
-        </is>
+      <c r="W17" t="n">
+        <v>17.50056139447045</v>
       </c>
       <c r="X17" t="n">
         <v>-30004.38342051718</v>
@@ -7092,7 +6874,7 @@
         <v>9.463125812017704e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>337.6700000000001</v>
+        <v>1971.80928950046</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000049399e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>87.08194290508197</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 19.618x + -33555.578</t>
-        </is>
+      <c r="W18" t="n">
+        <v>19.61792743862667</v>
       </c>
       <c r="X18" t="n">
         <v>-33555.57762910577</v>
@@ -7144,7 +6924,7 @@
         <v>2.132741841604442e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>319.4000000000001</v>
+        <v>1948.8704975274</v>
       </c>
       <c r="AA18" t="n">
         <v>1.00000000000546e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>87.01667204533068</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 19.188x + -32377.096</t>
-        </is>
+      <c r="W19" t="n">
+        <v>19.18796441125966</v>
       </c>
       <c r="X19" t="n">
         <v>-32377.09633251138</v>
@@ -7196,7 +6974,7 @@
         <v>1.157994264965029e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>317.95</v>
+        <v>1926.463805741966</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>87.17222440948095</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.245x + -33903.544</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.24533045520981</v>
       </c>
       <c r="X20" t="n">
         <v>-33903.54393270001</v>
@@ -7248,7 +7024,7 @@
         <v>2.84339648003393e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>307.3299999999999</v>
+        <v>1904.315773347781</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000007e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>87.02268624965933</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 19.227x + -31673.888</t>
-        </is>
+      <c r="W21" t="n">
+        <v>19.22679437068009</v>
       </c>
       <c r="X21" t="n">
         <v>-31673.88839292728</v>
@@ -7300,7 +7074,7 @@
         <v>8.359280786738904e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>310.1599999999999</v>
+        <v>1881.377922343777</v>
       </c>
       <c r="AA21" t="n">
         <v>1.00000000000018e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>87.15910525370883</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 20.152x + -32912.498</t>
-        </is>
+      <c r="W22" t="n">
+        <v>20.15168585893034</v>
       </c>
       <c r="X22" t="n">
         <v>-32912.49848217268</v>
@@ -7352,7 +7124,7 @@
         <v>1.467360730497264e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>298.0699999999999</v>
+        <v>1859.214645820526</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000671e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>83.63503772770461</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.965x + -22177.929</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.964686566517837</v>
       </c>
       <c r="X2" t="n">
         <v>-22177.92908583114</v>
@@ -7550,7 +7320,7 @@
         <v>6.182570499047168e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>928.0900000000001</v>
+        <v>2836.506792698845</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000036e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.08997401163158</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.641x + -25873.603</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.64056039767696</v>
       </c>
       <c r="X3" t="n">
         <v>-25873.60345906585</v>
@@ -7602,7 +7370,7 @@
         <v>2.641420491502718e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>663.3600000000001</v>
+        <v>2577.065457548962</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000043e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>85.58355515337779</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.948x + -27929.120</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.94757686828144</v>
       </c>
       <c r="X4" t="n">
         <v>-27929.11952677896</v>
@@ -7654,7 +7420,7 @@
         <v>1.935819490544788e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>558.0100000000002</v>
+        <v>2506.729730222475</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000040485e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>85.82559054158641</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.701x + -29087.006</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.70118710416935</v>
       </c>
       <c r="X5" t="n">
         <v>-29087.00570661683</v>
@@ -7706,7 +7470,7 @@
         <v>2.861860459995864e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>509.7000000000003</v>
+        <v>2463.603182842488</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000003e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>86.14632727722568</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.845x + -31185.382</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.84541089672301</v>
       </c>
       <c r="X6" t="n">
         <v>-31185.3822423091</v>
@@ -7758,7 +7520,7 @@
         <v>1.447256478326925e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>459.8699999999999</v>
+        <v>2426.451270190614</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000004894e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>86.27191915962126</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.347x + -31797.228</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.34701108456082</v>
       </c>
       <c r="X7" t="n">
         <v>-31797.22813634483</v>
@@ -7810,7 +7570,7 @@
         <v>1.033027993547383e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>431.5800000000002</v>
+        <v>2389.775832998311</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000003441e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>86.52124993113947</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.450x + -33745.744</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.44997663615734</v>
       </c>
       <c r="X8" t="n">
         <v>-33745.74401886032</v>
@@ -7862,7 +7620,7 @@
         <v>1.920523641782357e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>398.52</v>
+        <v>2354.487893738019</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001441e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>86.33751659904978</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.623x + -31401.606</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.62265647296377</v>
       </c>
       <c r="X9" t="n">
         <v>-31401.60645278211</v>
@@ -7914,7 +7670,7 @@
         <v>2.164242542498674e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>403.7499999999998</v>
+        <v>2319.877383328213</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000035413e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>86.29157954390369</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.429x + -30527.163</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.4286035577321</v>
       </c>
       <c r="X10" t="n">
         <v>-30527.16340045061</v>
@@ -7966,7 +7720,7 @@
         <v>8.618416090041746e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>388.8300000000002</v>
+        <v>2287.782641462251</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000444e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>86.24885512448218</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.252x + -29729.496</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.25238180311318</v>
       </c>
       <c r="X11" t="n">
         <v>-29729.4956525476</v>
@@ -8018,7 +7770,7 @@
         <v>3.488565273240728e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>386.5</v>
+        <v>2257.43812124825</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000007784e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.24095623139149</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.012x + -25001.691</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.01164730377898</v>
       </c>
       <c r="X2" t="n">
         <v>-25001.69081116027</v>
@@ -8216,7 +7966,7 @@
         <v>8.614824750024697e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>620.1099999999999</v>
+        <v>2399.94346229863</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000002177e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>86.16521386443776</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.919x + -29924.882</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.91874600207334</v>
       </c>
       <c r="X3" t="n">
         <v>-29924.88177488731</v>
@@ -8268,7 +8016,7 @@
         <v>9.034253212907334e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>458.4399999999998</v>
+        <v>2310.751011394418</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000281e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>86.1224753536069</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.754x + -28957.730</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.75381506966897</v>
       </c>
       <c r="X4" t="n">
         <v>-28957.73037579245</v>
@@ -8320,7 +8066,7 @@
         <v>1.288773157832972e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>441.5000000000002</v>
+        <v>2273.456502967149</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000146725e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>86.46458198322632</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.186x + -31609.437</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.18565145398889</v>
       </c>
       <c r="X5" t="n">
         <v>-31609.43672057775</v>
@@ -8372,7 +8116,7 @@
         <v>8.146716851668575e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>410.3099999999999</v>
+        <v>2246.025450272327</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000152916e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>86.50419148557604</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.370x + -31639.705</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.36950782869518</v>
       </c>
       <c r="X6" t="n">
         <v>-31639.7050943957</v>
@@ -8424,7 +8166,7 @@
         <v>9.128634375804588e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>404.9699999999998</v>
+        <v>2220.941541587195</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000029e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>86.47439655625823</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.231x + -30998.940</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.23082347670283</v>
       </c>
       <c r="X7" t="n">
         <v>-30998.9395754244</v>
@@ -8476,7 +8216,7 @@
         <v>1.01343190634668e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>396.1199999999999</v>
+        <v>2199.870963468618</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000006521e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>86.30722350466797</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 15.494x + -29165.055</t>
-        </is>
+      <c r="W8" t="n">
+        <v>15.4941473154193</v>
       </c>
       <c r="X8" t="n">
         <v>-29165.0548599034</v>
@@ -8528,7 +8266,7 @@
         <v>1.270165455564024e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>408.4200000000001</v>
+        <v>2177.329610599659</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000014658e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>86.49018023772855</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.304x + -30472.432</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.30399774858492</v>
       </c>
       <c r="X9" t="n">
         <v>-30472.43202429854</v>
@@ -8580,7 +8316,7 @@
         <v>6.065072671323593e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>385.4199999999998</v>
+        <v>2153.720312297246</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000355e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>86.66014286444735</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.136x + -31800.165</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.13572389088087</v>
       </c>
       <c r="X10" t="n">
         <v>-31800.16477470212</v>
@@ -8632,7 +8366,7 @@
         <v>3.110470417100931e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>373.8799999999999</v>
+        <v>2130.472622984718</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000075e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>86.71182300552242</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.406x + -31994.031</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.40565167238079</v>
       </c>
       <c r="X11" t="n">
         <v>-31994.03138025086</v>
@@ -8684,7 +8416,7 @@
         <v>2.091815773086266e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>369.9100000000001</v>
+        <v>2107.606532311479</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000142e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>86.53389226853824</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 16.510x + -29867.562</t>
-        </is>
+      <c r="W12" t="n">
+        <v>16.51012398774608</v>
       </c>
       <c r="X12" t="n">
         <v>-29867.56232307294</v>
@@ -8736,7 +8466,7 @@
         <v>1.32397366149695e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>372.7500000000002</v>
+        <v>2084.665423401611</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000003696e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>86.72309669613963</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 17.466x + -31383.629</t>
-        </is>
+      <c r="W13" t="n">
+        <v>17.46566464517314</v>
       </c>
       <c r="X13" t="n">
         <v>-31383.62879914522</v>
@@ -8788,7 +8516,7 @@
         <v>1.743200290483485e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>350.9500000000003</v>
+        <v>2062.165297819159</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000847e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>86.77244950582413</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 17.733x + -31538.116</t>
-        </is>
+      <c r="W14" t="n">
+        <v>17.73331282166365</v>
       </c>
       <c r="X14" t="n">
         <v>-31538.11576055409</v>
@@ -8840,7 +8566,7 @@
         <v>2.058927311162519e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>342.5800000000002</v>
+        <v>2039.402210844883</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000002522e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>86.8254226228315</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 18.030x + -31728.962</t>
-        </is>
+      <c r="W15" t="n">
+        <v>18.02984448720051</v>
       </c>
       <c r="X15" t="n">
         <v>-31728.96189146264</v>
@@ -8892,7 +8616,7 @@
         <v>1.367241277796674e-07</v>
       </c>
       <c r="Z15" t="n">
-        <v>327.3299999999999</v>
+        <v>2016.192286684543</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000456e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>86.8837951853873</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 18.368x + -32006.938</t>
-        </is>
+      <c r="W16" t="n">
+        <v>18.36826429033929</v>
       </c>
       <c r="X16" t="n">
         <v>-32006.93782961402</v>
@@ -8944,7 +8666,7 @@
         <v>4.556427182879011e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>337.0600000000002</v>
+        <v>1993.319305247415</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000095e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>86.83410191399658</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 18.079x + -31086.690</t>
-        </is>
+      <c r="W17" t="n">
+        <v>18.07937436872513</v>
       </c>
       <c r="X17" t="n">
         <v>-31086.68979129966</v>
@@ -8996,7 +8716,7 @@
         <v>3.153163672748359e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>334.8299999999999</v>
+        <v>1970.265963456888</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000215e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>86.98419580198654</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 18.981x + -32379.190</t>
-        </is>
+      <c r="W18" t="n">
+        <v>18.98095929896683</v>
       </c>
       <c r="X18" t="n">
         <v>-32379.18983177853</v>
@@ -9048,7 +8766,7 @@
         <v>1.619802128066902e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>320.0599999999999</v>
+        <v>1947.038536450478</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>87.12366954272167</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 19.903x + -33667.700</t>
-        </is>
+      <c r="W19" t="n">
+        <v>19.9030119455071</v>
       </c>
       <c r="X19" t="n">
         <v>-33667.70040112365</v>
@@ -9100,7 +8816,7 @@
         <v>4.89175714841225e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>313.4200000000001</v>
+        <v>1924.050760428205</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>87.08398938991256</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 19.632x + -32750.634</t>
-        </is>
+      <c r="W20" t="n">
+        <v>19.6317193209327</v>
       </c>
       <c r="X20" t="n">
         <v>-32750.63359749494</v>
@@ -9152,7 +8866,7 @@
         <v>7.722922622809486e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>300.1600000000001</v>
+        <v>1900.609551264085</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000101e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>87.14094224806178</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 20.023x + -33032.993</t>
-        </is>
+      <c r="W21" t="n">
+        <v>20.02345561047489</v>
       </c>
       <c r="X21" t="n">
         <v>-33032.99326825517</v>
@@ -9204,7 +8916,7 @@
         <v>4.358347694258068e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>295.3899999999999</v>
+        <v>1877.277228200415</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000023054e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>87.00352108731381</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 19.104x + -30999.440</t>
-        </is>
+      <c r="W22" t="n">
+        <v>19.10359946225696</v>
       </c>
       <c r="X22" t="n">
         <v>-30999.43984475506</v>
@@ -9256,7 +8966,7 @@
         <v>4.557780522910367e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>299.6400000000001</v>
+        <v>1853.739314703515</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000025e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>84.00238532110781</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.518x + -19687.671</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.518176228242169</v>
       </c>
       <c r="X2" t="n">
         <v>-19687.67058978109</v>
@@ -9454,7 +9162,7 @@
         <v>1.227213321259076e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>862.5200000000002</v>
+        <v>2331.000620958536</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>85.7863302037798</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.573x + -24905.664</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.57307300665303</v>
       </c>
       <c r="X3" t="n">
         <v>-24905.66372225419</v>
@@ -9506,7 +9212,7 @@
         <v>1.171980325841046e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>563.0599999999999</v>
+        <v>2092.307869183674</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000602e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>86.21063658149419</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.098x + -26779.132</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.09810750449062</v>
       </c>
       <c r="X4" t="n">
         <v>-26779.13229182119</v>
@@ -9558,7 +9262,7 @@
         <v>4.249067248825103e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>469.71</v>
+        <v>2029.528002474151</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000013e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>86.327269592563</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.579x + -27094.245</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.57894975621988</v>
       </c>
       <c r="X5" t="n">
         <v>-27094.24542119744</v>
@@ -9610,7 +9312,7 @@
         <v>1.46915560628849e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>427.3399999999999</v>
+        <v>1992.585398079097</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000118e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>86.26507633017883</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.319x + -26104.724</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.31881392212656</v>
       </c>
       <c r="X6" t="n">
         <v>-26104.72380503079</v>
@@ -9662,7 +9362,7 @@
         <v>4.462544229633462e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>421.24</v>
+        <v>1958.77864196675</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000038e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>86.44243777535029</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.085x + -27035.563</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.0846461414013</v>
       </c>
       <c r="X7" t="n">
         <v>-27035.56261448654</v>
@@ -9714,7 +9412,7 @@
         <v>1.34133417951443e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>393.6000000000001</v>
+        <v>1924.150154369358</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000583e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>86.628056008865</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.972x + -28160.046</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.97229146442941</v>
       </c>
       <c r="X8" t="n">
         <v>-28160.04567139671</v>
@@ -9766,7 +9462,7 @@
         <v>2.147090937601186e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>390.27</v>
+        <v>1890.043765844406</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000017e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>86.69976234518663</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.342x + -28316.699</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.34190288765311</v>
       </c>
       <c r="X9" t="n">
         <v>-28316.6990865787</v>
@@ -9818,7 +9512,7 @@
         <v>8.221931878622256e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>371.4400000000001</v>
+        <v>1857.435200470321</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000000014e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>86.77015134218537</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.721x + -28499.631</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.72066813388714</v>
       </c>
       <c r="X10" t="n">
         <v>-28499.6313728429</v>
@@ -9870,7 +9562,7 @@
         <v>2.161654329277473e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>362.1300000000001</v>
+        <v>1826.801596949331</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000015e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>86.81805336551434</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.988x + -28516.759</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.98800242908816</v>
       </c>
       <c r="X11" t="n">
         <v>-28516.75874047502</v>
@@ -9922,7 +9612,7 @@
         <v>1.333681706639339e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>358.3999999999999</v>
+        <v>1798.781127294667</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-623.0099999999998</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-504.3099999999999</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-469.9100000000003</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-419.7399999999998</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-399.7500000000002</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-405.3399999999999</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-385.0799999999999</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-367.98</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-358.04</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-357.1300000000001</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-840.25</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-620.2400000000002</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-522.1799999999998</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-475.6400000000003</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-440.3799999999997</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-409.71</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-396.3199999999997</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-376.7100000000003</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-362.6399999999999</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-366.0299999999997</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-857.8899999999999</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-631.5700000000002</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-530.1599999999999</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-488.0500000000002</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-454.6600000000003</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-417.4000000000001</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-390.25</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-393.5499999999997</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-376.1499999999999</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-357.8499999999999</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-928.0900000000001</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-663.3600000000001</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-558.0100000000002</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-509.7000000000003</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-459.8699999999999</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-431.5800000000002</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-398.52</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-403.7499999999998</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-388.8300000000002</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-386.5</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-862.5200000000002</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-563.0599999999999</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-469.71</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-427.3399999999999</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-421.24</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-393.6000000000001</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-390.27</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-371.4400000000001</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-362.1300000000001</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-358.3999999999999</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-623.0099999999998</v>
+        <v>1852.065</v>
       </c>
       <c r="D2" t="n">
         <v>1.57401e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-504.3099999999999</v>
+        <v>1740.486</v>
       </c>
       <c r="D3" t="n">
         <v>1.56412e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-469.9100000000003</v>
+        <v>1694.133</v>
       </c>
       <c r="D4" t="n">
         <v>1.55721e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-419.7399999999998</v>
+        <v>1680.005</v>
       </c>
       <c r="D5" t="n">
         <v>1.55024e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-399.7500000000002</v>
+        <v>1655.06</v>
       </c>
       <c r="D6" t="n">
         <v>1.54605e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-405.3399999999999</v>
+        <v>1609.273</v>
       </c>
       <c r="D7" t="n">
         <v>1.5422e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-385.0799999999999</v>
+        <v>1589.43</v>
       </c>
       <c r="D8" t="n">
         <v>1.53894e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-367.98</v>
+        <v>1570.141</v>
       </c>
       <c r="D9" t="n">
         <v>1.53697e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-358.04</v>
+        <v>1549.192</v>
       </c>
       <c r="D10" t="n">
         <v>1.53505e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-357.1300000000001</v>
+        <v>1520.05</v>
       </c>
       <c r="D11" t="n">
         <v>1.53331e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-502.9199999999998</v>
+        <v>1688.479</v>
       </c>
       <c r="D2" t="n">
         <v>1.50004e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-454.5299999999997</v>
+        <v>1595.146</v>
       </c>
       <c r="D3" t="n">
         <v>1.51102e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-439.6499999999999</v>
+        <v>1558.569</v>
       </c>
       <c r="D4" t="n">
         <v>1.51466e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-430.99</v>
+        <v>1530.965</v>
       </c>
       <c r="D5" t="n">
         <v>1.5165e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-427.6199999999999</v>
+        <v>1506.139</v>
       </c>
       <c r="D6" t="n">
         <v>1.51811e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-420.1199999999999</v>
+        <v>1483.101</v>
       </c>
       <c r="D7" t="n">
         <v>1.51943e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-411.7600000000002</v>
+        <v>1464.335</v>
       </c>
       <c r="D8" t="n">
         <v>1.5207e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-413.1200000000001</v>
+        <v>1434.761</v>
       </c>
       <c r="D9" t="n">
         <v>1.5216e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-398.1199999999999</v>
+        <v>1425.297</v>
       </c>
       <c r="D10" t="n">
         <v>1.52248e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-399.3900000000001</v>
+        <v>1401.616</v>
       </c>
       <c r="D11" t="n">
         <v>1.52341e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-385.4700000000003</v>
+        <v>1392.639</v>
       </c>
       <c r="D12" t="n">
         <v>1.52439e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-393.46</v>
+        <v>1360.371</v>
       </c>
       <c r="D13" t="n">
         <v>1.52549e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-381.6299999999999</v>
+        <v>1348.013</v>
       </c>
       <c r="D14" t="n">
         <v>1.52653e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-376.5700000000002</v>
+        <v>1333.18</v>
       </c>
       <c r="D15" t="n">
         <v>1.52702e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-368.3100000000002</v>
+        <v>1316.403</v>
       </c>
       <c r="D16" t="n">
         <v>1.5283e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-375.6699999999998</v>
+        <v>1289.453</v>
       </c>
       <c r="D17" t="n">
         <v>1.5291e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-359.3899999999999</v>
+        <v>1281.755</v>
       </c>
       <c r="D18" t="n">
         <v>1.52989e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-357.77</v>
+        <v>1263.034</v>
       </c>
       <c r="D19" t="n">
         <v>1.53084e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-345.74</v>
+        <v>1250.145</v>
       </c>
       <c r="D20" t="n">
         <v>1.53203e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-349.1199999999999</v>
+        <v>1224.865</v>
       </c>
       <c r="D21" t="n">
         <v>1.5329e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-338.77</v>
+        <v>1216.396</v>
       </c>
       <c r="D22" t="n">
         <v>1.53389e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-525.4000000000001</v>
+        <v>1769.584</v>
       </c>
       <c r="D2" t="n">
         <v>1.53124e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-448.2999999999997</v>
+        <v>1645.954</v>
       </c>
       <c r="D3" t="n">
         <v>1.53789e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-404.02</v>
+        <v>1624.189</v>
       </c>
       <c r="D4" t="n">
         <v>1.53565e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-375.6399999999999</v>
+        <v>1611.416</v>
       </c>
       <c r="D5" t="n">
         <v>1.53249e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-382.3599999999999</v>
+        <v>1572.867</v>
       </c>
       <c r="D6" t="n">
         <v>1.53002e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-354.0700000000002</v>
+        <v>1571.369</v>
       </c>
       <c r="D7" t="n">
         <v>1.52852e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-356.72</v>
+        <v>1540.72</v>
       </c>
       <c r="D8" t="n">
         <v>1.52785e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-353.77</v>
+        <v>1523.677</v>
       </c>
       <c r="D9" t="n">
         <v>1.52729e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-347.2399999999998</v>
+        <v>1503.217</v>
       </c>
       <c r="D10" t="n">
         <v>1.5272e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-344.2400000000002</v>
+        <v>1481.863</v>
       </c>
       <c r="D11" t="n">
         <v>1.52684e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-335.3699999999999</v>
+        <v>1465.444</v>
       </c>
       <c r="D12" t="n">
         <v>1.52707e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-332.99</v>
+        <v>1445.193</v>
       </c>
       <c r="D13" t="n">
         <v>1.52718e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-326.0100000000002</v>
+        <v>1425.42</v>
       </c>
       <c r="D14" t="n">
         <v>1.52771e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-324.01</v>
+        <v>1404.177</v>
       </c>
       <c r="D15" t="n">
         <v>1.52781e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-317.4999999999998</v>
+        <v>1390.899</v>
       </c>
       <c r="D16" t="n">
         <v>1.52811e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-306.2199999999998</v>
+        <v>1376.801</v>
       </c>
       <c r="D17" t="n">
         <v>1.52868e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-308.04</v>
+        <v>1351.382</v>
       </c>
       <c r="D18" t="n">
         <v>1.52882e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-298.8399999999999</v>
+        <v>1338.642</v>
       </c>
       <c r="D19" t="n">
         <v>1.52934e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-299.3900000000001</v>
+        <v>1312.019</v>
       </c>
       <c r="D20" t="n">
         <v>1.53015e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-300.7099999999998</v>
+        <v>1291.17</v>
       </c>
       <c r="D21" t="n">
         <v>1.53017e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-285.3499999999999</v>
+        <v>1281.491</v>
       </c>
       <c r="D22" t="n">
         <v>1.53087e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-840.25</v>
+        <v>2178.327</v>
       </c>
       <c r="D2" t="n">
         <v>1.5001e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-620.2400000000002</v>
+        <v>1900.605</v>
       </c>
       <c r="D3" t="n">
         <v>1.54464e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-522.1799999999998</v>
+        <v>1836.41</v>
       </c>
       <c r="D4" t="n">
         <v>1.54627e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-475.6400000000003</v>
+        <v>1798.322</v>
       </c>
       <c r="D5" t="n">
         <v>1.54211e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-440.3799999999997</v>
+        <v>1759.257</v>
       </c>
       <c r="D6" t="n">
         <v>1.54191e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-409.71</v>
+        <v>1735.943</v>
       </c>
       <c r="D7" t="n">
         <v>1.54119e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-396.3199999999997</v>
+        <v>1700.435</v>
       </c>
       <c r="D8" t="n">
         <v>1.54148e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-376.7100000000003</v>
+        <v>1677.745</v>
       </c>
       <c r="D9" t="n">
         <v>1.54227e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-362.6399999999999</v>
+        <v>1648.179</v>
       </c>
       <c r="D10" t="n">
         <v>1.54354e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-366.0299999999997</v>
+        <v>1610.714</v>
       </c>
       <c r="D11" t="n">
         <v>1.5438e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-610.2400000000002</v>
+        <v>1764.862</v>
       </c>
       <c r="D2" t="n">
         <v>1.55122e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-472.5199999999998</v>
+        <v>1641.607</v>
       </c>
       <c r="D3" t="n">
         <v>1.54604e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-412.55</v>
+        <v>1610.878</v>
       </c>
       <c r="D4" t="n">
         <v>1.5459e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-387.5799999999999</v>
+        <v>1587.512</v>
       </c>
       <c r="D5" t="n">
         <v>1.54624e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-383.3</v>
+        <v>1556.887</v>
       </c>
       <c r="D6" t="n">
         <v>1.54669e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-370.26</v>
+        <v>1539.989</v>
       </c>
       <c r="D7" t="n">
         <v>1.54689e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-371.8799999999999</v>
+        <v>1511.447</v>
       </c>
       <c r="D8" t="n">
         <v>1.54753e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-362.5799999999999</v>
+        <v>1493.047</v>
       </c>
       <c r="D9" t="n">
         <v>1.54803e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-342.3600000000001</v>
+        <v>1487.687</v>
       </c>
       <c r="D10" t="n">
         <v>1.54834e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-348.3599999999999</v>
+        <v>1458.771</v>
       </c>
       <c r="D11" t="n">
         <v>1.5487e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-340.8999999999999</v>
+        <v>1437.555</v>
       </c>
       <c r="D12" t="n">
         <v>1.54927e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-339.7200000000003</v>
+        <v>1413.471</v>
       </c>
       <c r="D13" t="n">
         <v>1.54918e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-320.9699999999998</v>
+        <v>1406.915</v>
       </c>
       <c r="D14" t="n">
         <v>1.54987e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-315.3</v>
+        <v>1388.66</v>
       </c>
       <c r="D15" t="n">
         <v>1.55014e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-308.0999999999999</v>
+        <v>1371.678</v>
       </c>
       <c r="D16" t="n">
         <v>1.55091e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-312.95</v>
+        <v>1341.192</v>
       </c>
       <c r="D17" t="n">
         <v>1.55166e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-293.53</v>
+        <v>1334.44</v>
       </c>
       <c r="D18" t="n">
         <v>1.5523e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-287.75</v>
+        <v>1315.413</v>
       </c>
       <c r="D19" t="n">
         <v>1.5529e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-285.6800000000001</v>
+        <v>1293.375</v>
       </c>
       <c r="D20" t="n">
         <v>1.55332e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-289.1899999999998</v>
+        <v>1263.856</v>
       </c>
       <c r="D21" t="n">
         <v>1.55423e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-284.26</v>
+        <v>1247.206</v>
       </c>
       <c r="D22" t="n">
         <v>1.55471e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-857.8899999999999</v>
+        <v>2122.309</v>
       </c>
       <c r="D2" t="n">
         <v>1.51828e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-631.5700000000002</v>
+        <v>1885.563</v>
       </c>
       <c r="D3" t="n">
         <v>1.5463e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-530.1599999999999</v>
+        <v>1833.062</v>
       </c>
       <c r="D4" t="n">
         <v>1.54451e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-488.0500000000002</v>
+        <v>1798.479</v>
       </c>
       <c r="D5" t="n">
         <v>1.53886e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-454.6600000000003</v>
+        <v>1755.353</v>
       </c>
       <c r="D6" t="n">
         <v>1.54082e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-417.4000000000001</v>
+        <v>1744.804</v>
       </c>
       <c r="D7" t="n">
         <v>1.54129e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-390.25</v>
+        <v>1720.706</v>
       </c>
       <c r="D8" t="n">
         <v>1.54278e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-393.5499999999997</v>
+        <v>1678.333</v>
       </c>
       <c r="D9" t="n">
         <v>1.54435e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-376.1499999999999</v>
+        <v>1656.884</v>
       </c>
       <c r="D10" t="n">
         <v>1.54613e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-357.8499999999999</v>
+        <v>1638.843</v>
       </c>
       <c r="D11" t="n">
         <v>1.54794e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-640.0799999999999</v>
+        <v>1718.342</v>
       </c>
       <c r="D2" t="n">
         <v>1.55451e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-497.1400000000001</v>
+        <v>1610.434</v>
       </c>
       <c r="D3" t="n">
         <v>1.54978e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-429.1699999999998</v>
+        <v>1592.685</v>
       </c>
       <c r="D4" t="n">
         <v>1.54721e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-415.5899999999999</v>
+        <v>1556.143</v>
       </c>
       <c r="D5" t="n">
         <v>1.54876e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-398.5099999999998</v>
+        <v>1535.808</v>
       </c>
       <c r="D6" t="n">
         <v>1.55017e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-388.0299999999997</v>
+        <v>1514.839</v>
       </c>
       <c r="D7" t="n">
         <v>1.55111e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-368.4100000000001</v>
+        <v>1506.431</v>
       </c>
       <c r="D8" t="n">
         <v>1.55234e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-366.96</v>
+        <v>1483.257</v>
       </c>
       <c r="D9" t="n">
         <v>1.55307e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-371.05</v>
+        <v>1454.908</v>
       </c>
       <c r="D10" t="n">
         <v>1.55378e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-367.7599999999998</v>
+        <v>1434.402</v>
       </c>
       <c r="D11" t="n">
         <v>1.55444e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-361.4200000000001</v>
+        <v>1417.292</v>
       </c>
       <c r="D12" t="n">
         <v>1.55496e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-354.8200000000002</v>
+        <v>1404.086</v>
       </c>
       <c r="D13" t="n">
         <v>1.55583e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-342.6299999999999</v>
+        <v>1389.497</v>
       </c>
       <c r="D14" t="n">
         <v>1.55627e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-347</v>
+        <v>1361.281</v>
       </c>
       <c r="D15" t="n">
         <v>1.55733e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-339.0800000000002</v>
+        <v>1348.774</v>
       </c>
       <c r="D16" t="n">
         <v>1.55792e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-337.6700000000001</v>
+        <v>1324.518</v>
       </c>
       <c r="D17" t="n">
         <v>1.55865e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-319.4000000000001</v>
+        <v>1321.127</v>
       </c>
       <c r="D18" t="n">
         <v>1.55936e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-317.95</v>
+        <v>1298.433</v>
       </c>
       <c r="D19" t="n">
         <v>1.55983e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-307.3299999999999</v>
+        <v>1286.323</v>
       </c>
       <c r="D20" t="n">
         <v>1.56098e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-310.1599999999999</v>
+        <v>1261.093</v>
       </c>
       <c r="D21" t="n">
         <v>1.56129e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-298.0699999999999</v>
+        <v>1249.709</v>
       </c>
       <c r="D22" t="n">
         <v>1.56205e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-928.0900000000001</v>
+        <v>2088.844</v>
       </c>
       <c r="D2" t="n">
         <v>1.50818e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-663.3600000000001</v>
+        <v>1829.747</v>
       </c>
       <c r="D3" t="n">
         <v>1.55608e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-558.0100000000002</v>
+        <v>1760.926</v>
       </c>
       <c r="D4" t="n">
         <v>1.55542e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-509.7000000000003</v>
+        <v>1727.173</v>
       </c>
       <c r="D5" t="n">
         <v>1.55174e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-459.8699999999999</v>
+        <v>1702.897</v>
       </c>
       <c r="D6" t="n">
         <v>1.5523e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-431.5800000000002</v>
+        <v>1673.924</v>
       </c>
       <c r="D7" t="n">
         <v>1.5533e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-398.52</v>
+        <v>1653.709</v>
       </c>
       <c r="D8" t="n">
         <v>1.55459e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-403.7499999999998</v>
+        <v>1616.318</v>
       </c>
       <c r="D9" t="n">
         <v>1.55649e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-388.8300000000002</v>
+        <v>1582.14</v>
       </c>
       <c r="D10" t="n">
         <v>1.55979e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-386.5</v>
+        <v>1552.786</v>
       </c>
       <c r="D11" t="n">
         <v>1.56226e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-620.1099999999999</v>
+        <v>1679.799</v>
       </c>
       <c r="D2" t="n">
         <v>1.57138e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-458.4399999999998</v>
+        <v>1600.857</v>
       </c>
       <c r="D3" t="n">
         <v>1.56059e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-441.5000000000002</v>
+        <v>1556.955</v>
       </c>
       <c r="D4" t="n">
         <v>1.55947e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-410.3099999999999</v>
+        <v>1547.604</v>
       </c>
       <c r="D5" t="n">
         <v>1.56151e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-404.9699999999998</v>
+        <v>1528.567</v>
       </c>
       <c r="D6" t="n">
         <v>1.56145e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-396.1199999999999</v>
+        <v>1502.115</v>
       </c>
       <c r="D7" t="n">
         <v>1.56295e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-408.4200000000001</v>
+        <v>1476.099</v>
       </c>
       <c r="D8" t="n">
         <v>1.56656e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-385.4199999999998</v>
+        <v>1461.996</v>
       </c>
       <c r="D9" t="n">
         <v>1.56748e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-373.8799999999999</v>
+        <v>1448.296</v>
       </c>
       <c r="D10" t="n">
         <v>1.56694e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-369.9100000000001</v>
+        <v>1428.58</v>
       </c>
       <c r="D11" t="n">
         <v>1.56884e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-372.7500000000002</v>
+        <v>1400.32</v>
       </c>
       <c r="D12" t="n">
         <v>1.56939e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-350.9500000000003</v>
+        <v>1393.618</v>
       </c>
       <c r="D13" t="n">
         <v>1.57091e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-342.5800000000002</v>
+        <v>1372.41</v>
       </c>
       <c r="D14" t="n">
         <v>1.5723e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-327.3299999999999</v>
+        <v>1355.007</v>
       </c>
       <c r="D15" t="n">
         <v>1.57241e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-337.0600000000002</v>
+        <v>1334.625</v>
       </c>
       <c r="D16" t="n">
         <v>1.57271e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-334.8299999999999</v>
+        <v>1314.383</v>
       </c>
       <c r="D17" t="n">
         <v>1.57264e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-320.0599999999999</v>
+        <v>1303.558</v>
       </c>
       <c r="D18" t="n">
         <v>1.57417e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-313.4200000000001</v>
+        <v>1286.945</v>
       </c>
       <c r="D19" t="n">
         <v>1.57495e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-300.1600000000001</v>
+        <v>1267.219</v>
       </c>
       <c r="D20" t="n">
         <v>1.57697e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-295.3899999999999</v>
+        <v>1246.586</v>
       </c>
       <c r="D21" t="n">
         <v>1.57805e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-299.6400000000001</v>
+        <v>1220.686</v>
       </c>
       <c r="D22" t="n">
         <v>1.57798e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-862.5200000000002</v>
+        <v>1656.272</v>
       </c>
       <c r="D2" t="n">
         <v>1.55519e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-563.0599999999999</v>
+        <v>1418.672</v>
       </c>
       <c r="D3" t="n">
         <v>1.57788e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-469.71</v>
+        <v>1354.417</v>
       </c>
       <c r="D4" t="n">
         <v>1.5718e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-427.3399999999999</v>
+        <v>1320.446</v>
       </c>
       <c r="D5" t="n">
         <v>1.56788e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-421.24</v>
+        <v>1280.727</v>
       </c>
       <c r="D6" t="n">
         <v>1.56482e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-393.6000000000001</v>
+        <v>1258.651</v>
       </c>
       <c r="D7" t="n">
         <v>1.56741e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-390.27</v>
+        <v>1237.212</v>
       </c>
       <c r="D8" t="n">
         <v>1.56929e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-371.4400000000001</v>
+        <v>1210.55</v>
       </c>
       <c r="D9" t="n">
         <v>1.57095e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-362.1300000000001</v>
+        <v>1190.579</v>
       </c>
       <c r="D10" t="n">
         <v>1.57463e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-358.3999999999999</v>
+        <v>1163.373</v>
       </c>
       <c r="D11" t="n">
         <v>1.57704e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>1852.065</v>
       </c>
+      <c r="C2" t="n">
+        <v>2330.528909500215</v>
+      </c>
       <c r="D2" t="n">
         <v>1.57401e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>1740.486</v>
       </c>
+      <c r="C3" t="n">
+        <v>2201.65235182682</v>
+      </c>
       <c r="D3" t="n">
         <v>1.56412e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>1694.133</v>
       </c>
+      <c r="C4" t="n">
+        <v>2158.275679832005</v>
+      </c>
       <c r="D4" t="n">
         <v>1.55721e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>1680.005</v>
       </c>
+      <c r="C5" t="n">
+        <v>2145.785490304964</v>
+      </c>
       <c r="D5" t="n">
         <v>1.55024e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1655.06</v>
       </c>
+      <c r="C6" t="n">
+        <v>2123.170936610426</v>
+      </c>
       <c r="D6" t="n">
         <v>1.54605e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1609.273</v>
       </c>
+      <c r="C7" t="n">
+        <v>2081.340594142706</v>
+      </c>
       <c r="D7" t="n">
         <v>1.5422e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1589.43</v>
       </c>
+      <c r="C8" t="n">
+        <v>2063.265496734332</v>
+      </c>
       <c r="D8" t="n">
         <v>1.53894e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1570.141</v>
       </c>
+      <c r="C9" t="n">
+        <v>2043.954931825243</v>
+      </c>
       <c r="D9" t="n">
         <v>1.53697e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1549.192</v>
       </c>
+      <c r="C10" t="n">
+        <v>2021.428335313965</v>
+      </c>
       <c r="D10" t="n">
         <v>1.53505e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1520.05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1994.102542632603</v>
       </c>
       <c r="D11" t="n">
         <v>1.53331e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>1688.479</v>
       </c>
+      <c r="C2" t="n">
+        <v>2179.905642016238</v>
+      </c>
       <c r="D2" t="n">
         <v>1.50004e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1595.146</v>
       </c>
+      <c r="C3" t="n">
+        <v>2057.176124999146</v>
+      </c>
       <c r="D3" t="n">
         <v>1.51102e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1558.569</v>
       </c>
+      <c r="C4" t="n">
+        <v>2021.406381895755</v>
+      </c>
       <c r="D4" t="n">
         <v>1.51466e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1530.965</v>
       </c>
+      <c r="C5" t="n">
+        <v>1997.144161002714</v>
+      </c>
       <c r="D5" t="n">
         <v>1.5165e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1506.139</v>
       </c>
+      <c r="C6" t="n">
+        <v>1970.867818627416</v>
+      </c>
       <c r="D6" t="n">
         <v>1.51811e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1483.101</v>
       </c>
+      <c r="C7" t="n">
+        <v>1951.435631213821</v>
+      </c>
       <c r="D7" t="n">
         <v>1.51943e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1464.335</v>
       </c>
+      <c r="C8" t="n">
+        <v>1931.701820055622</v>
+      </c>
       <c r="D8" t="n">
         <v>1.5207e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1434.761</v>
       </c>
+      <c r="C9" t="n">
+        <v>1908.893095007386</v>
+      </c>
       <c r="D9" t="n">
         <v>1.5216e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1425.297</v>
       </c>
+      <c r="C10" t="n">
+        <v>1899.004457950135</v>
+      </c>
       <c r="D10" t="n">
         <v>1.52248e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1401.616</v>
       </c>
+      <c r="C11" t="n">
+        <v>1873.430404927851</v>
+      </c>
       <c r="D11" t="n">
         <v>1.52341e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1392.639</v>
       </c>
+      <c r="C12" t="n">
+        <v>1865.63397296379</v>
+      </c>
       <c r="D12" t="n">
         <v>1.52439e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1360.371</v>
       </c>
+      <c r="C13" t="n">
+        <v>1836.345176859164</v>
+      </c>
       <c r="D13" t="n">
         <v>1.52549e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1348.013</v>
       </c>
+      <c r="C14" t="n">
+        <v>1824.522802296413</v>
+      </c>
       <c r="D14" t="n">
         <v>1.52653e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1333.18</v>
       </c>
+      <c r="C15" t="n">
+        <v>1807.122000548209</v>
+      </c>
       <c r="D15" t="n">
         <v>1.52702e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1316.403</v>
       </c>
+      <c r="C16" t="n">
+        <v>1791.017991984264</v>
+      </c>
       <c r="D16" t="n">
         <v>1.5283e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1289.453</v>
       </c>
+      <c r="C17" t="n">
+        <v>1766.961556779421</v>
+      </c>
       <c r="D17" t="n">
         <v>1.5291e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1281.755</v>
       </c>
+      <c r="C18" t="n">
+        <v>1759.534437466741</v>
+      </c>
       <c r="D18" t="n">
         <v>1.52989e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1263.034</v>
       </c>
+      <c r="C19" t="n">
+        <v>1739.469696427149</v>
+      </c>
       <c r="D19" t="n">
         <v>1.53084e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1250.145</v>
       </c>
+      <c r="C20" t="n">
+        <v>1728.570823609823</v>
+      </c>
       <c r="D20" t="n">
         <v>1.53203e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1224.865</v>
       </c>
+      <c r="C21" t="n">
+        <v>1703.928394005184</v>
+      </c>
       <c r="D21" t="n">
         <v>1.5329e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1216.396</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1693.195496936511</v>
       </c>
       <c r="D22" t="n">
         <v>1.53389e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>1769.584</v>
       </c>
+      <c r="C2" t="n">
+        <v>2262.738091870229</v>
+      </c>
       <c r="D2" t="n">
         <v>1.53124e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>1645.954</v>
       </c>
+      <c r="C3" t="n">
+        <v>2112.263462720934</v>
+      </c>
       <c r="D3" t="n">
         <v>1.53789e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>1624.189</v>
       </c>
+      <c r="C4" t="n">
+        <v>2087.624413922089</v>
+      </c>
       <c r="D4" t="n">
         <v>1.53565e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>1611.416</v>
       </c>
+      <c r="C5" t="n">
+        <v>2073.806058224671</v>
+      </c>
       <c r="D5" t="n">
         <v>1.53249e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1572.867</v>
       </c>
+      <c r="C6" t="n">
+        <v>2040.107328380194</v>
+      </c>
       <c r="D6" t="n">
         <v>1.53002e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1571.369</v>
       </c>
+      <c r="C7" t="n">
+        <v>2035.181145226356</v>
+      </c>
       <c r="D7" t="n">
         <v>1.52852e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1540.72</v>
       </c>
+      <c r="C8" t="n">
+        <v>2011.046800636804</v>
+      </c>
       <c r="D8" t="n">
         <v>1.52785e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1523.677</v>
       </c>
+      <c r="C9" t="n">
+        <v>1987.89571211114</v>
+      </c>
       <c r="D9" t="n">
         <v>1.52729e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1503.217</v>
       </c>
+      <c r="C10" t="n">
+        <v>1970.143024573659</v>
+      </c>
       <c r="D10" t="n">
         <v>1.5272e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1481.863</v>
       </c>
+      <c r="C11" t="n">
+        <v>1947.790556592857</v>
+      </c>
       <c r="D11" t="n">
         <v>1.52684e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1465.444</v>
       </c>
+      <c r="C12" t="n">
+        <v>1930.763840768138</v>
+      </c>
       <c r="D12" t="n">
         <v>1.52707e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1445.193</v>
       </c>
+      <c r="C13" t="n">
+        <v>1914.066383190073</v>
+      </c>
       <c r="D13" t="n">
         <v>1.52718e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1425.42</v>
       </c>
+      <c r="C14" t="n">
+        <v>1894.698757104264</v>
+      </c>
       <c r="D14" t="n">
         <v>1.52771e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1404.177</v>
       </c>
+      <c r="C15" t="n">
+        <v>1877.640421006484</v>
+      </c>
       <c r="D15" t="n">
         <v>1.52781e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1390.899</v>
       </c>
+      <c r="C16" t="n">
+        <v>1859.594126002203</v>
+      </c>
       <c r="D16" t="n">
         <v>1.52811e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1376.801</v>
       </c>
+      <c r="C17" t="n">
+        <v>1846.023515008473</v>
+      </c>
       <c r="D17" t="n">
         <v>1.52868e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1351.382</v>
       </c>
+      <c r="C18" t="n">
+        <v>1823.966140580003</v>
+      </c>
       <c r="D18" t="n">
         <v>1.52882e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1338.642</v>
       </c>
+      <c r="C19" t="n">
+        <v>1808.763084296227</v>
+      </c>
       <c r="D19" t="n">
         <v>1.52934e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1312.019</v>
       </c>
+      <c r="C20" t="n">
+        <v>1786.019456461066</v>
+      </c>
       <c r="D20" t="n">
         <v>1.53015e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1291.17</v>
       </c>
+      <c r="C21" t="n">
+        <v>1764.566202062177</v>
+      </c>
       <c r="D21" t="n">
         <v>1.53017e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1281.491</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1755.989229737874</v>
       </c>
       <c r="D22" t="n">
         <v>1.53087e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2178.327</v>
       </c>
+      <c r="C2" t="n">
+        <v>2689.654986133477</v>
+      </c>
       <c r="D2" t="n">
         <v>1.5001e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>1900.605</v>
       </c>
+      <c r="C3" t="n">
+        <v>2342.428870516804</v>
+      </c>
       <c r="D3" t="n">
         <v>1.54464e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>1836.41</v>
       </c>
+      <c r="C4" t="n">
+        <v>2265.94818011531</v>
+      </c>
       <c r="D4" t="n">
         <v>1.54627e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1798.322</v>
       </c>
+      <c r="C5" t="n">
+        <v>2230.302704674209</v>
+      </c>
       <c r="D5" t="n">
         <v>1.54211e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1759.257</v>
       </c>
+      <c r="C6" t="n">
+        <v>2195.440386296954</v>
+      </c>
       <c r="D6" t="n">
         <v>1.54191e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1735.943</v>
       </c>
+      <c r="C7" t="n">
+        <v>2172.283088367635</v>
+      </c>
       <c r="D7" t="n">
         <v>1.54119e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1700.435</v>
       </c>
+      <c r="C8" t="n">
+        <v>2141.433676904085</v>
+      </c>
       <c r="D8" t="n">
         <v>1.54148e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1677.745</v>
       </c>
+      <c r="C9" t="n">
+        <v>2118.510979408547</v>
+      </c>
       <c r="D9" t="n">
         <v>1.54227e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1648.179</v>
       </c>
+      <c r="C10" t="n">
+        <v>2089.047040951454</v>
+      </c>
       <c r="D10" t="n">
         <v>1.54354e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1610.714</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2056.172090178296</v>
       </c>
       <c r="D11" t="n">
         <v>1.5438e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>1764.862</v>
       </c>
+      <c r="C2" t="n">
+        <v>2243.062355467591</v>
+      </c>
       <c r="D2" t="n">
         <v>1.55122e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1641.607</v>
       </c>
+      <c r="C3" t="n">
+        <v>2095.878806318231</v>
+      </c>
       <c r="D3" t="n">
         <v>1.54604e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1610.878</v>
       </c>
+      <c r="C4" t="n">
+        <v>2061.480079179276</v>
+      </c>
       <c r="D4" t="n">
         <v>1.5459e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1587.512</v>
       </c>
+      <c r="C5" t="n">
+        <v>2035.996601100511</v>
+      </c>
       <c r="D5" t="n">
         <v>1.54624e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1556.887</v>
       </c>
+      <c r="C6" t="n">
+        <v>2012.818832915482</v>
+      </c>
       <c r="D6" t="n">
         <v>1.54669e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1539.989</v>
       </c>
+      <c r="C7" t="n">
+        <v>1995.552711949931</v>
+      </c>
       <c r="D7" t="n">
         <v>1.54689e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1511.447</v>
       </c>
+      <c r="C8" t="n">
+        <v>1971.189198715282</v>
+      </c>
       <c r="D8" t="n">
         <v>1.54753e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1493.047</v>
       </c>
+      <c r="C9" t="n">
+        <v>1952.958203198017</v>
+      </c>
       <c r="D9" t="n">
         <v>1.54803e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1487.687</v>
       </c>
+      <c r="C10" t="n">
+        <v>1947.254830353564</v>
+      </c>
       <c r="D10" t="n">
         <v>1.54834e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1458.771</v>
       </c>
+      <c r="C11" t="n">
+        <v>1917.361988592903</v>
+      </c>
       <c r="D11" t="n">
         <v>1.5487e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1437.555</v>
       </c>
+      <c r="C12" t="n">
+        <v>1895.054777996552</v>
+      </c>
       <c r="D12" t="n">
         <v>1.54927e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1413.471</v>
       </c>
+      <c r="C13" t="n">
+        <v>1877.971467429573</v>
+      </c>
       <c r="D13" t="n">
         <v>1.54918e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1406.915</v>
       </c>
+      <c r="C14" t="n">
+        <v>1869.44774920784</v>
+      </c>
       <c r="D14" t="n">
         <v>1.54987e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1388.66</v>
       </c>
+      <c r="C15" t="n">
+        <v>1850.06970103604</v>
+      </c>
       <c r="D15" t="n">
         <v>1.55014e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1371.678</v>
       </c>
+      <c r="C16" t="n">
+        <v>1833.0086550681</v>
+      </c>
       <c r="D16" t="n">
         <v>1.55091e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1341.192</v>
       </c>
+      <c r="C17" t="n">
+        <v>1806.618713297441</v>
+      </c>
       <c r="D17" t="n">
         <v>1.55166e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1334.44</v>
       </c>
+      <c r="C18" t="n">
+        <v>1798.15757162344</v>
+      </c>
       <c r="D18" t="n">
         <v>1.5523e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1315.413</v>
       </c>
+      <c r="C19" t="n">
+        <v>1780.974598335715</v>
+      </c>
       <c r="D19" t="n">
         <v>1.5529e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1293.375</v>
       </c>
+      <c r="C20" t="n">
+        <v>1760.491722186731</v>
+      </c>
       <c r="D20" t="n">
         <v>1.55332e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1263.856</v>
       </c>
+      <c r="C21" t="n">
+        <v>1731.969120500866</v>
+      </c>
       <c r="D21" t="n">
         <v>1.55423e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1247.206</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1715.347998537714</v>
       </c>
       <c r="D22" t="n">
         <v>1.55471e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2122.309</v>
       </c>
+      <c r="C2" t="n">
+        <v>2616.956571393936</v>
+      </c>
       <c r="D2" t="n">
         <v>1.51828e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>1885.563</v>
       </c>
+      <c r="C3" t="n">
+        <v>2331.043774954389</v>
+      </c>
       <c r="D3" t="n">
         <v>1.5463e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>1833.062</v>
       </c>
+      <c r="C4" t="n">
+        <v>2270.118088728216</v>
+      </c>
       <c r="D4" t="n">
         <v>1.54451e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1798.479</v>
       </c>
+      <c r="C5" t="n">
+        <v>2235.312360101401</v>
+      </c>
       <c r="D5" t="n">
         <v>1.53886e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1755.353</v>
       </c>
+      <c r="C6" t="n">
+        <v>2198.090228887604</v>
+      </c>
       <c r="D6" t="n">
         <v>1.54082e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1744.804</v>
       </c>
+      <c r="C7" t="n">
+        <v>2180.008815068026</v>
+      </c>
       <c r="D7" t="n">
         <v>1.54129e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1720.706</v>
       </c>
+      <c r="C8" t="n">
+        <v>2159.781755177186</v>
+      </c>
       <c r="D8" t="n">
         <v>1.54278e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1678.333</v>
       </c>
+      <c r="C9" t="n">
+        <v>2121.453862826894</v>
+      </c>
       <c r="D9" t="n">
         <v>1.54435e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1656.884</v>
       </c>
+      <c r="C10" t="n">
+        <v>2096.159086068368</v>
+      </c>
       <c r="D10" t="n">
         <v>1.54613e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1638.843</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2076.26438431242</v>
       </c>
       <c r="D11" t="n">
         <v>1.54794e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>1718.342</v>
       </c>
+      <c r="C2" t="n">
+        <v>2190.631368218961</v>
+      </c>
       <c r="D2" t="n">
         <v>1.55451e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1610.434</v>
       </c>
+      <c r="C3" t="n">
+        <v>2067.400184855127</v>
+      </c>
       <c r="D3" t="n">
         <v>1.54978e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>1592.685</v>
       </c>
+      <c r="C4" t="n">
+        <v>2040.721803632413</v>
+      </c>
       <c r="D4" t="n">
         <v>1.54721e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1556.143</v>
       </c>
+      <c r="C5" t="n">
+        <v>2010.052384700257</v>
+      </c>
       <c r="D5" t="n">
         <v>1.54876e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1535.808</v>
       </c>
+      <c r="C6" t="n">
+        <v>1991.420759334986</v>
+      </c>
       <c r="D6" t="n">
         <v>1.55017e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1514.839</v>
       </c>
+      <c r="C7" t="n">
+        <v>1971.270488283465</v>
+      </c>
       <c r="D7" t="n">
         <v>1.55111e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1506.431</v>
       </c>
+      <c r="C8" t="n">
+        <v>1963.008169882385</v>
+      </c>
       <c r="D8" t="n">
         <v>1.55234e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1483.257</v>
       </c>
+      <c r="C9" t="n">
+        <v>1939.655064582159</v>
+      </c>
       <c r="D9" t="n">
         <v>1.55307e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1454.908</v>
       </c>
+      <c r="C10" t="n">
+        <v>1912.7565124483</v>
+      </c>
       <c r="D10" t="n">
         <v>1.55378e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1434.402</v>
       </c>
+      <c r="C11" t="n">
+        <v>1896.304374829477</v>
+      </c>
       <c r="D11" t="n">
         <v>1.55444e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1417.292</v>
       </c>
+      <c r="C12" t="n">
+        <v>1878.856303721721</v>
+      </c>
       <c r="D12" t="n">
         <v>1.55496e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1404.086</v>
       </c>
+      <c r="C13" t="n">
+        <v>1862.928031477302</v>
+      </c>
       <c r="D13" t="n">
         <v>1.55583e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1389.497</v>
       </c>
+      <c r="C14" t="n">
+        <v>1850.571773580557</v>
+      </c>
       <c r="D14" t="n">
         <v>1.55627e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1361.281</v>
       </c>
+      <c r="C15" t="n">
+        <v>1825.082549018697</v>
+      </c>
       <c r="D15" t="n">
         <v>1.55733e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1348.774</v>
       </c>
+      <c r="C16" t="n">
+        <v>1812.414525812664</v>
+      </c>
       <c r="D16" t="n">
         <v>1.55792e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1324.518</v>
       </c>
+      <c r="C17" t="n">
+        <v>1785.512943428149</v>
+      </c>
       <c r="D17" t="n">
         <v>1.55865e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1321.127</v>
       </c>
+      <c r="C18" t="n">
+        <v>1783.267337343021</v>
+      </c>
       <c r="D18" t="n">
         <v>1.55936e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1298.433</v>
       </c>
+      <c r="C19" t="n">
+        <v>1760.818288315126</v>
+      </c>
       <c r="D19" t="n">
         <v>1.55983e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1286.323</v>
       </c>
+      <c r="C20" t="n">
+        <v>1749.012051627349</v>
+      </c>
       <c r="D20" t="n">
         <v>1.56098e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1261.093</v>
       </c>
+      <c r="C21" t="n">
+        <v>1722.037425364234</v>
+      </c>
       <c r="D21" t="n">
         <v>1.56129e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1249.709</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1711.666902874609</v>
       </c>
       <c r="D22" t="n">
         <v>1.56205e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>2088.844</v>
       </c>
+      <c r="C2" t="n">
+        <v>2633.053789694123</v>
+      </c>
       <c r="D2" t="n">
         <v>1.50818e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>1829.747</v>
       </c>
+      <c r="C3" t="n">
+        <v>2289.348152473246</v>
+      </c>
       <c r="D3" t="n">
         <v>1.55608e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1760.926</v>
       </c>
+      <c r="C4" t="n">
+        <v>2212.767442393761</v>
+      </c>
       <c r="D4" t="n">
         <v>1.55542e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1727.173</v>
       </c>
+      <c r="C5" t="n">
+        <v>2177.623793060864</v>
+      </c>
       <c r="D5" t="n">
         <v>1.55174e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1702.897</v>
       </c>
+      <c r="C6" t="n">
+        <v>2155.393993030149</v>
+      </c>
       <c r="D6" t="n">
         <v>1.5523e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1673.924</v>
       </c>
+      <c r="C7" t="n">
+        <v>2124.142922228038</v>
+      </c>
       <c r="D7" t="n">
         <v>1.5533e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1653.709</v>
       </c>
+      <c r="C8" t="n">
+        <v>2103.249614811314</v>
+      </c>
       <c r="D8" t="n">
         <v>1.55459e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1616.318</v>
       </c>
+      <c r="C9" t="n">
+        <v>2066.155298666802</v>
+      </c>
       <c r="D9" t="n">
         <v>1.55649e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1582.14</v>
       </c>
+      <c r="C10" t="n">
+        <v>2036.559320545551</v>
+      </c>
       <c r="D10" t="n">
         <v>1.55979e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1552.786</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2009.59247565715</v>
       </c>
       <c r="D11" t="n">
         <v>1.56226e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>1679.799</v>
       </c>
+      <c r="C2" t="n">
+        <v>2168.33062458162</v>
+      </c>
       <c r="D2" t="n">
         <v>1.57138e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1600.857</v>
       </c>
+      <c r="C3" t="n">
+        <v>2065.04777400224</v>
+      </c>
       <c r="D3" t="n">
         <v>1.56059e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1556.955</v>
       </c>
+      <c r="C4" t="n">
+        <v>2021.317409809695</v>
+      </c>
       <c r="D4" t="n">
         <v>1.55947e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1547.604</v>
       </c>
+      <c r="C5" t="n">
+        <v>2008.56620585737</v>
+      </c>
       <c r="D5" t="n">
         <v>1.56151e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1528.567</v>
       </c>
+      <c r="C6" t="n">
+        <v>1991.012064699562</v>
+      </c>
       <c r="D6" t="n">
         <v>1.56145e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1502.115</v>
       </c>
+      <c r="C7" t="n">
+        <v>1966.90296193571</v>
+      </c>
       <c r="D7" t="n">
         <v>1.56295e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1476.099</v>
       </c>
+      <c r="C8" t="n">
+        <v>1941.03170615722</v>
+      </c>
       <c r="D8" t="n">
         <v>1.56656e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1461.996</v>
       </c>
+      <c r="C9" t="n">
+        <v>1929.087723729359</v>
+      </c>
       <c r="D9" t="n">
         <v>1.56748e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1448.296</v>
       </c>
+      <c r="C10" t="n">
+        <v>1915.73710368412</v>
+      </c>
       <c r="D10" t="n">
         <v>1.56694e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1428.58</v>
       </c>
+      <c r="C11" t="n">
+        <v>1899.061776511361</v>
+      </c>
       <c r="D11" t="n">
         <v>1.56884e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1400.32</v>
       </c>
+      <c r="C12" t="n">
+        <v>1873.796152743545</v>
+      </c>
       <c r="D12" t="n">
         <v>1.56939e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1393.618</v>
       </c>
+      <c r="C13" t="n">
+        <v>1861.67534642676</v>
+      </c>
       <c r="D13" t="n">
         <v>1.57091e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1372.41</v>
       </c>
+      <c r="C14" t="n">
+        <v>1844.210725582781</v>
+      </c>
       <c r="D14" t="n">
         <v>1.5723e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1355.007</v>
       </c>
+      <c r="C15" t="n">
+        <v>1826.978643687235</v>
+      </c>
       <c r="D15" t="n">
         <v>1.57241e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1334.625</v>
       </c>
+      <c r="C16" t="n">
+        <v>1809.301315417756</v>
+      </c>
       <c r="D16" t="n">
         <v>1.57271e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1314.383</v>
       </c>
+      <c r="C17" t="n">
+        <v>1788.015939176099</v>
+      </c>
       <c r="D17" t="n">
         <v>1.57264e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1303.558</v>
       </c>
+      <c r="C18" t="n">
+        <v>1774.506481096019</v>
+      </c>
       <c r="D18" t="n">
         <v>1.57417e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1286.945</v>
       </c>
+      <c r="C19" t="n">
+        <v>1763.651387473071</v>
+      </c>
       <c r="D19" t="n">
         <v>1.57495e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1267.219</v>
       </c>
+      <c r="C20" t="n">
+        <v>1740.70156899483</v>
+      </c>
       <c r="D20" t="n">
         <v>1.57697e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1246.586</v>
       </c>
+      <c r="C21" t="n">
+        <v>1726.086119674266</v>
+      </c>
       <c r="D21" t="n">
         <v>1.57805e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1220.686</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1698.004922464293</v>
       </c>
       <c r="D22" t="n">
         <v>1.57798e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>1656.272</v>
       </c>
+      <c r="C2" t="n">
+        <v>2266.624129783494</v>
+      </c>
       <c r="D2" t="n">
         <v>1.55519e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1418.672</v>
       </c>
+      <c r="C3" t="n">
+        <v>1923.060824157982</v>
+      </c>
       <c r="D3" t="n">
         <v>1.57788e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1354.417</v>
       </c>
+      <c r="C4" t="n">
+        <v>1847.932409335374</v>
+      </c>
       <c r="D4" t="n">
         <v>1.5718e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1320.446</v>
       </c>
+      <c r="C5" t="n">
+        <v>1812.26646507746</v>
+      </c>
       <c r="D5" t="n">
         <v>1.56788e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1280.727</v>
       </c>
+      <c r="C6" t="n">
+        <v>1779.292269399794</v>
+      </c>
       <c r="D6" t="n">
         <v>1.56482e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1258.651</v>
       </c>
+      <c r="C7" t="n">
+        <v>1759.201184789707</v>
+      </c>
       <c r="D7" t="n">
         <v>1.56741e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1237.212</v>
       </c>
+      <c r="C8" t="n">
+        <v>1739.493066753244</v>
+      </c>
       <c r="D8" t="n">
         <v>1.56929e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>1210.55</v>
       </c>
+      <c r="C9" t="n">
+        <v>1716.475086994664</v>
+      </c>
       <c r="D9" t="n">
         <v>1.57095e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>1190.579</v>
       </c>
+      <c r="C10" t="n">
+        <v>1693.044736622755</v>
+      </c>
       <c r="D10" t="n">
         <v>1.57463e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>1163.373</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1670.918211402351</v>
       </c>
       <c r="D11" t="n">
         <v>1.57704e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
@@ -565,7 +565,7 @@
         <v>1852.065</v>
       </c>
       <c r="C2" t="n">
-        <v>2330.528909500215</v>
+        <v>938.3297860055416</v>
       </c>
       <c r="D2" t="n">
         <v>1.57401e-07</v>
@@ -598,16 +598,13 @@
         <v>-28201.09178890567</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.056416622690032e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2581.254761896013</v>
+        <v>340.9243250089311</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000016756e-08</v>
+        <v>7.426702913081527e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8242676901990474</v>
+        <v>0.9995956302782112</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>1740.486</v>
       </c>
       <c r="C3" t="n">
-        <v>2201.65235182682</v>
+        <v>863.0523785177672</v>
       </c>
       <c r="D3" t="n">
         <v>1.56412e-07</v>
@@ -651,16 +648,13 @@
         <v>-31360.18726880851</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.112707972135273e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2476.106213132825</v>
+        <v>410.0745255075796</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>8.972508901908877e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8241254196300632</v>
+        <v>0.9957221918538069</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>1694.133</v>
       </c>
       <c r="C4" t="n">
-        <v>2158.275679832005</v>
+        <v>836.2112852822037</v>
       </c>
       <c r="D4" t="n">
         <v>1.55721e-07</v>
@@ -704,16 +698,13 @@
         <v>-31127.173971162</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.815855118874455e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2439.113361443799</v>
+        <v>419.2858317209763</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>9.130945426556304e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8237063366450689</v>
+        <v>0.9965424696724984</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>1680.005</v>
       </c>
       <c r="C5" t="n">
-        <v>2145.785490304964</v>
+        <v>815.8921659391742</v>
       </c>
       <c r="D5" t="n">
         <v>1.55024e-07</v>
@@ -757,16 +748,13 @@
         <v>-35125.19756241179</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.63302351941651e-11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2409.721247893156</v>
+        <v>454.9786682186835</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>1.614267423191809e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8234555665830496</v>
+        <v>0.9713503980061718</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>1655.06</v>
       </c>
       <c r="C6" t="n">
-        <v>2123.170936610426</v>
+        <v>799.9307603818058</v>
       </c>
       <c r="D6" t="n">
         <v>1.54605e-07</v>
@@ -810,16 +798,13 @@
         <v>-35969.18841330808</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.488599732128164e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2379.388754172694</v>
+        <v>450.7856778393001</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000001406e-08</v>
+        <v>1.291749214016228e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8234316890880138</v>
+        <v>0.9876541106111288</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>1609.273</v>
       </c>
       <c r="C7" t="n">
-        <v>2081.340594142706</v>
+        <v>785.5764115918989</v>
       </c>
       <c r="D7" t="n">
         <v>1.5422e-07</v>
@@ -863,16 +848,13 @@
         <v>-32754.61125789627</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.765633490352265e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2348.738601048445</v>
+        <v>439.450098003427</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000069956e-08</v>
+        <v>1.194719832636508e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8235496976852456</v>
+        <v>0.992435472619883</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>1589.43</v>
       </c>
       <c r="C8" t="n">
-        <v>2063.265496734332</v>
+        <v>771.4254296107749</v>
       </c>
       <c r="D8" t="n">
         <v>1.53894e-07</v>
@@ -916,16 +898,13 @@
         <v>-34622.08000848163</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.956228576195496e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2315.924558131071</v>
+        <v>449.6820241540568</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000019195e-08</v>
+        <v>9.983593538559728e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8238142756687453</v>
+        <v>0.9999482227088174</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +915,7 @@
         <v>1570.141</v>
       </c>
       <c r="C9" t="n">
-        <v>2043.954931825243</v>
+        <v>759.1986955223941</v>
       </c>
       <c r="D9" t="n">
         <v>1.53697e-07</v>
@@ -969,16 +948,13 @@
         <v>-36377.15682085705</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.814563337053614e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2285.518688244928</v>
+        <v>471.0906204643708</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000029614e-08</v>
+        <v>1.045235821661902e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8241104811090402</v>
+        <v>0.9996988247351124</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +965,7 @@
         <v>1549.192</v>
       </c>
       <c r="C10" t="n">
-        <v>2021.428335313965</v>
+        <v>748.0419529915692</v>
       </c>
       <c r="D10" t="n">
         <v>1.53505e-07</v>
@@ -1022,16 +998,13 @@
         <v>-36705.94919155094</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23578224501478e-07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2256.066654033975</v>
+        <v>473.4954488129835</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000441e-08</v>
+        <v>1.140102806073937e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8244502093963471</v>
+        <v>0.9991586630668612</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1015,7 @@
         <v>1520.05</v>
       </c>
       <c r="C11" t="n">
-        <v>1994.102542632603</v>
+        <v>737.861190095428</v>
       </c>
       <c r="D11" t="n">
         <v>1.53331e-07</v>
@@ -1075,16 +1048,13 @@
         <v>-36054.00851363573</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.74785093408461e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2228.394763180187</v>
+        <v>483.6008100568645</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000217e-08</v>
+        <v>1.197654579043478e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8247941255967071</v>
+        <v>0.9935019011951741</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1211,7 @@
         <v>1688.479</v>
       </c>
       <c r="C2" t="n">
-        <v>2179.905642016238</v>
+        <v>831.4235414345426</v>
       </c>
       <c r="D2" t="n">
         <v>1.50004e-07</v>
@@ -1274,16 +1244,13 @@
         <v>-28991.16153508377</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.510135070532941e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2395.134252965344</v>
+        <v>415.0889266524691</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000001778e-08</v>
+        <v>1.459404910101108e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8265850089570875</v>
+        <v>0.973257443539572</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>1595.146</v>
       </c>
       <c r="C3" t="n">
-        <v>2057.176124999146</v>
+        <v>785.6407161889139</v>
       </c>
       <c r="D3" t="n">
         <v>1.51102e-07</v>
@@ -1327,16 +1294,13 @@
         <v>-30954.55371271355</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.79831657726653e-07</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2292.798956728872</v>
+        <v>430.1592713774823</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000024504e-08</v>
+        <v>1.12633364444139e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8267268638347558</v>
+        <v>0.9913530006041411</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1311,7 @@
         <v>1558.569</v>
       </c>
       <c r="C4" t="n">
-        <v>2021.406381895755</v>
+        <v>769.1607083919117</v>
       </c>
       <c r="D4" t="n">
         <v>1.51466e-07</v>
@@ -1380,16 +1344,13 @@
         <v>-31391.21171684274</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.991055649108947e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2256.385991460089</v>
+        <v>423.2054668031598</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000051e-08</v>
+        <v>1.252357670288462e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8266248727835603</v>
+        <v>0.9901710483650886</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1361,7 @@
         <v>1530.965</v>
       </c>
       <c r="C5" t="n">
-        <v>1997.144161002714</v>
+        <v>755.9930144095107</v>
       </c>
       <c r="D5" t="n">
         <v>1.5165e-07</v>
@@ -1433,16 +1394,13 @@
         <v>-30736.7377805057</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.850830035747453e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2229.873538728859</v>
+        <v>439.6472263638547</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000080165e-08</v>
+        <v>1.141375092828346e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8266088071396418</v>
+        <v>0.9919712182849472</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1411,7 @@
         <v>1506.139</v>
       </c>
       <c r="C6" t="n">
-        <v>1970.867818627416</v>
+        <v>746.8223258420535</v>
       </c>
       <c r="D6" t="n">
         <v>1.51811e-07</v>
@@ -1486,16 +1444,13 @@
         <v>-29952.36625244576</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.844789500519175e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2202.272950076202</v>
+        <v>448.4067735425489</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000004047e-08</v>
+        <v>1.192081228661964e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8267189876327405</v>
+        <v>0.9926820565422769</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1461,7 @@
         <v>1483.101</v>
       </c>
       <c r="C7" t="n">
-        <v>1951.435631213821</v>
+        <v>735.0354109048349</v>
       </c>
       <c r="D7" t="n">
         <v>1.51943e-07</v>
@@ -1539,16 +1494,13 @@
         <v>-30162.5259755867</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.52258029742102e-07</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2175.928952545116</v>
+        <v>431.584805533605</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.046374258886767e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8268609504714997</v>
+        <v>0.9993288387040341</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1511,7 @@
         <v>1464.335</v>
       </c>
       <c r="C8" t="n">
-        <v>1931.701820055622</v>
+        <v>725.9420587365572</v>
       </c>
       <c r="D8" t="n">
         <v>1.5207e-07</v>
@@ -1592,16 +1544,13 @@
         <v>-30478.48684392136</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.485356779899677e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2150.672623079922</v>
+        <v>427.0472358519696</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000008346e-08</v>
+        <v>1.304670251903687e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8270277682538686</v>
+        <v>0.9922736151848796</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1561,7 @@
         <v>1434.761</v>
       </c>
       <c r="C9" t="n">
-        <v>1908.893095007386</v>
+        <v>716.2289890305988</v>
       </c>
       <c r="D9" t="n">
         <v>1.5216e-07</v>
@@ -1645,16 +1594,13 @@
         <v>-29548.28009746718</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.025157866703415e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2126.060245595298</v>
+        <v>449.2044934392667</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.196246076932783e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8272128362855552</v>
+        <v>0.9928575432478317</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1611,7 @@
         <v>1425.297</v>
       </c>
       <c r="C10" t="n">
-        <v>1899.004457950135</v>
+        <v>707.1830627196978</v>
       </c>
       <c r="D10" t="n">
         <v>1.52248e-07</v>
@@ -1698,16 +1644,13 @@
         <v>-31727.57024208668</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.363936699890571e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2102.50280066501</v>
+        <v>497.4732069823108</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>2.688045698698489e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8274422784139749</v>
+        <v>0.9429859026884023</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1661,7 @@
         <v>1401.616</v>
       </c>
       <c r="C11" t="n">
-        <v>1873.430404927851</v>
+        <v>699.9777065802062</v>
       </c>
       <c r="D11" t="n">
         <v>1.52341e-07</v>
@@ -1751,16 +1694,13 @@
         <v>-30061.4637081375</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.247260777176046e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2079.622519861135</v>
+        <v>460.1896014456175</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000136e-08</v>
+        <v>1.205101973614942e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8276841655474365</v>
+        <v>0.9922058664239661</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1711,7 @@
         <v>1392.639</v>
       </c>
       <c r="C12" t="n">
-        <v>1865.63397296379</v>
+        <v>693.2167979702575</v>
       </c>
       <c r="D12" t="n">
         <v>1.52439e-07</v>
@@ -1804,16 +1744,13 @@
         <v>-32328.5981546775</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.956810348397113e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2057.309668834576</v>
+        <v>453.7250243068431</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000007325e-08</v>
+        <v>1.50890208373326e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8279487310879348</v>
+        <v>0.9849598213390245</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1761,7 @@
         <v>1360.371</v>
       </c>
       <c r="C13" t="n">
-        <v>1836.345176859164</v>
+        <v>684.6518851110208</v>
       </c>
       <c r="D13" t="n">
         <v>1.52549e-07</v>
@@ -1857,16 +1794,13 @@
         <v>-29390.55095881574</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.863094206737142e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2035.023675134674</v>
+        <v>444.793593984823</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000015e-08</v>
+        <v>1.143252709334901e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8282284202666524</v>
+        <v>0.9979196434174308</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1811,7 @@
         <v>1348.013</v>
       </c>
       <c r="C14" t="n">
-        <v>1824.522802296413</v>
+        <v>676.2437916633896</v>
       </c>
       <c r="D14" t="n">
         <v>1.52653e-07</v>
@@ -1910,16 +1844,13 @@
         <v>-30458.10196291071</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.533076738296481e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2012.9000484975</v>
+        <v>457.9523478307871</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.20595102376599e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8285339454945814</v>
+        <v>0.9992683915865924</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1861,7 @@
         <v>1333.18</v>
       </c>
       <c r="C15" t="n">
-        <v>1807.122000548209</v>
+        <v>669.218742690853</v>
       </c>
       <c r="D15" t="n">
         <v>1.52702e-07</v>
@@ -1963,16 +1894,13 @@
         <v>-30643.92707375035</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.423201680666198e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1991.069193723529</v>
+        <v>463.5570912801267</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.00000000000358e-08</v>
+        <v>1.301661794910811e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8288536447033206</v>
+        <v>0.9944077426894324</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1911,7 @@
         <v>1316.403</v>
       </c>
       <c r="C16" t="n">
-        <v>1791.017991984264</v>
+        <v>660.3548738428585</v>
       </c>
       <c r="D16" t="n">
         <v>1.5283e-07</v>
@@ -2016,16 +1944,13 @@
         <v>-31012.74184024507</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.717588606704249e-11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1969.449034051546</v>
+        <v>460.0970784956578</v>
       </c>
       <c r="AA16" t="n">
-        <v>1e-08</v>
+        <v>1.2505130723182e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8291749244229223</v>
+        <v>0.9991672991738348</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1961,7 @@
         <v>1289.453</v>
       </c>
       <c r="C17" t="n">
-        <v>1766.961556779421</v>
+        <v>653.9255341206592</v>
       </c>
       <c r="D17" t="n">
         <v>1.5291e-07</v>
@@ -2069,16 +1994,13 @@
         <v>-29230.51674900182</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.576323773700991e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1948.413987382764</v>
+        <v>450.9928928221051</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.602026424554346e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.829507767945693</v>
+        <v>0.9816042123207244</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2011,7 @@
         <v>1281.755</v>
       </c>
       <c r="C18" t="n">
-        <v>1759.534437466741</v>
+        <v>647.4462029502265</v>
       </c>
       <c r="D18" t="n">
         <v>1.52989e-07</v>
@@ -2122,16 +2044,13 @@
         <v>-31257.84190078008</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.013589953556943e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1927.069102713171</v>
+        <v>439.7606061310655</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000001457e-08</v>
+        <v>1.605132449621161e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8298581761819848</v>
+        <v>0.9868117209386786</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2061,7 @@
         <v>1263.034</v>
       </c>
       <c r="C19" t="n">
-        <v>1739.469696427149</v>
+        <v>640.9269595184348</v>
       </c>
       <c r="D19" t="n">
         <v>1.53084e-07</v>
@@ -2175,16 +2094,13 @@
         <v>-30525.32398314323</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.953048004923163e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1905.719562304891</v>
+        <v>452.7434029114725</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.0000000000009e-08</v>
+        <v>1.833662057743371e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8302197522919494</v>
+        <v>0.9762803004648369</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2111,7 @@
         <v>1250.145</v>
       </c>
       <c r="C20" t="n">
-        <v>1728.570823609823</v>
+        <v>632.2715153704669</v>
       </c>
       <c r="D20" t="n">
         <v>1.53203e-07</v>
@@ -2228,16 +2144,13 @@
         <v>-31775.45002257308</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.841031908188941e-11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1884.579597572348</v>
+        <v>468.687135836435</v>
       </c>
       <c r="AA20" t="n">
-        <v>1e-08</v>
+        <v>1.875476329540999e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8305808911348863</v>
+        <v>0.9765457140926546</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2161,7 @@
         <v>1224.865</v>
       </c>
       <c r="C21" t="n">
-        <v>1703.928394005184</v>
+        <v>627.0229924808326</v>
       </c>
       <c r="D21" t="n">
         <v>1.5329e-07</v>
@@ -2281,16 +2194,13 @@
         <v>-29922.06724334456</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.242137843961746e-07</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1863.316605824914</v>
+        <v>437.491137021729</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000021e-08</v>
+        <v>1.276019722756425e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8309558658949489</v>
+        <v>0.9998858559887627</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2211,7 @@
         <v>1216.396</v>
       </c>
       <c r="C22" t="n">
-        <v>1693.195496936511</v>
+        <v>621.9966708097581</v>
       </c>
       <c r="D22" t="n">
         <v>1.53389e-07</v>
@@ -2334,16 +2244,13 @@
         <v>-31136.93196388157</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.494309733862835e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1842.231028052715</v>
+        <v>481.4749228136113</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000012e-08</v>
+        <v>4.592064397083395e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8313228917593165</v>
+        <v>0.9148220850890496</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2407,7 @@
         <v>1769.584</v>
       </c>
       <c r="C2" t="n">
-        <v>2262.738091870229</v>
+        <v>869.9040460540422</v>
       </c>
       <c r="D2" t="n">
         <v>1.53124e-07</v>
@@ -2533,16 +2440,13 @@
         <v>-30166.94007316015</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.05281980478126e-13</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2490.927275342699</v>
+        <v>395.045621792841</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000011e-08</v>
+        <v>8.607123201472872e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8251954356590534</v>
+        <v>0.9949079241645444</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2457,7 @@
         <v>1645.954</v>
       </c>
       <c r="C3" t="n">
-        <v>2112.263462720934</v>
+        <v>806.5290969650316</v>
       </c>
       <c r="D3" t="n">
         <v>1.53789e-07</v>
@@ -2586,16 +2490,13 @@
         <v>-30519.50844804617</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.660224636532493e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2379.443356561666</v>
+        <v>433.789093666688</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.00000000000403e-08</v>
+        <v>1.322545337056137e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8252864880973554</v>
+        <v>0.9848462162184136</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2507,7 @@
         <v>1624.189</v>
       </c>
       <c r="C4" t="n">
-        <v>2087.624413922089</v>
+        <v>786.2730546003091</v>
       </c>
       <c r="D4" t="n">
         <v>1.53565e-07</v>
@@ -2639,16 +2540,13 @@
         <v>-33959.31579090837</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.182037553156567e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2345.279277117374</v>
+        <v>446.0742136095402</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000266e-08</v>
+        <v>1.206512106095153e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8250530874427202</v>
+        <v>0.9894720342578648</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2557,7 @@
         <v>1611.416</v>
       </c>
       <c r="C5" t="n">
-        <v>2073.806058224671</v>
+        <v>772.9990174011846</v>
       </c>
       <c r="D5" t="n">
         <v>1.53249e-07</v>
@@ -2692,16 +2590,13 @@
         <v>-36290.28550049723</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.514443058564051e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2320.684009820747</v>
+        <v>464.2632693777193</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000171e-08</v>
+        <v>1.157338529821252e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8249425961151271</v>
+        <v>0.9942270491191884</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2607,7 @@
         <v>1572.867</v>
       </c>
       <c r="C6" t="n">
-        <v>2040.107328380194</v>
+        <v>762.256571261373</v>
       </c>
       <c r="D6" t="n">
         <v>1.53002e-07</v>
@@ -2745,16 +2640,13 @@
         <v>-32714.96106571314</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.519367777101565e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2296.347114203406</v>
+        <v>532.2083320372215</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000005195e-08</v>
+        <v>4.285955723677508e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8249900597356645</v>
+        <v>0.9107383557088209</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2657,7 @@
         <v>1571.369</v>
       </c>
       <c r="C7" t="n">
-        <v>2035.181145226356</v>
+        <v>752.0075568148492</v>
       </c>
       <c r="D7" t="n">
         <v>1.52852e-07</v>
@@ -2798,16 +2690,13 @@
         <v>-37110.33527682364</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.215015646185163e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2271.132823863362</v>
+        <v>468.0561911947859</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000486655e-08</v>
+        <v>1.094719250043644e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8251202635819013</v>
+        <v>0.9970879044312784</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2707,7 @@
         <v>1540.72</v>
       </c>
       <c r="C8" t="n">
-        <v>2011.046800636804</v>
+        <v>741.7245531665563</v>
       </c>
       <c r="D8" t="n">
         <v>1.52785e-07</v>
@@ -2851,16 +2740,13 @@
         <v>-35776.91518777932</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.521091378039949e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2246.079576360868</v>
+        <v>473.5266263084546</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000008e-08</v>
+        <v>1.184807498777201e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8252998589228745</v>
+        <v>0.9940534825143444</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2757,7 @@
         <v>1523.677</v>
       </c>
       <c r="C9" t="n">
-        <v>1987.89571211114</v>
+        <v>739.5030697448841</v>
       </c>
       <c r="D9" t="n">
         <v>1.52729e-07</v>
@@ -2904,16 +2790,13 @@
         <v>-35000.37010581527</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.685100697067799e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2222.159574987513</v>
+        <v>462.2507095106949</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.381520591074743e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8254979992962646</v>
+        <v>0.9877972350523354</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2807,7 @@
         <v>1503.217</v>
       </c>
       <c r="C10" t="n">
-        <v>1970.143024573659</v>
+        <v>729.5326820986685</v>
       </c>
       <c r="D10" t="n">
         <v>1.5272e-07</v>
@@ -2957,16 +2840,13 @@
         <v>-35287.14975881372</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.090302632229841e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2199.120134081117</v>
+        <v>476.2100026149653</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000109261e-08</v>
+        <v>1.281593183364249e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8257033486524447</v>
+        <v>0.9907747676032437</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2857,7 @@
         <v>1481.863</v>
       </c>
       <c r="C11" t="n">
-        <v>1947.790556592857</v>
+        <v>721.0137156181147</v>
       </c>
       <c r="D11" t="n">
         <v>1.52684e-07</v>
@@ -3010,16 +2890,13 @@
         <v>-34407.43105320478</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.937229951758916e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2176.092588861285</v>
+        <v>478.9816503486248</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000429e-08</v>
+        <v>1.232624493317763e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8259341023867339</v>
+        <v>0.9916803307908364</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2907,7 @@
         <v>1465.444</v>
       </c>
       <c r="C12" t="n">
-        <v>1930.763840768138</v>
+        <v>712.5437815011315</v>
       </c>
       <c r="D12" t="n">
         <v>1.52707e-07</v>
@@ -3063,16 +2940,13 @@
         <v>-34705.3107485142</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.499255348249995e-12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2153.305815194798</v>
+        <v>473.8997797145327</v>
       </c>
       <c r="AA12" t="n">
-        <v>1e-08</v>
+        <v>1.196497124321134e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8262020762927021</v>
+        <v>0.9992327296227989</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2957,7 @@
         <v>1445.193</v>
       </c>
       <c r="C13" t="n">
-        <v>1914.066383190073</v>
+        <v>705.2914780217393</v>
       </c>
       <c r="D13" t="n">
         <v>1.52718e-07</v>
@@ -3116,16 +2990,13 @@
         <v>-34809.40230175739</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.087622909754997e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2129.940765735583</v>
+        <v>466.0387417155439</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000122232e-08</v>
+        <v>1.106995796832994e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8264990874504575</v>
+        <v>0.999960204522956</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3007,7 @@
         <v>1425.42</v>
       </c>
       <c r="C14" t="n">
-        <v>1894.698757104264</v>
+        <v>696.7330969064384</v>
       </c>
       <c r="D14" t="n">
         <v>1.52771e-07</v>
@@ -3169,16 +3040,13 @@
         <v>-34976.81278903653</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.525177688158116e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2106.236350545985</v>
+        <v>444.6244633545149</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000006e-08</v>
+        <v>1.321017168727804e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8268283521545878</v>
+        <v>0.993821613093321</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3057,7 @@
         <v>1404.177</v>
       </c>
       <c r="C15" t="n">
-        <v>1877.640421006484</v>
+        <v>688.3052169705171</v>
       </c>
       <c r="D15" t="n">
         <v>1.52781e-07</v>
@@ -3222,16 +3090,13 @@
         <v>-35072.03224711869</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.664232797329004e-07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2082.413684566668</v>
+        <v>453.7119906600398</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000005796e-08</v>
+        <v>1.408723707790787e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8271788112347632</v>
+        <v>0.9882374681640889</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3107,7 @@
         <v>1390.899</v>
       </c>
       <c r="C16" t="n">
-        <v>1859.594126002203</v>
+        <v>682.4741832734843</v>
       </c>
       <c r="D16" t="n">
         <v>1.52811e-07</v>
@@ -3275,16 +3140,13 @@
         <v>-35328.71272590429</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.89096825964452e-11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2058.941304661459</v>
+        <v>469.1982748767684</v>
       </c>
       <c r="AA16" t="n">
-        <v>1e-08</v>
+        <v>1.651118908427148e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8275372123783906</v>
+        <v>0.9762855172281845</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3157,7 @@
         <v>1376.801</v>
       </c>
       <c r="C17" t="n">
-        <v>1846.023515008473</v>
+        <v>674.0833610450849</v>
       </c>
       <c r="D17" t="n">
         <v>1.52868e-07</v>
@@ -3328,16 +3190,13 @@
         <v>-36897.20660805568</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.978464390456257e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2035.344534759897</v>
+        <v>471.3296071668893</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000046e-08</v>
+        <v>1.198237878206786e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8278950204766552</v>
+        <v>0.9987720709963922</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3207,7 @@
         <v>1351.382</v>
       </c>
       <c r="C18" t="n">
-        <v>1823.966140580003</v>
+        <v>666.3669553619676</v>
       </c>
       <c r="D18" t="n">
         <v>1.52882e-07</v>
@@ -3381,16 +3240,13 @@
         <v>-35564.23592944665</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.284714122398459e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2012.017147002048</v>
+        <v>470.8224281492369</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000346e-08</v>
+        <v>1.22758312952349e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8282612677417099</v>
+        <v>0.9979659152637217</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3257,7 @@
         <v>1338.642</v>
       </c>
       <c r="C19" t="n">
-        <v>1808.763084296227</v>
+        <v>660.607668680163</v>
       </c>
       <c r="D19" t="n">
         <v>1.52934e-07</v>
@@ -3434,16 +3290,13 @@
         <v>-35864.19313921292</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.354485503458207e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1988.552696207287</v>
+        <v>465.6915927301571</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000003194e-08</v>
+        <v>1.236190818913747e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8286278357126966</v>
+        <v>0.9996080080475959</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3307,7 @@
         <v>1312.019</v>
       </c>
       <c r="C20" t="n">
-        <v>1786.019456461066</v>
+        <v>652.1104859330301</v>
       </c>
       <c r="D20" t="n">
         <v>1.53015e-07</v>
@@ -3487,16 +3340,13 @@
         <v>-34407.53095909335</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.139287850934626e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1964.995383232124</v>
+        <v>442.3747247576478</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000001523e-08</v>
+        <v>1.080346282109195e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8290005492378028</v>
+        <v>0.9999850663986865</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3357,7 @@
         <v>1291.17</v>
       </c>
       <c r="C21" t="n">
-        <v>1764.566202062177</v>
+        <v>645.1794393631928</v>
       </c>
       <c r="D21" t="n">
         <v>1.53017e-07</v>
@@ -3540,16 +3390,13 @@
         <v>-33569.69663751725</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.362127781428673e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1941.746070284501</v>
+        <v>447.4077886217331</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000026e-08</v>
+        <v>1.176646048604766e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8293730125661111</v>
+        <v>0.9992844004056024</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3407,7 @@
         <v>1281.491</v>
       </c>
       <c r="C22" t="n">
-        <v>1755.989229737874</v>
+        <v>639.1659952735016</v>
       </c>
       <c r="D22" t="n">
         <v>1.53087e-07</v>
@@ -3593,16 +3440,13 @@
         <v>-36339.8189413394</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.372464324196523e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1918.842308706892</v>
+        <v>474.0226521691518</v>
       </c>
       <c r="AA22" t="n">
-        <v>1e-08</v>
+        <v>1.701281129500041e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8297530188150996</v>
+        <v>0.9852740503399423</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3603,7 @@
         <v>2178.327</v>
       </c>
       <c r="C2" t="n">
-        <v>2689.654986133477</v>
+        <v>1399.276071845218</v>
       </c>
       <c r="D2" t="n">
         <v>1.5001e-07</v>
@@ -3792,16 +3636,13 @@
         <v>-24997.43137088413</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.303982630054166e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2909.818712444293</v>
+        <v>6.036390657834042</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000181e-08</v>
+        <v>1.686887814168767e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8258388708884479</v>
+        <v>0.9040977607609282</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3653,7 @@
         <v>1900.605</v>
       </c>
       <c r="C3" t="n">
-        <v>2342.428870516804</v>
+        <v>1006.015111570054</v>
       </c>
       <c r="D3" t="n">
         <v>1.54464e-07</v>
@@ -3845,16 +3686,13 @@
         <v>-27565.46982795976</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.027264422883348e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2638.38498157474</v>
+        <v>264.7550970373837</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>9.976729963501417e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8265687249403512</v>
+        <v>0.9805341742509953</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3703,7 @@
         <v>1836.41</v>
       </c>
       <c r="C4" t="n">
-        <v>2265.94818011531</v>
+        <v>909.0058010409224</v>
       </c>
       <c r="D4" t="n">
         <v>1.54627e-07</v>
@@ -3898,16 +3736,13 @@
         <v>-30145.25553207761</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.490016179154979e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2564.013292644723</v>
+        <v>352.1797390967625</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>7.962082092647653e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8265884527879066</v>
+        <v>0.9998342668906171</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3753,7 @@
         <v>1798.322</v>
       </c>
       <c r="C5" t="n">
-        <v>2230.302704674209</v>
+        <v>879.6061300638004</v>
       </c>
       <c r="D5" t="n">
         <v>1.54211e-07</v>
@@ -3951,16 +3786,13 @@
         <v>-31587.87185633738</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.144489126443623e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2521.660895132992</v>
+        <v>375.5126385857138</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000022e-08</v>
+        <v>1.058823643643899e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8265766186621232</v>
+        <v>0.9828371113546222</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3803,7 @@
         <v>1759.257</v>
       </c>
       <c r="C6" t="n">
-        <v>2195.440386296954</v>
+        <v>853.6735223957462</v>
       </c>
       <c r="D6" t="n">
         <v>1.54191e-07</v>
@@ -4004,16 +3836,13 @@
         <v>-31474.98355327969</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.548216533372171e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2483.543930865728</v>
+        <v>398.244271049706</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000003255e-08</v>
+        <v>1.347107798194449e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8266483033213513</v>
+        <v>0.9784274989170733</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3853,7 @@
         <v>1735.943</v>
       </c>
       <c r="C7" t="n">
-        <v>2172.283088367635</v>
+        <v>833.3397238433437</v>
       </c>
       <c r="D7" t="n">
         <v>1.54119e-07</v>
@@ -4057,16 +3886,13 @@
         <v>-33203.45057500096</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.732947559555632e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2446.986355741294</v>
+        <v>411.003200354112</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000745e-08</v>
+        <v>9.481399788303183e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8267952413704284</v>
+        <v>0.9945970854489743</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3903,7 @@
         <v>1700.435</v>
       </c>
       <c r="C8" t="n">
-        <v>2141.433676904085</v>
+        <v>817.0359831573629</v>
       </c>
       <c r="D8" t="n">
         <v>1.54148e-07</v>
@@ -4110,16 +3936,13 @@
         <v>-32524.18541169792</v>
       </c>
       <c r="Y8" t="n">
-        <v>55.32024370684625</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2423.477231855946</v>
+        <v>412.9211124323685</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.21800867779173e-08</v>
+        <v>9.965605989177344e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8153662182863143</v>
+        <v>0.9966596406795593</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3953,7 @@
         <v>1677.745</v>
       </c>
       <c r="C9" t="n">
-        <v>2118.510979408547</v>
+        <v>800.7483755778767</v>
       </c>
       <c r="D9" t="n">
         <v>1.54227e-07</v>
@@ -4163,16 +3986,13 @@
         <v>-34119.53825081394</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.279973392616429e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2374.879365483864</v>
+        <v>408.6724406610296</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000267e-08</v>
+        <v>9.224974774112335e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8271923041919251</v>
+        <v>0.9993512868646801</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4003,7 @@
         <v>1648.179</v>
       </c>
       <c r="C10" t="n">
-        <v>2089.047040951454</v>
+        <v>784.8916550616186</v>
       </c>
       <c r="D10" t="n">
         <v>1.54354e-07</v>
@@ -4216,16 +4036,13 @@
         <v>-34552.01601601497</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.131601412929603e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2340.505857145611</v>
+        <v>403.3771427192406</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000002425e-08</v>
+        <v>9.049010035262272e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8274572559379482</v>
+        <v>0.9998860127304122</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4053,7 @@
         <v>1610.714</v>
       </c>
       <c r="C11" t="n">
-        <v>2056.172090178296</v>
+        <v>773.522627544584</v>
       </c>
       <c r="D11" t="n">
         <v>1.5438e-07</v>
@@ -4269,16 +4086,13 @@
         <v>-32136.09250418279</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.417712274107404e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2307.848882026657</v>
+        <v>437.8847645827218</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.00000000000012e-08</v>
+        <v>1.118743352031218e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8277414423943498</v>
+        <v>0.9940775461044599</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4249,7 @@
         <v>1764.862</v>
       </c>
       <c r="C2" t="n">
-        <v>2243.062355467591</v>
+        <v>890.8948951288924</v>
       </c>
       <c r="D2" t="n">
         <v>1.55122e-07</v>
@@ -4468,16 +4282,13 @@
         <v>-27105.56415712392</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.447897582249577e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2459.372221786146</v>
+        <v>353.8208746323074</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000419e-08</v>
+        <v>9.648068333286722e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8269099999641284</v>
+        <v>0.984285139352159</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4299,7 @@
         <v>1641.607</v>
       </c>
       <c r="C3" t="n">
-        <v>2095.878806318231</v>
+        <v>812.2979820778069</v>
       </c>
       <c r="D3" t="n">
         <v>1.54604e-07</v>
@@ -4521,16 +4332,13 @@
         <v>-29385.84419624559</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.205559113675395e-07</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2348.770161627056</v>
+        <v>473.3269481529431</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000014e-08</v>
+        <v>2.768159923980736e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8271180947318536</v>
+        <v>0.9346579318123147</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4349,7 @@
         <v>1610.878</v>
       </c>
       <c r="C4" t="n">
-        <v>2061.480079179276</v>
+        <v>784.3648059121383</v>
       </c>
       <c r="D4" t="n">
         <v>1.5459e-07</v>
@@ -4574,16 +4382,13 @@
         <v>-31996.78182317718</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.485706429267026e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2308.411583632859</v>
+        <v>417.507109762123</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000015418e-08</v>
+        <v>1.015774503938006e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8270087841248112</v>
+        <v>0.9965165634214246</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4399,7 @@
         <v>1587.512</v>
       </c>
       <c r="C5" t="n">
-        <v>2035.996601100511</v>
+        <v>769.1264040133963</v>
       </c>
       <c r="D5" t="n">
         <v>1.54624e-07</v>
@@ -4627,16 +4432,13 @@
         <v>-32934.34229431956</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.632115304134711e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2279.438270186269</v>
+        <v>412.4845490041997</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000057924e-08</v>
+        <v>9.051768614901509e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8269396847626918</v>
+        <v>0.9993253211116451</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4449,7 @@
         <v>1556.887</v>
       </c>
       <c r="C6" t="n">
-        <v>2012.818832915482</v>
+        <v>756.9015712923816</v>
       </c>
       <c r="D6" t="n">
         <v>1.54669e-07</v>
@@ -4680,16 +4482,13 @@
         <v>-32047.95423730018</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.985211892199435e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2254.426849274328</v>
+        <v>439.1575069576135</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000274e-08</v>
+        <v>1.046355694563712e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.826894879562493</v>
+        <v>0.9996335264738108</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4499,7 @@
         <v>1539.989</v>
       </c>
       <c r="C7" t="n">
-        <v>1995.552711949931</v>
+        <v>747.3568989519499</v>
       </c>
       <c r="D7" t="n">
         <v>1.54689e-07</v>
@@ -4733,16 +4532,13 @@
         <v>-32526.56197133243</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.891140733194403e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2229.998570064815</v>
+        <v>446.037513696111</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000022e-08</v>
+        <v>1.109757353945327e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8269644167517142</v>
+        <v>0.9944645504252938</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4549,7 @@
         <v>1511.447</v>
       </c>
       <c r="C8" t="n">
-        <v>1971.189198715282</v>
+        <v>737.548158510423</v>
       </c>
       <c r="D8" t="n">
         <v>1.54753e-07</v>
@@ -4786,16 +4582,13 @@
         <v>-31434.63661951823</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73059805577069e-07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2206.114757424268</v>
+        <v>520.6395201112938</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000143e-08</v>
+        <v>4.607214717305916e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8270838825182354</v>
+        <v>0.9092166427716672</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4599,7 @@
         <v>1493.047</v>
       </c>
       <c r="C9" t="n">
-        <v>1952.958203198017</v>
+        <v>727.2104925938354</v>
       </c>
       <c r="D9" t="n">
         <v>1.54803e-07</v>
@@ -4839,16 +4632,13 @@
         <v>-31850.46018202034</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.111847671222076e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2182.328950149695</v>
+        <v>450.9362582652123</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000265015e-08</v>
+        <v>1.104125342651259e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.827259533955124</v>
+        <v>0.9999808311290369</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4649,7 @@
         <v>1487.687</v>
       </c>
       <c r="C10" t="n">
-        <v>1947.254830353564</v>
+        <v>719.5979949315022</v>
       </c>
       <c r="D10" t="n">
         <v>1.54834e-07</v>
@@ -4892,16 +4682,13 @@
         <v>-34772.73658822454</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.644906582154696e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2158.899897121277</v>
+        <v>454.8089379775988</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000005e-08</v>
+        <v>1.342346919063196e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8275119222540035</v>
+        <v>0.9901238933500002</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4699,7 @@
         <v>1458.771</v>
       </c>
       <c r="C11" t="n">
-        <v>1917.361988592903</v>
+        <v>711.8568981692844</v>
       </c>
       <c r="D11" t="n">
         <v>1.5487e-07</v>
@@ -4945,16 +4732,13 @@
         <v>-32495.99702496241</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.996092547629272e-12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2134.927758173419</v>
+        <v>459.7099151571182</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.248831826792467e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8278024218732957</v>
+        <v>0.9946351000634668</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4749,7 @@
         <v>1437.555</v>
       </c>
       <c r="C12" t="n">
-        <v>1895.054777996552</v>
+        <v>702.7326573458631</v>
       </c>
       <c r="D12" t="n">
         <v>1.54927e-07</v>
@@ -4998,16 +4782,13 @@
         <v>-31530.90224453312</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.114934500518794e-07</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2111.004690412993</v>
+        <v>446.9486347652123</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000032092e-08</v>
+        <v>1.105524340619508e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8281110816190586</v>
+        <v>0.9980802210224954</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4799,7 @@
         <v>1413.471</v>
       </c>
       <c r="C13" t="n">
-        <v>1877.971467429573</v>
+        <v>693.2877644466341</v>
       </c>
       <c r="D13" t="n">
         <v>1.54918e-07</v>
@@ -5051,16 +4832,13 @@
         <v>-31509.52581457571</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.32968214810881e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2087.096422352067</v>
+        <v>458.5977343019009</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000099046e-08</v>
+        <v>1.126044884170163e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8284451324124779</v>
+        <v>0.9966766085602843</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4849,7 @@
         <v>1406.915</v>
       </c>
       <c r="C14" t="n">
-        <v>1869.44774920784</v>
+        <v>685.7350727082583</v>
       </c>
       <c r="D14" t="n">
         <v>1.54987e-07</v>
@@ -5104,16 +4882,13 @@
         <v>-34341.29255935515</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.504153050287589e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2063.006822522449</v>
+        <v>455.6038836254566</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000566e-08</v>
+        <v>1.22804915713566e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8287898612707991</v>
+        <v>0.998406329449205</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4899,7 @@
         <v>1388.66</v>
       </c>
       <c r="C15" t="n">
-        <v>1850.06970103604</v>
+        <v>677.8275841548367</v>
       </c>
       <c r="D15" t="n">
         <v>1.55014e-07</v>
@@ -5157,16 +4932,13 @@
         <v>-34612.01789997334</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.083282705389819e-07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2038.575381786189</v>
+        <v>456.9912916581382</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000035747e-08</v>
+        <v>1.148648651940107e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8291597473511912</v>
+        <v>0.9965260819436523</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4949,7 @@
         <v>1371.678</v>
       </c>
       <c r="C16" t="n">
-        <v>1833.0086550681</v>
+        <v>670.4175660640103</v>
       </c>
       <c r="D16" t="n">
         <v>1.55091e-07</v>
@@ -5210,16 +4982,13 @@
         <v>-34961.10598432533</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.640999144036718e-09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2014.978127763932</v>
+        <v>429.8726236749467</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.3738514530688e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8295226583781842</v>
+        <v>0.9934173755704578</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +4999,7 @@
         <v>1341.192</v>
       </c>
       <c r="C17" t="n">
-        <v>1806.618713297441</v>
+        <v>662.0535263213118</v>
       </c>
       <c r="D17" t="n">
         <v>1.55166e-07</v>
@@ -5263,16 +5032,13 @@
         <v>-32462.68281610273</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.641468707511774e-07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1991.248229495919</v>
+        <v>462.549341040597</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000742e-08</v>
+        <v>1.287194723536827e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8299037479201862</v>
+        <v>0.995900187472195</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5049,7 @@
         <v>1334.44</v>
       </c>
       <c r="C18" t="n">
-        <v>1798.15757162344</v>
+        <v>654.0953568852295</v>
       </c>
       <c r="D18" t="n">
         <v>1.5523e-07</v>
@@ -5316,16 +5082,13 @@
         <v>-35418.1106533694</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.361552495473717e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1967.586212221529</v>
+        <v>479.492327804492</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000006193e-08</v>
+        <v>2.461554304875058e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8302911440284173</v>
+        <v>0.9576618127160347</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5099,7 @@
         <v>1315.413</v>
       </c>
       <c r="C19" t="n">
-        <v>1780.974598335715</v>
+        <v>646.8530408705817</v>
       </c>
       <c r="D19" t="n">
         <v>1.5529e-07</v>
@@ -5369,16 +5132,13 @@
         <v>-35432.79796440994</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.443762620555358e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1944.175870618619</v>
+        <v>495.8915854772243</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000007964e-08</v>
+        <v>4.702049726209905e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8306843462999087</v>
+        <v>0.916286988563861</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5149,7 @@
         <v>1293.375</v>
       </c>
       <c r="C20" t="n">
-        <v>1760.491722186731</v>
+        <v>638.9342670674519</v>
       </c>
       <c r="D20" t="n">
         <v>1.55332e-07</v>
@@ -5422,16 +5182,13 @@
         <v>-34469.82774745971</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.370783292064139e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1920.597611260568</v>
+        <v>446.614154320543</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000004e-08</v>
+        <v>1.271648891715432e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8310789482890005</v>
+        <v>0.9995989249264611</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5199,7 @@
         <v>1263.856</v>
       </c>
       <c r="C21" t="n">
-        <v>1731.969120500866</v>
+        <v>631.5295049191583</v>
       </c>
       <c r="D21" t="n">
         <v>1.55423e-07</v>
@@ -5475,16 +5232,13 @@
         <v>-31823.6538609025</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.725611565560686e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1896.732161770606</v>
+        <v>427.8099533647041</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>1.28327832644975e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8314747356605672</v>
+        <v>0.9959672176816359</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5249,7 @@
         <v>1247.206</v>
       </c>
       <c r="C22" t="n">
-        <v>1715.347998537714</v>
+        <v>624.891264947163</v>
       </c>
       <c r="D22" t="n">
         <v>1.55471e-07</v>
@@ -5528,16 +5282,13 @@
         <v>-32106.82479283401</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.971610374595483e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1873.651128718761</v>
+        <v>422.4527834142527</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000006e-08</v>
+        <v>1.328628046731469e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.831892729535577</v>
+        <v>0.9968344424735059</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5445,7 @@
         <v>2122.309</v>
       </c>
       <c r="C2" t="n">
-        <v>2616.956571393936</v>
+        <v>1396.238314636439</v>
       </c>
       <c r="D2" t="n">
         <v>1.51828e-07</v>
@@ -5727,16 +5478,13 @@
         <v>-23988.67161412517</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.094284275004969e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2861.355575806176</v>
+        <v>7.251025411831696</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000491e-08</v>
+        <v>1.763677737107376e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8253028516832255</v>
+        <v>0.8994769770848056</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5495,7 @@
         <v>1885.563</v>
       </c>
       <c r="C3" t="n">
-        <v>2331.043774954389</v>
+        <v>1010.376947168452</v>
       </c>
       <c r="D3" t="n">
         <v>1.5463e-07</v>
@@ -5780,16 +5528,13 @@
         <v>-26656.46554165931</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.777000906103705e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2639.04534560048</v>
+        <v>283.9466899216123</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000023e-08</v>
+        <v>9.786224522428403e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.825870838465928</v>
+        <v>0.9727431950948441</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5545,7 @@
         <v>1833.062</v>
       </c>
       <c r="C4" t="n">
-        <v>2270.118088728216</v>
+        <v>907.4086119319549</v>
       </c>
       <c r="D4" t="n">
         <v>1.54451e-07</v>
@@ -5833,16 +5578,13 @@
         <v>-30015.88560368071</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.871236760553751e-14</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2571.783365457188</v>
+        <v>361.686792423683</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>8.794360266156421e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.82590012173334</v>
+        <v>0.9962672541490148</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5595,7 @@
         <v>1798.479</v>
       </c>
       <c r="C5" t="n">
-        <v>2235.312360101401</v>
+        <v>880.522240437454</v>
       </c>
       <c r="D5" t="n">
         <v>1.53886e-07</v>
@@ -5886,16 +5628,13 @@
         <v>-31510.32553480652</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.029584111272498e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2532.379522275629</v>
+        <v>390.4119475471026</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000001307e-08</v>
+        <v>1.098777867441923e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8259081854434839</v>
+        <v>0.984374170167623</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5645,7 @@
         <v>1755.353</v>
       </c>
       <c r="C6" t="n">
-        <v>2198.090228887604</v>
+        <v>854.3636642764939</v>
       </c>
       <c r="D6" t="n">
         <v>1.54082e-07</v>
@@ -5939,16 +5678,13 @@
         <v>-30286.84957451514</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.84097581558627e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2496.352419223506</v>
+        <v>403.7201560343931</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.00000000000009e-08</v>
+        <v>8.866221848852909e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8259859256404509</v>
+        <v>0.999449906888936</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5695,7 @@
         <v>1744.804</v>
       </c>
       <c r="C7" t="n">
-        <v>2180.008815068026</v>
+        <v>840.0661489594072</v>
       </c>
       <c r="D7" t="n">
         <v>1.54129e-07</v>
@@ -5992,16 +5728,13 @@
         <v>-33262.27268777401</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.654196279765398e-12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2461.186323952877</v>
+        <v>405.4581130331833</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>8.656572676215104e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.82614900257313</v>
+        <v>0.9993547779854375</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5745,7 @@
         <v>1720.706</v>
       </c>
       <c r="C8" t="n">
-        <v>2159.781755177186</v>
+        <v>820.8383050219946</v>
       </c>
       <c r="D8" t="n">
         <v>1.54278e-07</v>
@@ -6045,16 +5778,13 @@
         <v>-35276.91877928114</v>
       </c>
       <c r="Y8" t="n">
-        <v>56.41577637011398</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2434.615413122013</v>
+        <v>415.2660935517986</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.215077235745217e-08</v>
+        <v>9.522729905856552e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8146841725410688</v>
+        <v>0.997893783250417</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5795,7 @@
         <v>1678.333</v>
       </c>
       <c r="C9" t="n">
-        <v>2121.453862826894</v>
+        <v>807.4357222610715</v>
       </c>
       <c r="D9" t="n">
         <v>1.54435e-07</v>
@@ -6098,16 +5828,13 @@
         <v>-32521.82245420742</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.124629398836019e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2390.707416245429</v>
+        <v>421.4846314300658</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>9.940912412850598e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8266126128866734</v>
+        <v>0.9975908834534816</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5845,7 @@
         <v>1656.884</v>
       </c>
       <c r="C10" t="n">
-        <v>2096.159086068368</v>
+        <v>793.9765362564571</v>
       </c>
       <c r="D10" t="n">
         <v>1.54613e-07</v>
@@ -6151,16 +5878,13 @@
         <v>-33030.03958684207</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.852318402191515e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2357.173159253746</v>
+        <v>424.0205235660923</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000721248e-08</v>
+        <v>1.041081931700596e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8268687985707787</v>
+        <v>0.9885531611586872</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5895,7 @@
         <v>1638.843</v>
       </c>
       <c r="C11" t="n">
-        <v>2076.26438431242</v>
+        <v>781.3484747056342</v>
       </c>
       <c r="D11" t="n">
         <v>1.54794e-07</v>
@@ -6204,16 +5928,13 @@
         <v>-34703.40742953988</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.292427635820399e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2325.861417769378</v>
+        <v>434.1470214650478</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.105140245667603e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8271394971160694</v>
+        <v>0.9982929172265176</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6091,7 @@
         <v>1718.342</v>
       </c>
       <c r="C2" t="n">
-        <v>2190.631368218961</v>
+        <v>885.9341408863594</v>
       </c>
       <c r="D2" t="n">
         <v>1.55451e-07</v>
@@ -6403,16 +6124,13 @@
         <v>-25360.25761020574</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.272520016605016e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2417.257251795772</v>
+        <v>318.9079205623863</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.00000000000001e-08</v>
+        <v>8.010290111274336e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8272098373655483</v>
+        <v>0.9960103451716296</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6141,7 @@
         <v>1610.434</v>
       </c>
       <c r="C3" t="n">
-        <v>2067.400184855127</v>
+        <v>805.6067203180061</v>
       </c>
       <c r="D3" t="n">
         <v>1.54978e-07</v>
@@ -6456,16 +6174,13 @@
         <v>-27619.29941574144</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.504708599181555e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2321.521389353818</v>
+        <v>402.5012329891907</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>1.03101460078439e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8273663063473612</v>
+        <v>0.9931104520652099</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6191,7 @@
         <v>1592.685</v>
       </c>
       <c r="C4" t="n">
-        <v>2040.721803632413</v>
+        <v>779.3471430066114</v>
       </c>
       <c r="D4" t="n">
         <v>1.54721e-07</v>
@@ -6509,16 +6224,13 @@
         <v>-31237.97154215303</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.25461203434129e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2281.714614064709</v>
+        <v>404.3776120329477</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000026e-08</v>
+        <v>9.060202896258084e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8273605829591431</v>
+        <v>0.9996465702219999</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6241,7 @@
         <v>1556.143</v>
       </c>
       <c r="C5" t="n">
-        <v>2010.052384700257</v>
+        <v>762.7366383775764</v>
       </c>
       <c r="D5" t="n">
         <v>1.54876e-07</v>
@@ -6562,16 +6274,13 @@
         <v>-30741.488300718</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.467837727914035e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2251.90916464284</v>
+        <v>422.9016718349001</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000058e-08</v>
+        <v>1.118559149562526e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8273413122080273</v>
+        <v>0.993107972810532</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6291,7 @@
         <v>1535.808</v>
       </c>
       <c r="C6" t="n">
-        <v>1991.420759334986</v>
+        <v>751.7111554758186</v>
       </c>
       <c r="D6" t="n">
         <v>1.55017e-07</v>
@@ -6615,16 +6324,13 @@
         <v>-31255.29273366674</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.428258509733219e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2225.650434128286</v>
+        <v>427.9821392547165</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>9.878558789324794e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8274043718995371</v>
+        <v>0.9999998484198215</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6341,7 @@
         <v>1514.839</v>
       </c>
       <c r="C7" t="n">
-        <v>1971.270488283465</v>
+        <v>741.1578312811513</v>
       </c>
       <c r="D7" t="n">
         <v>1.55111e-07</v>
@@ -6668,16 +6374,13 @@
         <v>-31403.74141723057</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.139853926920892e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2199.84142326194</v>
+        <v>435.4474533286112</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000011329e-08</v>
+        <v>1.359904741899443e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8275555910164117</v>
+        <v>0.9883667375340147</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6391,7 @@
         <v>1506.431</v>
       </c>
       <c r="C8" t="n">
-        <v>1963.008169882385</v>
+        <v>731.2312417589818</v>
       </c>
       <c r="D8" t="n">
         <v>1.55234e-07</v>
@@ -6721,16 +6424,13 @@
         <v>-34287.76684967094</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.194038909073669e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2175.567918374628</v>
+        <v>446.7698484999153</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000012003e-08</v>
+        <v>1.234180457199197e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8277479681036791</v>
+        <v>0.9914798679362266</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6441,7 @@
         <v>1483.257</v>
       </c>
       <c r="C9" t="n">
-        <v>1939.655064582159</v>
+        <v>721.5442413834348</v>
       </c>
       <c r="D9" t="n">
         <v>1.55307e-07</v>
@@ -6774,16 +6474,13 @@
         <v>-33225.87018089015</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.911543712929486e-07</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2152.458574001397</v>
+        <v>449.7096626633433</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000221e-08</v>
+        <v>1.071625112728521e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8279835716156516</v>
+        <v>0.9977386528807707</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6491,7 @@
         <v>1454.908</v>
       </c>
       <c r="C10" t="n">
-        <v>1912.7565124483</v>
+        <v>714.2939829735024</v>
       </c>
       <c r="D10" t="n">
         <v>1.55378e-07</v>
@@ -6827,16 +6524,13 @@
         <v>-31091.60252052121</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.589425969651113e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2129.849988865153</v>
+        <v>438.9092089633874</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000010251e-08</v>
+        <v>1.074317133184682e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8282531796466067</v>
+        <v>0.9999651474644541</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6541,7 @@
         <v>1434.402</v>
       </c>
       <c r="C11" t="n">
-        <v>1896.304374829477</v>
+        <v>705.9670848108341</v>
       </c>
       <c r="D11" t="n">
         <v>1.55444e-07</v>
@@ -6880,16 +6574,13 @@
         <v>-31158.69792909854</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.218747229191968e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2107.427197217289</v>
+        <v>447.8517765230828</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000005637e-08</v>
+        <v>1.162493044597511e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8285636792480321</v>
+        <v>0.9978726767228896</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6591,7 @@
         <v>1417.292</v>
       </c>
       <c r="C12" t="n">
-        <v>1878.856303721721</v>
+        <v>697.5905667456514</v>
       </c>
       <c r="D12" t="n">
         <v>1.55496e-07</v>
@@ -6933,16 +6624,13 @@
         <v>-31181.09533649846</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.495794803160773e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2084.479934258037</v>
+        <v>452.322601916532</v>
       </c>
       <c r="AA12" t="n">
-        <v>1e-08</v>
+        <v>1.216482805154157e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8288912003939648</v>
+        <v>0.9964659238834771</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6641,7 @@
         <v>1404.086</v>
       </c>
       <c r="C13" t="n">
-        <v>1862.928031477302</v>
+        <v>690.7268748424742</v>
       </c>
       <c r="D13" t="n">
         <v>1.55583e-07</v>
@@ -6986,16 +6674,13 @@
         <v>-31400.85391835023</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.087838234381142e-07</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2062.319116559911</v>
+        <v>444.6922951968028</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000859348e-08</v>
+        <v>1.210220222560693e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8292267556824336</v>
+        <v>0.9972678196988473</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6691,7 @@
         <v>1389.497</v>
       </c>
       <c r="C14" t="n">
-        <v>1850.571773580557</v>
+        <v>681.2272524204872</v>
       </c>
       <c r="D14" t="n">
         <v>1.55627e-07</v>
@@ -7039,16 +6724,13 @@
         <v>-32649.95671846926</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.23833172258368e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2040.0715355379</v>
+        <v>434.0205741066142</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000011e-08</v>
+        <v>1.119993848609916e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8295688023830374</v>
+        <v>0.9992212187969393</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6741,7 @@
         <v>1361.281</v>
       </c>
       <c r="C15" t="n">
-        <v>1825.082549018697</v>
+        <v>674.0055869043307</v>
       </c>
       <c r="D15" t="n">
         <v>1.55733e-07</v>
@@ -7092,16 +6774,13 @@
         <v>-30680.44679676006</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.233578663534895e-07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2017.470223534055</v>
+        <v>454.0622201030697</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000128576e-08</v>
+        <v>1.286917555975535e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8299283596411257</v>
+        <v>0.9959148294896352</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6791,7 @@
         <v>1348.774</v>
       </c>
       <c r="C16" t="n">
-        <v>1812.414525812664</v>
+        <v>666.8623465528084</v>
       </c>
       <c r="D16" t="n">
         <v>1.55792e-07</v>
@@ -7145,16 +6824,13 @@
         <v>-31811.78809521202</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.110046833897703e-07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1994.414255381434</v>
+        <v>451.6983482611713</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000433062e-08</v>
+        <v>1.285094978167381e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8303118633528034</v>
+        <v>0.9962342904242589</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6841,7 @@
         <v>1324.518</v>
       </c>
       <c r="C17" t="n">
-        <v>1785.512943428149</v>
+        <v>658.8253193029803</v>
       </c>
       <c r="D17" t="n">
         <v>1.55865e-07</v>
@@ -7198,16 +6874,13 @@
         <v>-30004.38342051718</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.463125812017704e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1971.80928950046</v>
+        <v>439.8444303280077</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000049399e-08</v>
+        <v>1.182832240041175e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8306920563252771</v>
+        <v>0.9999956701688242</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6891,7 @@
         <v>1321.127</v>
       </c>
       <c r="C18" t="n">
-        <v>1783.267337343021</v>
+        <v>652.3101250008343</v>
       </c>
       <c r="D18" t="n">
         <v>1.55936e-07</v>
@@ -7251,16 +6924,13 @@
         <v>-33555.57762910577</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.132741841604442e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1948.8704975274</v>
+        <v>444.4881845478748</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.00000000000546e-08</v>
+        <v>1.317973515036621e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8310744570390908</v>
+        <v>0.9995336038446818</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6941,7 @@
         <v>1298.433</v>
       </c>
       <c r="C19" t="n">
-        <v>1760.818288315126</v>
+        <v>644.541616139451</v>
       </c>
       <c r="D19" t="n">
         <v>1.55983e-07</v>
@@ -7304,16 +6974,13 @@
         <v>-32377.09633251138</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.157994264965029e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1926.463805741966</v>
+        <v>430.9661092332632</v>
       </c>
       <c r="AA19" t="n">
-        <v>1e-08</v>
+        <v>1.520826934530931e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8314681343215892</v>
+        <v>0.9873747620493865</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +6991,7 @@
         <v>1286.323</v>
       </c>
       <c r="C20" t="n">
-        <v>1749.012051627349</v>
+        <v>637.6931858076397</v>
       </c>
       <c r="D20" t="n">
         <v>1.56098e-07</v>
@@ -7357,16 +7024,13 @@
         <v>-33903.54393270001</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.84339648003393e-07</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1904.315773347781</v>
+        <v>426.8643724591042</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>1.322407980798488e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8318499840812067</v>
+        <v>0.9982786152801657</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7041,7 @@
         <v>1261.093</v>
       </c>
       <c r="C21" t="n">
-        <v>1722.037425364234</v>
+        <v>631.2711747664042</v>
       </c>
       <c r="D21" t="n">
         <v>1.56129e-07</v>
@@ -7410,16 +7074,13 @@
         <v>-31673.88839292728</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.359280786738904e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1881.377922343777</v>
+        <v>443.1234589781881</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.00000000000018e-08</v>
+        <v>1.817266267796415e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8322595460561064</v>
+        <v>0.9740389841820039</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7091,7 @@
         <v>1249.709</v>
       </c>
       <c r="C22" t="n">
-        <v>1711.666902874609</v>
+        <v>624.2025720809053</v>
       </c>
       <c r="D22" t="n">
         <v>1.56205e-07</v>
@@ -7463,16 +7124,13 @@
         <v>-32912.49848217268</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.467360730497264e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1859.214645820526</v>
+        <v>437.9137632966633</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000671e-08</v>
+        <v>1.228528399413165e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8326683780320826</v>
+        <v>0.9995399554307766</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7287,7 @@
         <v>2088.844</v>
       </c>
       <c r="C2" t="n">
-        <v>2633.053789694123</v>
+        <v>1427.457009731745</v>
       </c>
       <c r="D2" t="n">
         <v>1.50818e-07</v>
@@ -7662,16 +7320,13 @@
         <v>-22177.92908583114</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.182570499047168e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2836.506792698845</v>
+        <v>5.04356630940404</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000036e-08</v>
+        <v>2.014198602415346e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8235389366040871</v>
+        <v>0.8884666752671683</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7337,7 @@
         <v>1829.747</v>
       </c>
       <c r="C3" t="n">
-        <v>2289.348152473246</v>
+        <v>945.0639597729212</v>
       </c>
       <c r="D3" t="n">
         <v>1.55608e-07</v>
@@ -7715,16 +7370,13 @@
         <v>-25873.60345906585</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.641420491502718e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2577.065457548962</v>
+        <v>337.30389158602</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000043e-08</v>
+        <v>8.441987990365849e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8244098618608863</v>
+        <v>0.9941462634016139</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7387,7 @@
         <v>1760.926</v>
       </c>
       <c r="C4" t="n">
-        <v>2212.767442393761</v>
+        <v>885.0694804017573</v>
       </c>
       <c r="D4" t="n">
         <v>1.55542e-07</v>
@@ -7768,16 +7420,13 @@
         <v>-27929.11952677896</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.935819490544788e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2506.729730222475</v>
+        <v>642.5551411952621</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000040485e-08</v>
+        <v>1.997326854719796e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8246569878850278</v>
+        <v>0.8194428574633617</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7437,7 @@
         <v>1727.173</v>
       </c>
       <c r="C5" t="n">
-        <v>2177.623793060864</v>
+        <v>856.1968728839227</v>
       </c>
       <c r="D5" t="n">
         <v>1.55174e-07</v>
@@ -7821,16 +7470,13 @@
         <v>-29087.00570661683</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.861860459995864e-11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2463.603182842488</v>
+        <v>395.958505322763</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.011726683789168e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8248754942505564</v>
+        <v>0.9887448550039413</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7487,7 @@
         <v>1702.897</v>
       </c>
       <c r="C6" t="n">
-        <v>2155.393993030149</v>
+        <v>831.1022058211713</v>
       </c>
       <c r="D6" t="n">
         <v>1.5523e-07</v>
@@ -7874,16 +7520,13 @@
         <v>-31185.3822423091</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.447256478326925e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2426.451270190614</v>
+        <v>495.508996235819</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000004894e-08</v>
+        <v>4.284317721517719e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8250863204450599</v>
+        <v>0.9050885288608147</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7537,7 @@
         <v>1673.924</v>
       </c>
       <c r="C7" t="n">
-        <v>2124.142922228038</v>
+        <v>810.2763254086723</v>
       </c>
       <c r="D7" t="n">
         <v>1.5533e-07</v>
@@ -7927,16 +7570,13 @@
         <v>-31797.22813634483</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.033027993547383e-07</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2389.775832998311</v>
+        <v>449.2018198018083</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.00000000003441e-08</v>
+        <v>1.589314403747035e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8253742726708515</v>
+        <v>0.966436379690124</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7587,7 @@
         <v>1653.709</v>
       </c>
       <c r="C8" t="n">
-        <v>2103.249614811314</v>
+        <v>792.1531991911269</v>
       </c>
       <c r="D8" t="n">
         <v>1.55459e-07</v>
@@ -7980,16 +7620,13 @@
         <v>-33745.74401886032</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.920523641782357e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2354.487893738019</v>
+        <v>433.843321637355</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000001441e-08</v>
+        <v>1.027762432367787e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8256439566405775</v>
+        <v>0.9885930710556742</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7637,7 @@
         <v>1616.318</v>
       </c>
       <c r="C9" t="n">
-        <v>2066.155298666802</v>
+        <v>784.8411332813276</v>
       </c>
       <c r="D9" t="n">
         <v>1.55649e-07</v>
@@ -8033,16 +7670,13 @@
         <v>-31401.60645278211</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.164242542498674e-07</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2319.877383328213</v>
+        <v>427.441387180023</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000035413e-08</v>
+        <v>1.243294209977379e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8258872042344967</v>
+        <v>0.9903030539720722</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7687,7 @@
         <v>1582.14</v>
       </c>
       <c r="C10" t="n">
-        <v>2036.559320545551</v>
+        <v>768.0027846239649</v>
       </c>
       <c r="D10" t="n">
         <v>1.55979e-07</v>
@@ -8086,16 +7720,13 @@
         <v>-30527.16340045061</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.618416090041746e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2287.782641462251</v>
+        <v>447.8936756769287</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000444e-08</v>
+        <v>1.005182645295967e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8261096052838799</v>
+        <v>0.9970190343066302</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7737,7 @@
         <v>1552.786</v>
       </c>
       <c r="C11" t="n">
-        <v>2009.59247565715</v>
+        <v>756.545750628622</v>
       </c>
       <c r="D11" t="n">
         <v>1.56226e-07</v>
@@ -8139,16 +7770,13 @@
         <v>-29729.4956525476</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.488565273240728e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2257.43812124825</v>
+        <v>442.2276878576348</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000007784e-08</v>
+        <v>1.330760193456481e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8263403127084581</v>
+        <v>0.9888340641499902</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7933,7 @@
         <v>1679.799</v>
       </c>
       <c r="C2" t="n">
-        <v>2168.33062458162</v>
+        <v>858.5559888362835</v>
       </c>
       <c r="D2" t="n">
         <v>1.57138e-07</v>
@@ -8338,16 +7966,13 @@
         <v>-25001.69081116027</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.614824750024697e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2399.94346229863</v>
+        <v>379.2057780354749</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000002177e-08</v>
+        <v>8.667543688737761e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8253812966683933</v>
+        <v>0.9986880272271763</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +7983,7 @@
         <v>1600.857</v>
       </c>
       <c r="C3" t="n">
-        <v>2065.04777400224</v>
+        <v>786.1609283523866</v>
       </c>
       <c r="D3" t="n">
         <v>1.56059e-07</v>
@@ -8391,16 +8016,13 @@
         <v>-29924.88177488731</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.034253212907334e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2310.751011394418</v>
+        <v>503.4950287014935</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000281e-08</v>
+        <v>4.035810437440948e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8255742954399388</v>
+        <v>0.911150364903012</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8033,7 @@
         <v>1556.955</v>
       </c>
       <c r="C4" t="n">
-        <v>2021.317409809695</v>
+        <v>769.7136281045989</v>
       </c>
       <c r="D4" t="n">
         <v>1.55947e-07</v>
@@ -8444,16 +8066,13 @@
         <v>-28957.73037579245</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.288773157832972e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2273.456502967149</v>
+        <v>509.6323256105301</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000146725e-08</v>
+        <v>4.15223615762147e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8255850427780846</v>
+        <v>0.9089070443033822</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8083,7 @@
         <v>1547.604</v>
       </c>
       <c r="C5" t="n">
-        <v>2008.56620585737</v>
+        <v>757.4110170037636</v>
       </c>
       <c r="D5" t="n">
         <v>1.56151e-07</v>
@@ -8497,16 +8116,13 @@
         <v>-31609.43672057775</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.146716851668575e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2246.025450272327</v>
+        <v>445.4577724570538</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000152916e-08</v>
+        <v>1.34551934490977e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.825630742229314</v>
+        <v>0.9875526355611911</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8133,7 @@
         <v>1528.567</v>
       </c>
       <c r="C6" t="n">
-        <v>1991.012064699562</v>
+        <v>749.4557177812634</v>
       </c>
       <c r="D6" t="n">
         <v>1.56145e-07</v>
@@ -8550,16 +8166,13 @@
         <v>-31639.7050943957</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.128634375804588e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2220.941541587195</v>
+        <v>461.4875404520388</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000029e-08</v>
+        <v>1.183793543474551e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8257774838069417</v>
+        <v>0.9873851641599939</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8183,7 @@
         <v>1502.115</v>
       </c>
       <c r="C7" t="n">
-        <v>1966.90296193571</v>
+        <v>737.9311024199098</v>
       </c>
       <c r="D7" t="n">
         <v>1.56295e-07</v>
@@ -8603,16 +8216,13 @@
         <v>-30998.9395754244</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.01343190634668e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2199.870963468618</v>
+        <v>517.2680006299253</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000006521e-08</v>
+        <v>4.456493094941367e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8258596233710385</v>
+        <v>0.9105534215546494</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8233,7 @@
         <v>1476.099</v>
       </c>
       <c r="C8" t="n">
-        <v>1941.03170615722</v>
+        <v>733.7084281770121</v>
       </c>
       <c r="D8" t="n">
         <v>1.56656e-07</v>
@@ -8656,16 +8266,13 @@
         <v>-29165.0548599034</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.270165455564024e-07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2177.329610599659</v>
+        <v>511.5563319144674</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000014658e-08</v>
+        <v>4.077637664835355e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8259844762401788</v>
+        <v>0.9124867186558907</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8283,7 @@
         <v>1461.996</v>
       </c>
       <c r="C9" t="n">
-        <v>1929.087723729359</v>
+        <v>721.2399609694819</v>
       </c>
       <c r="D9" t="n">
         <v>1.56748e-07</v>
@@ -8709,16 +8316,13 @@
         <v>-30472.43202429854</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.065072671323593e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2153.720312297246</v>
+        <v>461.7932878322764</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000355e-08</v>
+        <v>1.169154350422945e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8261797601106761</v>
+        <v>0.9955036415987997</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8333,7 @@
         <v>1448.296</v>
       </c>
       <c r="C10" t="n">
-        <v>1915.73710368412</v>
+        <v>713.1241577169702</v>
       </c>
       <c r="D10" t="n">
         <v>1.56694e-07</v>
@@ -8762,16 +8366,13 @@
         <v>-31800.16477470212</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.110470417100931e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2130.472622984718</v>
+        <v>466.7886645895289</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000075e-08</v>
+        <v>1.267829683695835e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8263988533012309</v>
+        <v>0.9913751892133996</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8383,7 @@
         <v>1428.58</v>
       </c>
       <c r="C11" t="n">
-        <v>1899.061776511361</v>
+        <v>703.7597859615177</v>
       </c>
       <c r="D11" t="n">
         <v>1.56884e-07</v>
@@ -8815,16 +8416,13 @@
         <v>-31994.03138025086</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.091815773086266e-07</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2107.606532311479</v>
+        <v>462.2768783366902</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000142e-08</v>
+        <v>1.192137446935499e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.826646192193352</v>
+        <v>0.9946763526978578</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8433,7 @@
         <v>1400.32</v>
       </c>
       <c r="C12" t="n">
-        <v>1873.796152743545</v>
+        <v>696.1444307035912</v>
       </c>
       <c r="D12" t="n">
         <v>1.56939e-07</v>
@@ -8868,16 +8466,13 @@
         <v>-29867.56232307294</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32397366149695e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2084.665423401611</v>
+        <v>461.3150816381173</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000003696e-08</v>
+        <v>1.133190616980566e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8269100335493037</v>
+        <v>0.99995986699673</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8483,7 @@
         <v>1393.618</v>
       </c>
       <c r="C13" t="n">
-        <v>1861.67534642676</v>
+        <v>687.6858332992754</v>
       </c>
       <c r="D13" t="n">
         <v>1.57091e-07</v>
@@ -8921,16 +8516,13 @@
         <v>-31383.62879914522</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.743200290483485e-07</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2062.165297819159</v>
+        <v>440.1463796044235</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000847e-08</v>
+        <v>1.339993817701277e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8272045140411995</v>
+        <v>0.9936103256347421</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8533,7 @@
         <v>1372.41</v>
       </c>
       <c r="C14" t="n">
-        <v>1844.210725582781</v>
+        <v>679.7572779447822</v>
       </c>
       <c r="D14" t="n">
         <v>1.5723e-07</v>
@@ -8974,16 +8566,13 @@
         <v>-31538.11576055409</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.058927311162519e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2039.402210844883</v>
+        <v>444.1272883234648</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000002522e-08</v>
+        <v>1.076357003554935e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8275311280678673</v>
+        <v>0.9991727497372915</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8583,7 @@
         <v>1355.007</v>
       </c>
       <c r="C15" t="n">
-        <v>1826.978643687235</v>
+        <v>669.9361430611284</v>
       </c>
       <c r="D15" t="n">
         <v>1.57241e-07</v>
@@ -9027,16 +8616,13 @@
         <v>-31728.96189146264</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.367241277796674e-07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2016.192286684543</v>
+        <v>465.0387826964258</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000456e-08</v>
+        <v>1.469491564802134e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8278656786794472</v>
+        <v>0.9911850209587255</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8633,7 @@
         <v>1334.625</v>
       </c>
       <c r="C16" t="n">
-        <v>1809.301315417756</v>
+        <v>664.6057892748427</v>
       </c>
       <c r="D16" t="n">
         <v>1.57271e-07</v>
@@ -9080,16 +8666,13 @@
         <v>-32006.93782961402</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.556427182879011e-09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1993.319305247415</v>
+        <v>493.992285094899</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000095e-08</v>
+        <v>2.554910599142419e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.82821351609438</v>
+        <v>0.9534297641124416</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8683,7 @@
         <v>1314.383</v>
       </c>
       <c r="C17" t="n">
-        <v>1788.015939176099</v>
+        <v>657.0094322853491</v>
       </c>
       <c r="D17" t="n">
         <v>1.57264e-07</v>
@@ -9133,16 +8716,13 @@
         <v>-31086.68979129966</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.153163672748359e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1970.265963456888</v>
+        <v>468.4394267104549</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000215e-08</v>
+        <v>1.632468101448588e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8285616354157982</v>
+        <v>0.9848004070445061</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8733,7 @@
         <v>1303.558</v>
       </c>
       <c r="C18" t="n">
-        <v>1774.506481096019</v>
+        <v>649.3003313765142</v>
       </c>
       <c r="D18" t="n">
         <v>1.57417e-07</v>
@@ -9186,16 +8766,13 @@
         <v>-32379.18983177853</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.619802128066902e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1947.038536450478</v>
+        <v>456.9496893290573</v>
       </c>
       <c r="AA18" t="n">
-        <v>1e-08</v>
+        <v>1.259529603141399e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8289442752101198</v>
+        <v>0.9979684593892342</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8783,7 @@
         <v>1286.945</v>
       </c>
       <c r="C19" t="n">
-        <v>1763.651387473071</v>
+        <v>641.8309528504385</v>
       </c>
       <c r="D19" t="n">
         <v>1.57495e-07</v>
@@ -9239,16 +8816,13 @@
         <v>-33667.70040112365</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.89175714841225e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1924.050760428205</v>
+        <v>459.1360647756629</v>
       </c>
       <c r="AA19" t="n">
-        <v>1e-08</v>
+        <v>1.271002309156894e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8293184717762465</v>
+        <v>0.9996070022863754</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8833,7 @@
         <v>1267.219</v>
       </c>
       <c r="C20" t="n">
-        <v>1740.70156899483</v>
+        <v>634.3752651052769</v>
       </c>
       <c r="D20" t="n">
         <v>1.57697e-07</v>
@@ -9292,16 +8866,13 @@
         <v>-32750.63359749494</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.722922622809486e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1900.609551264085</v>
+        <v>442.1513728937193</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000101e-08</v>
+        <v>1.182690102584468e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8297066466462508</v>
+        <v>0.9993814378616422</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8883,7 @@
         <v>1246.586</v>
       </c>
       <c r="C21" t="n">
-        <v>1726.086119674266</v>
+        <v>626.1799611762632</v>
       </c>
       <c r="D21" t="n">
         <v>1.57805e-07</v>
@@ -9345,16 +8916,13 @@
         <v>-33032.99326825517</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.358347694258068e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1877.277228200415</v>
+        <v>472.8002740202073</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000023054e-08</v>
+        <v>1.710270568297559e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8301054528868912</v>
+        <v>0.9842940311440729</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8933,7 @@
         <v>1220.686</v>
       </c>
       <c r="C22" t="n">
-        <v>1698.004922464293</v>
+        <v>620.518411673614</v>
       </c>
       <c r="D22" t="n">
         <v>1.57798e-07</v>
@@ -9398,16 +8966,13 @@
         <v>-30999.43984475506</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.557780522910367e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1853.739314703515</v>
+        <v>458.7838040757868</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000025e-08</v>
+        <v>1.939466635841878e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8304928078988155</v>
+        <v>0.9781026652408781</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9129,7 @@
         <v>1656.272</v>
       </c>
       <c r="C2" t="n">
-        <v>2266.624129783494</v>
+        <v>1282.571077185897</v>
       </c>
       <c r="D2" t="n">
         <v>1.55519e-07</v>
@@ -9597,16 +9162,13 @@
         <v>-19687.67058978109</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.227213321259076e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2331.000620958536</v>
+        <v>4.614624246582051</v>
       </c>
       <c r="AA2" t="n">
-        <v>1e-08</v>
+        <v>1.918681810731524e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8258135490724141</v>
+        <v>0.8979345683157428</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9179,7 @@
         <v>1418.672</v>
       </c>
       <c r="C3" t="n">
-        <v>1923.060824157982</v>
+        <v>733.1008408100257</v>
       </c>
       <c r="D3" t="n">
         <v>1.57788e-07</v>
@@ -9650,16 +9212,13 @@
         <v>-24905.66372225419</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.171980325841046e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2092.307869183674</v>
+        <v>423.9733819019196</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000602e-08</v>
+        <v>1.389937182089272e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8265843011122188</v>
+        <v>0.9840347509918508</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9229,7 @@
         <v>1354.417</v>
       </c>
       <c r="C4" t="n">
-        <v>1847.932409335374</v>
+        <v>692.6703150211328</v>
       </c>
       <c r="D4" t="n">
         <v>1.5718e-07</v>
@@ -9703,16 +9262,13 @@
         <v>-26779.13229182119</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.249067248825103e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2029.528002474151</v>
+        <v>445.225639926198</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000013e-08</v>
+        <v>1.075540211984024e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8267106954024259</v>
+        <v>0.9993101574587206</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9279,7 @@
         <v>1320.446</v>
       </c>
       <c r="C5" t="n">
-        <v>1812.26646507746</v>
+        <v>672.3486392749768</v>
       </c>
       <c r="D5" t="n">
         <v>1.56788e-07</v>
@@ -9756,16 +9312,13 @@
         <v>-27094.24542119744</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.46915560628849e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1992.585398079097</v>
+        <v>454.7342561056767</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000118e-08</v>
+        <v>1.138075438305589e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8267997364134732</v>
+        <v>0.9978562402343409</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9329,7 @@
         <v>1280.727</v>
       </c>
       <c r="C6" t="n">
-        <v>1779.292269399794</v>
+        <v>658.4229775946496</v>
       </c>
       <c r="D6" t="n">
         <v>1.56482e-07</v>
@@ -9809,16 +9362,13 @@
         <v>-26104.72380503079</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.462544229633462e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1958.77864196675</v>
+        <v>507.0523300330825</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000038e-08</v>
+        <v>2.440215868835488e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8270244849704278</v>
+        <v>0.9530774772808871</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9379,7 @@
         <v>1258.651</v>
       </c>
       <c r="C7" t="n">
-        <v>1759.201184789707</v>
+        <v>645.5207301924339</v>
       </c>
       <c r="D7" t="n">
         <v>1.56741e-07</v>
@@ -9862,16 +9412,13 @@
         <v>-27035.56261448654</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.34133417951443e-07</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1924.150154369358</v>
+        <v>459.9050925453559</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000583e-08</v>
+        <v>1.1989122930747e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8273420005662727</v>
+        <v>0.9995015605006953</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9429,7 @@
         <v>1237.212</v>
       </c>
       <c r="C8" t="n">
-        <v>1739.493066753244</v>
+        <v>636.4666648399135</v>
       </c>
       <c r="D8" t="n">
         <v>1.56929e-07</v>
@@ -9915,16 +9462,13 @@
         <v>-28160.04567139671</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.147090937601186e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1890.043765844406</v>
+        <v>464.8502781063953</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000017e-08</v>
+        <v>1.23702455640061e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8277202436395137</v>
+        <v>0.9998908626986495</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9479,7 @@
         <v>1210.55</v>
       </c>
       <c r="C9" t="n">
-        <v>1716.475086994664</v>
+        <v>624.6801110213236</v>
       </c>
       <c r="D9" t="n">
         <v>1.57095e-07</v>
@@ -9968,16 +9512,13 @@
         <v>-28316.6990865787</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.221931878622256e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1857.435200470321</v>
+        <v>459.013728356566</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.00000000000014e-08</v>
+        <v>1.233101305737869e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8281014582459626</v>
+        <v>0.9982565725028263</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9529,7 @@
         <v>1190.579</v>
       </c>
       <c r="C10" t="n">
-        <v>1693.044736622755</v>
+        <v>617.2670137631266</v>
       </c>
       <c r="D10" t="n">
         <v>1.57463e-07</v>
@@ -10021,16 +9562,13 @@
         <v>-28499.6313728429</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.161654329277473e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1826.801596949331</v>
+        <v>481.5491941684383</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000015e-08</v>
+        <v>1.719951084524489e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8284659277598504</v>
+        <v>0.9816256871513414</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9579,7 @@
         <v>1163.373</v>
       </c>
       <c r="C11" t="n">
-        <v>1670.918211402351</v>
+        <v>607.4899839731886</v>
       </c>
       <c r="D11" t="n">
         <v>1.57704e-07</v>
@@ -10074,16 +9612,13 @@
         <v>-28516.75874047502</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.333681706639339e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1798.781127294667</v>
+        <v>487.1728542869869</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>2.649911769799052e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8288280427575897</v>
+        <v>0.95623601504486</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 47.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1.000000000000217e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8247941255967071</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1852.065</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2287.092380386503</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.57401e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-72.952</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1650674662668564</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5549845837615387</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.363128930817634</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.149577294685953</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16.93084244871603</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.45292921465098</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.574126166089</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-28201.09178890567</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-11.50530909582562</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000016756e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8242676901990474</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1740.486</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.93975427428303</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2151.145380627682</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9405590255449815</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.56412e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-74.56399999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2736116545982634</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.268378182860415</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.15031638533613</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.674168130089671</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.80286403888009</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.097124853336</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.65768983811093</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-31360.18726880851</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.810641966766525</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8241254196300632</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1694.133</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9147265349758241</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2113.436570582687</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9240713618334603</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.55721e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-75.127</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.51330888409691</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.414204342249551</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.604457362102806</v>
+      </c>
+      <c r="L14" t="n">
+        <v>26.96022294770729</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.14648789362288</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.84603153122611</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-31127.173971162</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.736088488491532</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8237063366450689</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1680.005</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9070982929864773</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2089.489525190231</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9136008423223907</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.55024e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-75.589</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4702481162184389</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9661719137756178</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.293539875683755</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.946403148114801</v>
+      </c>
+      <c r="L15" t="n">
+        <v>41.56198688339764</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.59878191968943</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.82587261235322</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-35125.19756241179</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.181705561067247</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8234555665830496</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1655.06</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8936295432395731</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2062.990847363113</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9020146562748291</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.54605e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-75.898</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3791940254858774</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.126468990099835</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.15136111918272</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.846486941498246</v>
+      </c>
+      <c r="L16" t="n">
+        <v>44.74587739047713</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.71561516356934</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17.42579244517613</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-35969.18841330808</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5.493582563936343</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000001406e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8234316890880138</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1609.273</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8689074087572521</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2035.274707859368</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8898961516873317</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.5422e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-76.18000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1069857373370196</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3685025977628416</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.281113549117138</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.40172463083164</v>
+      </c>
+      <c r="L17" t="n">
+        <v>29.79253006075959</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.46749422115867</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.19902900569469</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-32754.61125789627</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.533804883145194</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000069956e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8235496976852456</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1589.43</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.858193421937135</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2010.51884996385</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8790719899228933</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.53894e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-76.45699999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1276451266109239</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9308488260428285</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.713901477001346</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.915748445427535</v>
+      </c>
+      <c r="L18" t="n">
+        <v>35.21684934252337</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.69009664940322</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.29114810385839</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-34622.08000848163</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>5.791662583133416</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000019195e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8238142756687453</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1570.141</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8477785606876649</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1982.556528720554</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8668458457220322</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.53697e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-76.702</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1727803459943715</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9901722831672802</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.107277902920565</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.457085246361697</v>
+      </c>
+      <c r="L19" t="n">
+        <v>43.03532824807541</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.87893981558044</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>18.33963268226879</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-36377.15682085705</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>6.990211751288143</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000029614e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8241104811090402</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1549.192</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8364674026019605</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1959.283724481965</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8566701289743527</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.53505e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-76.91</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3824880002434367</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.24481106596834</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.32645342256603</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.825841798127732</v>
+      </c>
+      <c r="L20" t="n">
+        <v>44.55603278052667</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.94331169274881</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.72661065638534</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-36705.94919155094</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>6.275823055941942</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000441e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8244502093963471</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1520.05</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8207325336853728</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1934.446319306239</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8458103117720719</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.53331e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-77.114</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1390257733706653</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8892175097959155</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.850109721214845</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.237524751820191</v>
+      </c>
+      <c r="L21" t="n">
+        <v>38.70147375986723</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.9312949383677</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18.65313944637202</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-36054.00851363573</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.392838826590605</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000217e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8247941255967071</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>1.000000000000012e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8313228917593165</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1688.479</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2133.658207694314</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.50004e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-75.64</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.06425795817064275</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6076386554385961</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.360816358586916</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.507661216995888</v>
+      </c>
+      <c r="L23" t="n">
+        <v>26.7300899720776</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.89058114120699</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.91863455735371</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-28991.16153508377</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-9.180124071929413</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000001778e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8265850089570875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1595.146</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9447236240427036</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2000.013419930086</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9373635443191963</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.51102e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.379</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3932157403624341</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.013037356104345</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.982198547551324</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.914076583735237</v>
+      </c>
+      <c r="L24" t="n">
+        <v>33.86824046029018</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.31767280895311</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15.53823673049421</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-30954.55371271355</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>6.733236637214873</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000024504e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8267268638347558</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1558.569</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9230609323539114</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1962.448518433205</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.919757677849386</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.51466e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.627</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5876815472593551</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.075886618148008</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.150526073785553</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.048025814431051</v>
+      </c>
+      <c r="L25" t="n">
+        <v>35.2842781878584</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.4262846092787</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.01175604184736</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-31391.21171684274</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>8.344005260044469</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000051e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8266248727835603</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1530.965</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9067124909459935</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1941.576968753743</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9099756285951071</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.5165e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-76.818</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.222575220508038</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9611648272170795</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.613633973016985</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.965925485010344</v>
+      </c>
+      <c r="L26" t="n">
+        <v>31.94690100165576</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.39875074378122</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.88901656105269</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-30736.7377805057</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>7.865790872746857</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000080165e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8266088071396418</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1506.139</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8920093172612749</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1916.420934562103</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.898185533020791</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.51811e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-76.982</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1440046312661648</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5818661082500007</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.614685331608231</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.513492003480348</v>
+      </c>
+      <c r="L27" t="n">
+        <v>29.18670127139052</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.35648859664379</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.70422609131919</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-29952.36625244576</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>8.457144291693567</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000004047e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8267189876327405</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1483.101</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8783650847893282</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1894.55090921725</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8879355195622221</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.51943e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.14</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.04717061174936945</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6962426477528748</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.585955181025398</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.43276517004047</v>
+      </c>
+      <c r="L28" t="n">
+        <v>29.7214047661177</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.4199536652922</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.98336725996145</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-30162.5259755867</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>7.964518861375382</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8268609504714997</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1464.335</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8672509400472259</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1875.211698374165</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8788716447703998</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.5207e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.29000000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2315810190666911</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8737129437598938</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.510702469073988</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.182012128743176</v>
+      </c>
+      <c r="L29" t="n">
+        <v>30.45296193901632</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.49432150808033</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.3233059569961</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-30478.48684392136</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>6.941144296912853</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000008346e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8270277682538686</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1434.761</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8497357681084573</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1856.279733766292</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8699986375850873</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.5216e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.437</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1948243618132591</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7170322281104334</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.188964489315391</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.234167935281457</v>
+      </c>
+      <c r="L30" t="n">
+        <v>28.1796550393625</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.43294306281678</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.04172200347248</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-29548.28009746718</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>5.814395348554285</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8272128362855552</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1425.297</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8441307235683713</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1836.902530915313</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8609169567511555</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.52248e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.578</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3564582982927729</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9738072229168079</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.692213325284977</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.749505495319023</v>
+      </c>
+      <c r="L31" t="n">
+        <v>35.48587501248416</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.69212434102343</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>17.30177099962916</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-31727.57024208668</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>5.662780323457582</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8274422784139749</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1401.616</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.830105674989147</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1818.973522581262</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8525140137355421</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.52341e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-77.712</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2534407658758364</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5916940763955781</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.206825929620066</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.097144385010214</v>
+      </c>
+      <c r="L32" t="n">
+        <v>29.2297717000819</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.56174560042169</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>16.64419821914188</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-30061.4637081375</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.756763326638065</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000136e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8276841655474365</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1392.639</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8247890557122711</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1802.003980015177</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8445607518190409</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.52439e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-77.849</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3503153845720646</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.123751886717174</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.767942774096321</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.080443501320247</v>
+      </c>
+      <c r="L33" t="n">
+        <v>36.93495941832646</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.81621396371668</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>17.97758862844818</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-32328.5981546775</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.976363162115149</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000007325e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8279487310879348</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1360.371</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8056783649663396</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1785.221856585072</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8366953292459287</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.52549e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-77.97799999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.07213260358113249</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6803670196235168</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.712619851829439</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.338202816288167</v>
+      </c>
+      <c r="L34" t="n">
+        <v>43.62611715266262</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.56116836155518</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>16.64139762140234</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-29390.55095881574</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.510971312862807</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8282284202666524</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1348.013</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7983593518190041</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1766.929100297817</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8281219053389091</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.52653e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-78.114</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3514438450363402</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.7614099968617162</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.126480799921935</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.287398595663241</v>
+      </c>
+      <c r="L35" t="n">
+        <v>30.9549680883127</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.70606722612064</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17.37517029881817</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-30458.10196291071</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.437348322503112</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8285339454945814</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1333.18</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7895745223955997</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1748.495245672871</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8194823516566602</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.52702e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.23699999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6028740639987121</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6861836116186314</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.147178207744133</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.194050857629477</v>
+      </c>
+      <c r="L36" t="n">
+        <v>31.69488557103657</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.75790308421584</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>17.65357924324432</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-30643.92707375035</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.429638917270722</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.00000000000358e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8288536447033206</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1316.403</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7796383609153563</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1731.455170494808</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8114960326123943</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.5283e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.36799999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2073903397471574</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8684943637873257</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.235085901281633</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.280292783794675</v>
+      </c>
+      <c r="L37" t="n">
+        <v>32.14686701685889</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.82729542649483</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>18.04050906164337</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-31012.74184024507</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.673247179262376</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8291749244229223</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1289.453</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7636772503537207</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1716.202158753001</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.804347272006407</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.5291e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.48399999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.06791133519174512</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6143765304703964</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.469837583735835</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.952546405014778</v>
+      </c>
+      <c r="L38" t="n">
+        <v>40.40165298776852</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.68360062180015</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>17.25720336505253</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-29230.51674900182</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.3768433154416471</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.829507767945693</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1281.755</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7591181175483972</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1702.288706049236</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.797826334091613</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.52989e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-78.624</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4030431277504534</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5960450346988236</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.287878751417443</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.702405313590097</v>
+      </c>
+      <c r="L39" t="n">
+        <v>33.48814521033854</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.9144181668314</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>18.55091909327782</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-31257.84190078008</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-1.554325625237425</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000001457e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8298581761819848</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1263.034</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7480306240113143</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1684.081176200044</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7892928539945984</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.53084e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-78.748</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0215291921705341</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8857525904918987</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.995128975193394</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.624781518826493</v>
+      </c>
+      <c r="L40" t="n">
+        <v>49.5543184928886</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.87903498585916</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>18.34019303632208</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-30525.32398314323</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-1.589607719634273</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.0000000000009e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8302197522919494</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1250.145</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7403971266447494</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1670.850867208864</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7830920909372965</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.53203e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-78.881</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4723982132646455</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.017224856929306</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.329350434276381</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.276299143391189</v>
+      </c>
+      <c r="L41" t="n">
+        <v>35.07082730472803</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.02362293112694</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>19.23285604809107</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-31775.45002257308</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-3.90128988173808</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8305808911348863</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1224.865</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.725425071913835</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1652.721819376445</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7745953936841733</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.5329e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-79.012</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1363695274804358</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7788871450986161</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.762340884121442</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.887475269664472</v>
+      </c>
+      <c r="L42" t="n">
+        <v>44.75524764933483</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.88913060003294</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>18.39982963730563</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-29922.06724334456</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-3.828892562514966</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8309558658949489</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1216.396</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7204093151291784</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1639.50409408514</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7684005283380558</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.53389e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.129</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1060031320689041</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9623639413515105</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.882772455950384</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.775384402384164</v>
+      </c>
+      <c r="L43" t="n">
+        <v>52.24298591091859</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.03347136547411</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>19.29682109598957</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-31136.93196388157</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-6.202936862460206</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8313228917593165</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8297530188150996</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1769.584</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2220.269080979098</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.53124e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-74.625</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1801920256102183</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8393173089589898</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.467900516677071</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.897011830636001</v>
+      </c>
+      <c r="L23" t="n">
+        <v>26.89246783280537</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.89071615359568</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.91909343246344</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-30166.94007316015</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-11.53729863557055</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8251954356590534</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1645.954</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9301361223880869</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2071.491060440997</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9329909956353157</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.53789e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-75.79600000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.02652691608029523</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3467496334630583</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.306101189873482</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.281490483888315</v>
+      </c>
+      <c r="L24" t="n">
+        <v>26.73770044640898</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.1608278406142</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.90165119489015</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-30519.50844804617</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>6.750257072984141</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.00000000000403e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8252864880973554</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1624.189</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9178366214884404</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2035.750664935338</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9168936694995587</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.53565e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.209</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1916138106092728</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.002635331976212</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.69541612363482</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.35585643513833</v>
+      </c>
+      <c r="L25" t="n">
+        <v>38.00938769098927</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.57862696020709</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.72651918017262</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-33959.31579090837</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>8.986113295822747</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000266e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8250530874427202</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1611.416</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9106185408547999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2012.914625283793</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9066084118039126</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.53249e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-76.479</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6667620513131908</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.13615347427783</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.558056504054709</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.938892018392753</v>
+      </c>
+      <c r="L26" t="n">
+        <v>51.71403513644741</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.81806056477348</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.98804321143036</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-36290.28550049723</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>9.82938981560585</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000171e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8249425961151271</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1572.867</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8888343249034802</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1993.985555388656</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.898082837107899</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.53002e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-76.69499999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2509806960501849</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6303373967366028</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.189991576524773</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.230030849991817</v>
+      </c>
+      <c r="L27" t="n">
+        <v>32.10123922334103</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.53586969744448</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.51957148521605</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-32714.96106571314</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>9.264967287219861</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000005195e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8249900597356645</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1571.369</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8879877982621904</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1970.601161788014</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8875506030642984</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.52852e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-76.88200000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.9773197322887962</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.261542882318882</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.341347683936883</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.148338173970164</v>
+      </c>
+      <c r="L28" t="n">
+        <v>56.65936494051753</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.94878174546064</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.76024640031629</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-37110.33527682364</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>10.31586079299746</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000486655e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8251202635819013</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1540.72</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8706679083897685</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1951.23678123384</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8788289662500638</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.52785e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.05200000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5367234467856273</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.072882720097479</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.895963325935674</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.600027398843837</v>
+      </c>
+      <c r="L29" t="n">
+        <v>45.59247811833898</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.87770306304131</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.33235389766648</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-35776.91518777932</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>9.396285568217763</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8252998589228745</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1523.677</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8610368312552557</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1929.663187937989</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8691123091652667</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.52729e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.212</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.317386472600338</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.068921856582534</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.680452373574527</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.971917522759614</v>
+      </c>
+      <c r="L30" t="n">
+        <v>39.63199549800601</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.84706650513631</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>18.15386642125246</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-35000.37010581527</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>9.738855860928766</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8254979992962646</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1503.217</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8494747918154777</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1914.091177762831</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8620987402656403</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.5272e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.36499999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4509203318924647</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.914255683905449</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.651544009852143</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.110013865780466</v>
+      </c>
+      <c r="L31" t="n">
+        <v>40.4382655462739</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.90282034536423</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.48131784129867</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-35287.14975881372</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>8.180013380923469</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000109261e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8257033486524447</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1481.863</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8374075488928471</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1892.7909388422</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8525052008594893</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.52684e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-77.50700000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2447465250465831</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5276828962240485</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.335563245290159</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.508110204517596</v>
+      </c>
+      <c r="L32" t="n">
+        <v>35.96843208271671</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.86137687425156</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>18.23680487197554</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-34407.43105320478</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>8.927997550263058</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000429e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8259341023867339</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1465.444</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8281290970081104</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1874.044186797946</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.84406174136854</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.52707e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-77.657</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2947751144627036</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6058344562378516</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.263029464626446</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.429218489871278</v>
+      </c>
+      <c r="L33" t="n">
+        <v>36.84529562467973</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.91743783836387</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18.56912670160928</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-34705.3107485142</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>8.740672786944629</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8262020762927021</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1445.193</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8166851644228249</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1858.354384897174</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8369951195634688</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.52718e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-77.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3909943412414645</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7338519648944231</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.454334862191505</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.917137437768965</v>
+      </c>
+      <c r="L34" t="n">
+        <v>37.71961080006641</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.95814273549837</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>18.81808817874004</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-34809.40230175739</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>6.818492686523655</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000122232e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8264990874504575</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1425.42</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8055113518205409</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1839.686709950199</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8285872760696782</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.52771e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-77.955</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.311509654026523</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8079733326397429</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.684933848340813</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.749402605756793</v>
+      </c>
+      <c r="L35" t="n">
+        <v>38.75544178424765</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.00304408435548</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.1005533340824</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-34976.81278903653</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>6.23602445740255</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8268283521545878</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1404.177</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7935068355048418</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1823.297078483478</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8212054539260786</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.52781e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.09</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2829165222740225</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9387506862166443</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.668597414829905</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.884688303713231</v>
+      </c>
+      <c r="L36" t="n">
+        <v>39.50877383454537</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.04276874533961</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>19.3575976773984</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-35072.03224711869</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.32196039973303</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000005796e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8271788112347632</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1390.899</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7860033770648922</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1803.814885967381</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8124307550920501</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.52811e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.22499999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4279143569390065</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5565234833939996</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.541323358907429</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.990274379990816</v>
+      </c>
+      <c r="L37" t="n">
+        <v>40.45841648378202</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.09344548909095</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.69569882429078</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-35328.71272590429</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.118849873102818</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8275372123783906</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1376.801</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7780365328800442</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1784.491422717651</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8037275472622999</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.52868e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.369</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4960560544405491</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.289551303158387</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.136175569799037</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.365018809311994</v>
+      </c>
+      <c r="L38" t="n">
+        <v>47.59883504618947</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.23894294840383</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>20.73532716721984</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-36897.20660805568</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.845458510158892</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8278950204766552</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1351.382</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7636721398927658</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1766.350943767254</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7955571506622637</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.52882e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-78.51000000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1351890199679069</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.016811985602027</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.091682274277697</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.804691196863292</v>
+      </c>
+      <c r="L39" t="n">
+        <v>42.19934442486388</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.17351607895897</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>20.25459736760367</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-35564.23592944665</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.114463504345508</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000346e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8282612677417099</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1338.642</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7564727077098348</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1750.078156183848</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7882279545198616</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.52934e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-78.65300000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5099623627577058</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9182516642162626</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.640542615174507</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.974601823056653</v>
+      </c>
+      <c r="L40" t="n">
+        <v>42.89551335266252</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.22612169028926</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20.63933666687459</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-35864.19313921292</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.045311214878666</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000003194e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8286278357126966</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1312.019</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7414279288239497</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1733.449021873927</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7807382612874595</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.53015e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-78.792</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.09914873155188095</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.4330389528465312</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.542463069421675</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.344261144732145</v>
+      </c>
+      <c r="L41" t="n">
+        <v>39.23390355961232</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.14887220293056</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.0792400701859</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-34407.53095909335</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-0.5230051962693096</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000001523e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8290005492378028</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1291.17</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7296460637076285</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1713.761487285293</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7718710772342764</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.53017e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-78.914</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1945374400380215</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7858199823204817</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.028605367811144</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.778542340618885</v>
+      </c>
+      <c r="L42" t="n">
+        <v>62.53606866656896</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.1156343712935</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>19.84747339109529</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-33569.69663751725</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-0.621031457994718</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8293730125661111</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1281.491</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7241764166041285</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1697.851084534714</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7647050977199541</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.53087e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.059</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1807140068647638</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9691180518124376</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.875278098436351</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.165418035876983</v>
+      </c>
+      <c r="L43" t="n">
+        <v>45.89279931207455</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.35126644074171</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>21.6159746562087</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-36339.8189413394</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-2.411902702996827</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8297530188150996</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.00000000000012e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8277414423943498</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2178.327</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2681.324546120289</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.5001e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-70.41200000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2178094390026852</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.579598051157125</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.347343251859648</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.991102803738245</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.13765766583666</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.19046246294992</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.82854326502509</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-24997.43137088413</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-42.46271796517931</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000181e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8258388708884479</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1900.605</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8725067448551111</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2336.880669531922</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8715396548743956</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.54464e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-73.14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2031715103409918</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9477794160965117</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.686984166233768</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.027621698722696</v>
+      </c>
+      <c r="L13" t="n">
+        <v>23.81224853521792</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.28715285424678</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.12992942070545</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-27565.46982795976</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-7.876422034118377</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8265687249403512</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1836.41</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8430368810559662</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2240.82146498625</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8357143741620461</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.54627e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-74.203</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2641956650395271</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8302785451606841</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.975736698305918</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.187621221848168</v>
+      </c>
+      <c r="L14" t="n">
+        <v>31.51938106155979</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.80846979182415</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.64502420854157</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-30145.25553207761</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.012932873968566</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8265884527879066</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1798.322</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8255519029053028</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2198.865107558584</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8200667504947157</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.54211e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-74.762</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2295164204649512</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.00616242414245</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.889171803704261</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.402527621983111</v>
+      </c>
+      <c r="L15" t="n">
+        <v>36.91859604907683</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.05945880664815</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.51714644016701</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-31587.87185633738</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6.316519627888056</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8265766186621232</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1759.257</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.807618415416969</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2163.613037377592</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8069194907823471</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.54191e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-75.22199999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1256973254048485</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7692802743076637</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.838299579266176</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.679565167381093</v>
+      </c>
+      <c r="L16" t="n">
+        <v>34.3280694541386</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.11307700200918</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.71803192158183</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-31474.98355327969</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.604012583426538</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000003255e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8266483033213513</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1735.943</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7969157064113881</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2131.490849212171</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.794939520579971</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.54119e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-75.56</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3900544419199495</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.233916613513748</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.274215194199154</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.53929771433787</v>
+      </c>
+      <c r="L17" t="n">
+        <v>47.76445268272009</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.35285388353074</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.68853310686682</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-33203.45057500096</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8.150127662421937</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000745e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8267952413704284</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1700.435</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7806151234410628</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2101.367822991493</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7837051378327337</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.54148e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-75.866</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1033303887548405</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9315123319930231</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.785893231407031</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.835390709562708</v>
+      </c>
+      <c r="L18" t="n">
+        <v>39.55742931302856</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.33888110495191</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15.62849495479089</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-32524.18541169792</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7.603064140563674</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.21800867779173e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8153662182863143</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1677.745</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7701988728046798</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2072.036322270123</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7727659545235701</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.54227e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-76.111</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4442439458367829</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9774636523192359</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.900375628405256</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.621944916236063</v>
+      </c>
+      <c r="L19" t="n">
+        <v>54.57605873390234</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.54551968335916</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.56583090095285</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-34119.53825081394</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7.180453590135812</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000267e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8271923041919251</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1648.179</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7566260712923266</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2040.515132658883</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7610101267343345</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.54354e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-76.369</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4929539753827957</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.152963934241642</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.035337931022544</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.767788394829134</v>
+      </c>
+      <c r="L20" t="n">
+        <v>59.02001720643462</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.63348124091696</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.99970595654379</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-34552.01601601497</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>8.420977447183986</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000002425e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8274572559379482</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1610.714</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.739427092442962</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2013.409205144679</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7509009709615188</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.5438e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-76.583</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1610144074664977</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6465140278659557</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.213670559821654</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.60206611131509</v>
+      </c>
+      <c r="L21" t="n">
+        <v>36.88207102180518</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.44959084298355</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16.11713549845106</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-32136.09250418279</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.689414499059353</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8277414423943498</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>1.000000000000006e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.831892729535577</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1764.862</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2201.022627793749</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.55122e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-73.96299999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.343244108179024</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.170537229285486</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.728661101182546</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.254400102491897</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.849220500133</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.4708409920854</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.62406292981802</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-27105.56415712392</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-14.56810625955154</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000419e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8269099999641284</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1641.607</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9301616783635208</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2053.032702104983</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.932763105740032</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.54604e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-75.68300000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.09405656314112094</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6759690630915296</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.413615112024564</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.381917775512362</v>
+      </c>
+      <c r="L24" t="n">
+        <v>27.52172227402621</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.05000010707244</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.48227357692545</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-29385.84419624559</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.794907429778505</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8271180947318536</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1610.878</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9127501187061652</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2011.876196299669</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9140642948847484</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.5459e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.233</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2975143819293747</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9937159720115946</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.726695406741832</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.111951068656441</v>
+      </c>
+      <c r="L25" t="n">
+        <v>37.63415879425644</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.42140310113929</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.98985786581498</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-31996.78182317718</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>7.342718849045127</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000015418e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8270087841248112</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1587.512</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8995105566327567</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1983.024612015455</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9009560315166731</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.54624e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-76.518</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1338677250870446</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.113558802404923</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.853608714771259</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.105258843879832</v>
+      </c>
+      <c r="L26" t="n">
+        <v>40.52170442952787</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.56204422563872</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.64564743187884</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-32934.34229431956</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>9.18241429803038</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000057924e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8269396847626918</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1556.887</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8821579250955599</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1962.143491606978</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8914690230030859</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.54669e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-76.70999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.09486613269935072</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7709446144972689</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.543080741583905</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.927732674784138</v>
+      </c>
+      <c r="L27" t="n">
+        <v>35.45556063195478</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.51364633659323</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.41401149195075</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-32047.95423730018</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>8.661831374726489</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000274e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.826894879562493</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1539.989</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8725832388028073</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1943.755496264282</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8831147266362521</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.54689e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-76.892</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2059889110799717</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8203002462826183</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.542490154682773</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.682035734203371</v>
+      </c>
+      <c r="L28" t="n">
+        <v>37.21257938312691</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.59770310977548</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16.82052486067492</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-32526.56197133243</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>7.311922394327212</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8269644167517142</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1511.447</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8564108695184101</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1922.339088520239</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8733845187439733</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.54753e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.045</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.06303532466437811</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6014548418497445</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.272114318500783</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.350095472693655</v>
+      </c>
+      <c r="L29" t="n">
+        <v>33.13941568566664</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.52518866776535</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.46866874225862</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-31434.63661951823</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>7.919161808558897</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000143e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8270838825182354</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1493.047</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8459851251825923</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1902.338292081431</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8642974715749688</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.54803e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.20399999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3188553373832474</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7285232382870646</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.522897906501201</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.296334669115968</v>
+      </c>
+      <c r="L30" t="n">
+        <v>33.9281509626128</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.60289325858444</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.84628396645909</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-31850.46018202034</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>7.714735602516157</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000265015e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.827259533955124</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1487.687</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8429480605282453</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1885.773851488714</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8567716786169381</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.54834e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.358</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3400186619084299</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.330540225779815</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.221899365461815</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.463382798537753</v>
+      </c>
+      <c r="L31" t="n">
+        <v>48.14014036384618</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.89942277969941</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.46102676625255</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-34772.73658822454</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>5.958688223407762</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8275119222540035</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1458.771</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8265637766578917</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1865.988393289999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8477824669891832</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.5487e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-77.506</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2121515769327901</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9506481374953056</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.148694459376462</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.634505929817847</v>
+      </c>
+      <c r="L32" t="n">
+        <v>35.50976064383462</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.73429990381979</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>17.52571243868437</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-32495.99702496241</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>5.898448236560739</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8278024218732957</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1437.555</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.814542440145462</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1846.381354663471</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8388743174867942</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.54927e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-77.679</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.09489999484065412</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4311979777969741</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.190339657586836</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.099742607596265</v>
+      </c>
+      <c r="L33" t="n">
+        <v>32.76931080055596</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.67873190410205</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>17.23184902886677</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-31530.90224453312</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>5.667888199008075</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000032092e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8281110816190586</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1413.471</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8008960473963405</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1830.118818516951</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8314856900637214</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.54918e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-77.82299999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.007234616303934139</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.3586948838538097</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.158081667695954</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.026069947177137</v>
+      </c>
+      <c r="L34" t="n">
+        <v>33.11977045828908</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.71155560266718</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17.40423320332699</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-31509.52581457571</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.744186381294753</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000099046e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8284451324124779</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1406.915</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7971813093601653</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1810.671282684107</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8226500081460226</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.54987e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-77.97799999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4581958408014727</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9793960053568523</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.528639437143441</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.915934468164805</v>
+      </c>
+      <c r="L35" t="n">
+        <v>44.70218133334625</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.99640089905161</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.05823060454423</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-34341.29255935515</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.119701937167406</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000566e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8287898612707991</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1388.66</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7868377244226461</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1788.980449425839</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8127951193391727</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.55014e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.126</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3645261053263743</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.09889366822235</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.846404053311056</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.261631878503264</v>
+      </c>
+      <c r="L36" t="n">
+        <v>45.46974460640434</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.05216231562386</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>19.41939204928792</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-34612.01789997334</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.576192582207227</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000035747e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8291597473511912</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1371.678</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7772154423405343</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1773.741959108779</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8058717510263559</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.55091e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.28</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2833758296267709</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.063099600661028</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.748898640851663</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.212672966300171</v>
+      </c>
+      <c r="L37" t="n">
+        <v>46.58390217819283</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.11243818638889</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.82546743512302</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-34961.10598432533</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.584327924042555</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8295226583781842</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1341.192</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7599415705023963</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1753.887664355158</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7968512645929551</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.55166e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.422</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1069776460038319</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6549158647336614</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.248227903487882</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.143663960820237</v>
+      </c>
+      <c r="L38" t="n">
+        <v>36.71814939995072</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.94054213592946</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>18.70962627575569</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-32462.68281610273</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.134187090397972</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000742e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8299037479201862</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1334.44</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7561157756243831</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1735.898129141071</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7886780023161746</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.5523e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-78.58</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.451997019423848</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.614050214777665</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.892888247249612</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.001089913411422</v>
+      </c>
+      <c r="L39" t="n">
+        <v>49.2343906052411</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.21101859249019</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>20.52739369706097</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-35418.1106533694</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.2550350834720803</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000006193e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8302911440284173</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1315.413</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7453347627179916</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1721.295733927795</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7820436338054279</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.5529e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-78.72499999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6044503028590926</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.323328430231166</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.822285498022811</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.222901477932556</v>
+      </c>
+      <c r="L40" t="n">
+        <v>51.28419153259743</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.24260243608222</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20.76288873458724</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-35432.79796440994</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-2.434156070946983</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000007964e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8306843462999087</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1293.375</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7328476674096899</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1701.463793602146</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7730333037546514</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.55332e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-78.873</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5541436089126346</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.636319352510031</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.657314220910577</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.943464659977168</v>
+      </c>
+      <c r="L41" t="n">
+        <v>45.44192702396482</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.20445645515159</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.47913229735686</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-34469.82774745971</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-2.838215459375419</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8310789482890005</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1263.856</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7161217137657224</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1682.270617683656</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7643131862619347</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.55423e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-79.024</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2149127891263654</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7512461198576351</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.858646667509359</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.616144574427232</v>
+      </c>
+      <c r="L42" t="n">
+        <v>67.55876472164553</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.02346503572944</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>19.23183397047734</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-31823.6538609025</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-3.151851900472593</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8314747356605672</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1247.206</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7066875483748871</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1667.425979359357</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7575687584051527</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.55471e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.157</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1379931430981599</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.918518666343635</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.9719984875297</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.704651795419183</v>
+      </c>
+      <c r="L43" t="n">
+        <v>69.6065199889767</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.08180461592221</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>19.61699616315311</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-32106.82479283401</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-5.409355196167894</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.831892729535577</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8271394971160694</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2122.309</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2609.18186604179</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.51828e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-70.357</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2216122307157797</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4412849162011018</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.528965517241383</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.753553038104981</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.5848113692186</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.06997857984675</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.627461124910004</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-23988.67161412517</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-34.39201480362067</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000491e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8253028516832255</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1885.563</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8884488545258959</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2326.204355648149</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.891545501646872</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.5463e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-73.116</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1088632306231208</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3916728236613677</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.612239523520143</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.688816192147043</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20.73098717059535</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.14728109852139</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.77869834955354</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-26656.46554165931</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-4.275092230749806</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000023e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.825870838465928</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1833.062</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8637111749514326</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2241.383977891543</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8590370824904558</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.54451e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-74.128</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.41852182547271</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7362285884925156</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.863180192457629</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.348382381368683</v>
+      </c>
+      <c r="L14" t="n">
+        <v>30.60692549954295</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.78090769053057</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.55556535748099</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-30015.88560368071</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.821500413588183</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.82590012173334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1798.479</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8474161868040891</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2200.920363558174</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8435289207712604</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.53886e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-74.675</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4119777516375659</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.042900854376783</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.018802145562122</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.488049043319196</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35.32855949190218</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.03689023723601</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.43421418648794</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-31510.32553480652</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8.987258801887037</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000001307e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8259081854434839</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1755.353</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8270958658706153</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2169.969321578445</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8316665656083057</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.54082e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-75.134</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.05512496199842216</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.429849780111535</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.239506887239859</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.5505126600295</v>
+      </c>
+      <c r="L16" t="n">
+        <v>28.61514969011886</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.95668707320529</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.14697252989372</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-30286.84957451514</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9.203123109947683</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.00000000000009e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8259859256404509</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1744.804</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8221253361315435</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2137.681901784232</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8192920277447588</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.54129e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-75.452</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3304586722413748</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.017652937610361</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.077607849190506</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.526871145307404</v>
+      </c>
+      <c r="L17" t="n">
+        <v>46.3782470482157</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.34013489689221</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.63386354372579</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-33262.27268777401</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>10.44872922941659</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.82614900257313</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1720.706</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8107707218882828</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2110.509865905611</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8088780216410595</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.54278e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-75.73099999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3880203045684867</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.195115332428903</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.688817204301153</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.073964832671592</v>
+      </c>
+      <c r="L18" t="n">
+        <v>28.17519798686017</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.581193104094</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.73910392781817</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-35276.91877928114</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>9.25990733387107</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.215077235745217e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8146841725410688</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1678.333</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7908052032008533</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2079.755049068187</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7970908720990153</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.54435e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-75.974</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.06931278845621631</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8534380006500225</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.606057007125864</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.008285753828983</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40.82871013427115</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.36678670884372</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.74885878059033</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-32521.82245420742</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>9.370607425677008</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8266126128866734</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1656.884</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7806987578151908</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2051.168421524883</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7861347069058738</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.54613e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-76.20099999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3675462602126122</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.087407004741156</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.177479896442853</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.195114678432455</v>
+      </c>
+      <c r="L20" t="n">
+        <v>42.05196782341935</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.46740804464203</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.19863283205609</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-33030.03958684207</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>9.190929045563507</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000721248e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8268687985707787</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1638.843</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7721981106427009</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2024.341915389996</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7758531291883404</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.54794e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-76.40600000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6013967672703947</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.397486766518532</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.33420676087883</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.761883474509469</v>
+      </c>
+      <c r="L21" t="n">
+        <v>58.59438551615129</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.66742351906323</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.17324502233394</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-34703.40742953988</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>9.636348095315725</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8271394971160694</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>1.000000000000671e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8326683780320826</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1718.342</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2149.151485106405</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.55451e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-74.03</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1461101091074448</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9255509875273277</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.76166963436632</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.790784098875858</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20.10709059263578</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.26503803742386</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.07301918239592</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-25360.25761020574</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-8.762618706733747</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8272098373655483</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1610.434</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9372022565938564</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2028.656513876709</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9439337003162761</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.54978e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-75.67700000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.08755284990593351</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6342144965496943</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.162328698122521</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.021326505918887</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23.96118726412003</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.85756892798655</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.80733014501527</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-27619.29941574144</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>5.445910869217073</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8273663063473612</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1592.685</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.926873113734053</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1989.415083430937</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.925674666126404</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.54721e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.22799999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3242874798871323</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8462575621109579</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.722481243399608</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.025226734126893</v>
+      </c>
+      <c r="L25" t="n">
+        <v>35.08678122639542</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.37244468159501</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.77348852016064</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-31237.97154215303</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>7.283348624220025</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8273605829591431</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1556.143</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9056072656083598</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1960.592690395986</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9122636091419661</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.54876e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-76.506</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.09819420241169272</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.916010130570728</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.506116735416825</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.829548226454254</v>
+      </c>
+      <c r="L26" t="n">
+        <v>32.30489660578142</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.36967910136703</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.76144008498152</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-30741.488300718</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>8.44255843764995</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000058e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8273413122080273</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1535.808</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8937731836852036</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1940.14084478889</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9027473671511959</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.55017e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-76.723</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1304772911869604</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7558626420622401</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.757614335514852</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.798639819763188</v>
+      </c>
+      <c r="L27" t="n">
+        <v>33.85140945906273</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.46644118551589</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.19418927705247</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-31255.29273366674</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>7.323282675475639</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8274043718995371</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1514.839</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8815701414503052</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1917.036868395046</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.891997088934907</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.55111e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-76.899</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2037572059711193</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7677133838948107</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.944534349645895</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.721832615290086</v>
+      </c>
+      <c r="L28" t="n">
+        <v>34.95228437943943</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.52047740049771</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16.44631538686392</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-31403.74141723057</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>7.882373789602184</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000011329e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8275555910164117</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1506.431</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8766770526472613</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1897.476244697544</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8828955324215311</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.55234e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.06699999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7001713863672027</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.465220578625757</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.060473649001391</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.913781177572388</v>
+      </c>
+      <c r="L29" t="n">
+        <v>54.51352189543636</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.82391415134171</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.02126371719265</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-34287.76684967094</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>6.979701947252011</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000012003e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8277479681036791</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1483.257</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8631907967098517</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1878.275782974499</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8739615592436961</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.55307e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.205</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5928028324336824</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.202176888437066</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.313450300382262</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.283741254977389</v>
+      </c>
+      <c r="L30" t="n">
+        <v>43.98469708685295</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.7647900908143</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>17.69123984545906</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-33225.87018089015</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>7.065605207112981</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000221e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8279835716156516</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1454.908</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8466929167767534</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1860.549672893721</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.865713601757395</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.55378e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.34999999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1544710366806198</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.5938928252737448</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.445974017913367</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.493430898708846</v>
+      </c>
+      <c r="L31" t="n">
+        <v>33.09154711779961</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.59667715992504</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>16.81544228231631</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-31091.60252052121</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>6.331221299764252</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000010251e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8282531796466067</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1434.402</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8347593203215659</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1847.549879775284</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8596647991445847</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.55444e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-77.48999999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1207446667834743</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7505893949850109</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.411430493443546</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.491364102943404</v>
+      </c>
+      <c r="L32" t="n">
+        <v>33.70999383301645</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.63710266218561</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>17.0180547001853</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-31158.69792909854</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.500424208046638</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000005637e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8285636792480321</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1417.292</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8248020475551433</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1825.904911042428</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8495933970666695</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.55496e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-77.63500000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2382856874445066</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7845834872993026</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.375496453670586</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.630155984089924</v>
+      </c>
+      <c r="L33" t="n">
+        <v>34.52561284823814</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.67237945162864</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>17.19887942365197</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-31181.09533649846</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4.305005637738304</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8288912003939648</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1404.086</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8171167322919418</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1808.238743540228</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8413733308569922</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.55583e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-77.76300000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2161550193640273</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6808942719817035</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.518387307861929</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.620584041759896</v>
+      </c>
+      <c r="L34" t="n">
+        <v>34.86415408509932</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.72741549520923</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17.48876422553271</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-31400.85391835023</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.934928387333571</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000859348e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8292267556824336</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1389.497</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8086265714275739</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1791.791384662858</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8337203761949546</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.55627e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-77.914</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3519499866584619</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.245911089930424</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.939230368150182</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.07381031396449</v>
+      </c>
+      <c r="L35" t="n">
+        <v>41.26069740994348</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.87501756284391</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>18.31656847015248</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-32649.95671846926</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.608622072859589</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8295688023830374</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1361.281</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7922060916860557</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1775.088215760568</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8259483931504638</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.55733e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.05800000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.07452943411675268</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5958709236379094</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.463868408600154</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.117434689885117</v>
+      </c>
+      <c r="L36" t="n">
+        <v>32.84097566787658</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.72566485057003</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>17.47939337060038</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-30680.44679676006</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.572561063981993</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000128576e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8299283596411257</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1348.774</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.784927563895895</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1756.382451908624</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8172446028492335</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.55792e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.18300000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2162934815568205</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7801161098374505</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.262194641201849</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.792309374735803</v>
+      </c>
+      <c r="L37" t="n">
+        <v>36.99726855151574</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.86596343878402</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>18.26354729329279</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-31811.78809521202</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.013011426792445</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000433062e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8303118633528034</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1324.518</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7708116312119474</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1737.451493222428</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8084360294111173</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.55865e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.342</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.07838058010472888</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8690599988315624</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.077133002665275</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.415511587012869</v>
+      </c>
+      <c r="L38" t="n">
+        <v>52.95001699589514</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.72961676194363</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>17.50056139447045</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-30004.38342051718</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.249738900504781</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000049399e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8306920563252771</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1321.127</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7688382173048206</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1723.758141651321</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8020645141103105</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.55936e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-78.471</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.7657535266191636</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9444762159669153</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.737976854215695</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.223350250879815</v>
+      </c>
+      <c r="L39" t="n">
+        <v>44.52741998391706</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.08194290508197</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>19.61792743862667</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-33555.57762910577</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-1.972187524784886</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.00000000000546e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8310744570390908</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1298.433</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7556313004046925</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1703.119588231958</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7924613969906527</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.55983e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-78.61799999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.05719654924308014</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9614640309811299</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.688993750298643</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.805198497840451</v>
+      </c>
+      <c r="L40" t="n">
+        <v>40.0761260394243</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.01667204533068</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>19.18796441125966</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-32377.09633251138</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-0.8661948927830281</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8314681343215892</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1286.323</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7485838092766167</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1688.370031407389</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7855984294768301</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.56098e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-78.746</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.7672995505878822</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.315655812727029</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.914459961870544</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.969941266394154</v>
+      </c>
+      <c r="L41" t="n">
+        <v>47.50383804629146</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.17222440948095</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.24533045520981</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-33903.54393270001</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-2.812381528552351</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8318499840812067</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1261.093</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7339010511295191</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1666.8930536347</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7756051935781395</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.56129e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-78.889</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4211083111009665</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9890083215020519</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.348875997099359</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.540133000461447</v>
+      </c>
+      <c r="L42" t="n">
+        <v>37.48063718076545</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.02268624965933</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>19.22679437068009</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-31673.88839292728</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-2.054262978217025</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.00000000000018e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8322595460561064</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1249.709</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7272760602953312</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1654.848513724342</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7700008702003666</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.56205e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.03100000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.555720480451233</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.097788605435654</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.07194101906383</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.654305533411074</v>
+      </c>
+      <c r="L43" t="n">
+        <v>42.94122329417656</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.15910525370883</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.15168585893034</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-32912.49848217268</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-5.510375744933185</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000671e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8326683780320826</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1.000000000007784e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8263403127084581</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2088.844</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2625.610990644247</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.50818e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-70.142</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1994732221246743</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4240167364016407</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.079463087248373</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.925574425574501</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.20417438251172</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.63503772770461</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.964686566517837</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-22177.92908583114</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-51.38062061704886</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8235389366040871</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1829.747</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8759615366202549</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2250.651245993478</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8571914323992202</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.55608e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-73.051</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2622679870036993</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.016160416102168</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.788669679446209</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.17922075762824</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.13064877003294</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.08997401163158</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.64056039767696</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-25873.60345906585</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.494043254926282</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8244098618608863</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1760.926</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8430146052074735</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2171.858845911627</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8271822648711251</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.55542e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-74.208</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1143068595357596</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7021589890325559</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.649448064829402</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.659569678833181</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.40533902646196</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.58355515337779</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.94757686828144</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-27929.11952677896</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>10.81281782344377</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000040485e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8246569878850278</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1727.173</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8268559069035312</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2135.434942055817</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8133097209239839</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.55174e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-74.773</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2233731826437387</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8129367396499096</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.532466627612913</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.745975177693677</v>
+      </c>
+      <c r="L15" t="n">
+        <v>27.60463979360149</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.82559054158641</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.70118710416935</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-29087.00570661683</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>10.6190759251549</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8248754942505564</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1702.897</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.815234167798074</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2106.218886788301</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8021823850880123</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.5523e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-75.238</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4380111507411761</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.946503896128835</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.92824690192442</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.485927688346285</v>
+      </c>
+      <c r="L16" t="n">
+        <v>38.92421143006025</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.14632727722568</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.84541089672301</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-31185.3822423091</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9.706808726068857</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000004894e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8250863204450599</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1673.924</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8013638165415895</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2070.405974243359</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7885425455715902</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.5533e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-75.584</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5291467156942083</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.214637296781612</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.109369487088906</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.552529062637802</v>
+      </c>
+      <c r="L17" t="n">
+        <v>42.98317447967308</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.27191915962126</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.34701108456082</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-31797.22813634483</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>12.20701059405928</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.00000000003441e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8253742726708515</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1653.709</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7916862149590874</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2043.154020924106</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7781632649331562</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.55459e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-75.905</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.390505359877544</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.075877192982474</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.164421768707504</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.328760226557464</v>
+      </c>
+      <c r="L18" t="n">
+        <v>27.14922839133954</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.52124993113947</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.44997663615734</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-33745.74401886032</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>11.38204411523873</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000001441e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8256439566405775</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1616.318</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7737858834838791</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2013.841199695326</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7669990744520722</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.55649e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-76.117</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5474835973437139</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9829253819042763</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.53047991584094</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.143740725676562</v>
+      </c>
+      <c r="L19" t="n">
+        <v>38.07220227551741</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.33751659904978</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.62265647296377</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-31401.60645278211</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>10.79851577138322</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000035413e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8258872042344967</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1582.14</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7574237233608637</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1985.851826680532</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7563389373965346</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.55979e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-76.375</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2830498359356353</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8907599945364864</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.430817859905218</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.439799492199469</v>
+      </c>
+      <c r="L20" t="n">
+        <v>33.86999757282</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.29157954390369</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.4286035577321</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-30527.16340045061</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>11.21737917692383</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000444e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8261096052838799</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1552.786</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7433709745677514</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1962.85797460527</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7475814130880228</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.56226e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-76.55</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.06429706158882542</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5985893896577428</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.326524792841036</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.461093294971591</v>
+      </c>
+      <c r="L21" t="n">
+        <v>30.0707324088152</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.24885512448218</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.25238180311318</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-29729.4956525476</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>9.668242438808875</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000007784e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8263403127084581</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>1.000000000000025e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8304928078988155</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1679.799</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2120.461756812334</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.57138e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-74.10599999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.4823709767576</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.40656131877337</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.294128228737363</v>
+      </c>
+      <c r="L23" t="n">
+        <v>19.29497651818394</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.24095623139149</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.01164730377898</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-25001.69081116027</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-4.221865322661415</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000002177e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8253812966683933</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1600.857</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9530050916806118</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2008.74718269297</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9473159212796634</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.56059e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-75.765</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3522347977594464</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.066168652087228</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.999465210836017</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.939323133232163</v>
+      </c>
+      <c r="L24" t="n">
+        <v>31.8984182178854</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.16521386443776</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.91874600207334</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-29924.88177488731</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>9.424902129772363</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000281e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8255742954399388</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1556.955</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9268698219251231</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1971.453100896054</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.929728204039726</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.55947e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.163</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2036626582116553</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3621534504698898</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.352183001761373</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.326520435890985</v>
+      </c>
+      <c r="L25" t="n">
+        <v>26.7646908631733</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.1224753536069</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.75381506966897</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-28957.73037579245</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>11.17422025657947</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000146725e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8255850427780846</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1547.604</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9213030844761783</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1948.00942781194</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9186722757690099</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.56151e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-76.396</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3079486906682764</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.134881203967945</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.133469796988982</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.025067970069523</v>
+      </c>
+      <c r="L26" t="n">
+        <v>37.37423936498105</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.46458198322632</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.18565145398889</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-31609.43672057775</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>10.92563955078231</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000152916e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.825630742229314</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1528.567</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.909970180956174</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1930.508814744645</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9104190672350331</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.56145e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-76.548</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8952941362593415</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.046172783536006</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.730912800668669</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.179552300981663</v>
+      </c>
+      <c r="L27" t="n">
+        <v>37.74461990416287</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.50419148557604</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.36950782869518</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-31639.7050943957</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>8.599996472341672</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000029e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8257774838069417</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1502.115</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8942230588302529</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1908.673260205914</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9001215202650958</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.56295e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-76.739</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3286553828928107</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.891791050443983</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.969828173078912</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.632240784608492</v>
+      </c>
+      <c r="L28" t="n">
+        <v>33.80572169469745</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.47439655625823</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16.23082347670283</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-30998.9395754244</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>10.97330345770308</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000006521e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8258596233710385</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1476.099</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8787354915677411</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1891.340063845219</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8919472646790144</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.56656e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-76.812</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1851896961456174</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4668496937274058</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.18122305904035</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.879880773385925</v>
+      </c>
+      <c r="L29" t="n">
+        <v>27.09548274502991</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.30722350466797</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>15.4941473154193</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-29165.0548599034</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>10.22448910541038</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000014658e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8259844762401788</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1461.996</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8703398442313635</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1874.193333695686</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8838609456994589</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.56748e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.02200000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0524435247607746</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7946072852291249</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.668789267608288</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.434991236314748</v>
+      </c>
+      <c r="L30" t="n">
+        <v>31.46587944301125</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.49018023772855</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.30399774858492</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-30472.43202429854</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>8.750889477633564</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000355e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8261797601106761</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1448.296</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8621841065508433</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1854.836451836959</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8747323293513736</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.56694e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.178</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3019451430327393</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.205121021963245</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.571007605126333</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.940788271314906</v>
+      </c>
+      <c r="L31" t="n">
+        <v>36.39970424869411</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.66014286444735</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>17.13572389088087</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-31800.16477470212</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>8.64544039522923</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000075e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8263988533012309</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1428.58</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8504469880027312</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1837.898920857167</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8667446677369269</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.56884e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-77.30200000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.252350930539006</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9873278202913608</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.683071971839047</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.807774279191396</v>
+      </c>
+      <c r="L32" t="n">
+        <v>36.99355517790342</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.71182300552242</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>17.40565167238079</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-31994.03138025086</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>7.288620994003281</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000142e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.826646192193352</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1400.32</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8336235466267095</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1819.008064593527</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8578358269134834</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.56939e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-77.459</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1237183724847317</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4227633001373961</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.172209744714361</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.092448736070843</v>
+      </c>
+      <c r="L33" t="n">
+        <v>30.22918929331317</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.53389226853824</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>16.51012398774608</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-29867.56232307294</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>7.063758574675148</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000003696e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8269100335493037</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1393.618</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8296337835657718</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1801.713622881158</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8496798478410917</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.57091e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-77.634</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1436135170764348</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.4576877683566348</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.457895047829971</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.695440702515718</v>
+      </c>
+      <c r="L34" t="n">
+        <v>34.51073339502064</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.72309669613963</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17.46566464517314</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-31383.62879914522</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>6.246500320703831</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000847e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8272045140411995</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1372.41</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8170084635125989</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1783.572349547521</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8411245068756837</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.5723e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-77.798</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.124310309935976</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6076091671486561</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.23562149662447</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.404716404455512</v>
+      </c>
+      <c r="L35" t="n">
+        <v>35.90034311547598</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.77244950582413</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17.73331282166365</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-31538.11576055409</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>5.587364605328503</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000002522e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8275311280678673</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1355.007</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8066482954210593</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1767.964994375872</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8337641500470321</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.57241e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.008</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3172758958305833</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7744531895494953</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.316187805856388</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.635200362016866</v>
+      </c>
+      <c r="L36" t="n">
+        <v>37.89010605348048</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.8254226228315</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>18.02984448720051</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-31728.96189146264</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.748734417774926</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000456e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8278656786794472</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1334.625</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7945147008659965</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1750.343969051756</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8254541556472245</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.57271e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.072</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.189432656286483</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8023910362825287</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.749955928354499</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.695098919485724</v>
+      </c>
+      <c r="L37" t="n">
+        <v>37.27325350820988</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.8837951853873</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>18.36826429033929</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-32006.93782961402</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.004353568931947</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000095e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.82821351609438</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1314.383</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7824644496156981</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1732.543980378587</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8170597629561122</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.57264e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.211</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1313457412788438</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.440704566292406</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.510458647452139</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.323166230389238</v>
+      </c>
+      <c r="L38" t="n">
+        <v>33.76551820004038</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.83410191399658</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>18.07937436872513</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-31086.68979129966</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.09898889680926</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000215e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8285616354157982</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1303.558</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7760202262294477</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1714.314689878795</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.808462913500456</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.57417e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-78.36499999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.353459504858812</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.132666423753909</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.694077240586154</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.602734985932872</v>
+      </c>
+      <c r="L39" t="n">
+        <v>39.2669945325752</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.98419580198654</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>18.98095929896683</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-32379.18983177853</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.361812202459078</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8289442752101198</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1286.945</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7661303525005076</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1700.105128980373</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8017617500143561</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.57495e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-78.496</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5501543546422062</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.251700665235457</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.957689468163936</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.205206508987711</v>
+      </c>
+      <c r="L40" t="n">
+        <v>45.97647248959593</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.12366954272167</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>19.9030119455071</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-33667.70040112365</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-1.254388185301423</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8293184717762465</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1267.219</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.754387280859198</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1680.338357113895</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7924398314261175</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.57697e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-78.697</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3493945162204768</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8543314544212635</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.710390318122641</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.807839724798174</v>
+      </c>
+      <c r="L41" t="n">
+        <v>42.42880582418234</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.08398938991256</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>19.6317193209327</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-32750.63359749494</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-1.292402569892374</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8297066466462508</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1246.586</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7421042636648789</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1663.500154743994</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7844990127266971</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.57805e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-78.84099999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4512036954263052</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9883676964958398</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.788345569724325</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.737193726092971</v>
+      </c>
+      <c r="L42" t="n">
+        <v>43.40387777232429</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.14094224806178</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>20.02345561047489</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-33032.99326825517</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-3.10835789792327</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000023054e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8301054528868912</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1220.686</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7266857522834577</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1646.356473281676</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7764141314939934</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.57798e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-78.97799999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1522414386676776</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8547876527996116</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.854582671808476</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.684667311948293</v>
+      </c>
+      <c r="L43" t="n">
+        <v>62.53527098464035</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.00352108731381</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>19.10359946225696</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-30999.43984475506</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-4.323414024908743</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8304928078988155</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.8288280427575897</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1656.272</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2196.089084195663</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.55519e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-72.762</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2984587129839105</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5503235085758734</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.295407063996701</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.201367887845575</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.06829981423687</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.00238532110781</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.518176228242169</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-19687.67058978109</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-55.82184097336653</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8258135490724141</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1418.672</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8565453017378789</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1849.88013977667</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8423520489626242</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.57788e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-76.021</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5473258795153151</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.915563526913495</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.668900354401958</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.655455202596611</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.74862233669194</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.7863302037798</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.57307300665303</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-24905.66372225419</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-3.441812370231105</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000602e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8265843011122188</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1354.417</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8177503453539032</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1779.961256548332</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8105141405045772</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.5718e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-77.06399999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3428758584215009</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7752308095820803</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.551726354173395</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.548997375451561</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25.35120121337593</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.21063658149419</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>15.09810750449062</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-26779.13229182119</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.588046419439365</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8267106954024259</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1320.446</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7972398253426974</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1747.659906775894</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7958055615107205</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.56788e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-77.556</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7096036637415876</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9578641893540959</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.499849518365299</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.141400817615567</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.93231034931165</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.327269592563</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.57894975621988</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-27094.24542119744</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.850034015339475</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000118e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8267997364134732</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1280.727</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.773258860863433</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1721.299648881532</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.783802288016915</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.56482e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-77.854</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0779883780275317</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5769559201787673</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.6304451067178</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.882517482755546</v>
+      </c>
+      <c r="L16" t="n">
+        <v>33.45898954220266</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.26507633017883</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.31881392212656</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-26104.72380503079</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.671134312554841</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000038e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8270244849704278</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1258.651</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7599301322488093</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1696.332446880768</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7724333493976019</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.56741e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-78.133</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2425594263848884</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.177764464245338</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.864105977116657</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.237019120512175</v>
+      </c>
+      <c r="L17" t="n">
+        <v>41.6141986595615</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.44243777535029</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.0846461414013</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-27035.56261448654</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.7460669541244442</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000583e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8273420005662727</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1237.212</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7469860022991393</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1670.041022942285</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7604614197852325</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.56929e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-78.286</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.438545367318975</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9688445409614496</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.427470375024197</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.783133730882984</v>
+      </c>
+      <c r="L18" t="n">
+        <v>28.97030910785634</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.628056008865</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.97229146442941</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-28160.04567139671</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-2.541899155619035</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8277202436395137</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1210.55</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7308884048030759</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1646.438251875716</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7497137815239121</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.57095e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-78.539</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4510895034805998</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7349982571398452</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.49288446168808</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.340661062500574</v>
+      </c>
+      <c r="L19" t="n">
+        <v>30.56489238584371</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.69976234518663</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.34190288765311</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-28316.6990865787</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-4.898928866860047</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.00000000000014e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8281014582459626</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1190.579</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7188306027029376</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1621.591673233809</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7383997693462109</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.57463e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-78.715</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5625408907901498</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.01682833919423</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.357429693205487</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.174363814642796</v>
+      </c>
+      <c r="L20" t="n">
+        <v>31.41782952084932</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.77015134218537</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17.72066813388714</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-28499.6313728429</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-6.042701182551582</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8284659277598504</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1163.373</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7024045567394728</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1599.663466093545</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7284146520310378</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.57704e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.87</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3773723588284709</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.92036495922839</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.588233970254703</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.44614223993069</v>
+      </c>
+      <c r="L21" t="n">
+        <v>32.16349160839334</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.81805336551434</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.98800242908816</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-28516.75874047502</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-7.227363732149911</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8288280427575897</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
